--- a/Lumin Light Financial Model - 2025-2026.xlsx
+++ b/Lumin Light Financial Model - 2025-2026.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Blended Gross Margin % (dollar-weighted across Sol 1-5 mix)</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: dollar-weighted, not simple-average-of-5-margins — matches scripts/config.py PRODUCTS</t>
+    <t xml:space="preserve">Empirically calibrated from an actual generate_sales_data() run (config.RANDOM_SEED=42), not a theoretical average — see Learning Doc 2.4. If PRODUCTS or RANDOM_SEED in config.py ever change, recheck this against a fresh run's realized margin.</t>
   </si>
   <si>
     <t xml:space="preserve">OPERATING EXPENSE ASSUMPTIONS</t>
@@ -855,7 +855,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1771,107 +1771,107 @@
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">SUM(D9:O9)</f>
-        <v>4356750</v>
+        <v>4136950</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">D6*(1-Assumptions!$C$11)</f>
-        <v>308603.125</v>
+        <v>293033.958333333</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">E6*(1-Assumptions!$C$11)</f>
-        <v>308603.125</v>
+        <v>293033.958333333</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">F6*(1-Assumptions!$C$11)</f>
-        <v>326756.25</v>
+        <v>310271.25</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">G6*(1-Assumptions!$C$11)</f>
-        <v>326756.25</v>
+        <v>310271.25</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">H6*(1-Assumptions!$C$11)</f>
-        <v>344909.375</v>
+        <v>327508.541666667</v>
       </c>
       <c r="I9" s="11" t="n">
         <f aca="false">I6*(1-Assumptions!$C$11)</f>
-        <v>363062.5</v>
+        <v>344745.833333333</v>
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">J6*(1-Assumptions!$C$11)</f>
-        <v>344909.375</v>
+        <v>327508.541666667</v>
       </c>
       <c r="K9" s="11" t="n">
         <f aca="false">K6*(1-Assumptions!$C$11)</f>
-        <v>326756.25</v>
+        <v>310271.25</v>
       </c>
       <c r="L9" s="11" t="n">
         <f aca="false">L6*(1-Assumptions!$C$11)</f>
-        <v>363062.5</v>
+        <v>344745.833333333</v>
       </c>
       <c r="M9" s="11" t="n">
         <f aca="false">M6*(1-Assumptions!$C$11)</f>
-        <v>381215.625</v>
+        <v>361983.125</v>
       </c>
       <c r="N9" s="11" t="n">
         <f aca="false">N6*(1-Assumptions!$C$11)</f>
-        <v>471981.25</v>
+        <v>448169.583333333</v>
       </c>
       <c r="O9" s="11" t="n">
         <f aca="false">O6*(1-Assumptions!$C$11)</f>
-        <v>490134.375</v>
+        <v>465406.875</v>
       </c>
       <c r="P9" s="7" t="n">
         <f aca="false">SUM(Q9:AB9)</f>
-        <v>4995000</v>
+        <v>4743000</v>
       </c>
       <c r="Q9" s="11" t="n">
         <f aca="false">Q6*(1-Assumptions!$C$11)</f>
-        <v>353812.5</v>
+        <v>335962.5</v>
       </c>
       <c r="R9" s="11" t="n">
         <f aca="false">R6*(1-Assumptions!$C$11)</f>
-        <v>353812.5</v>
+        <v>335962.5</v>
       </c>
       <c r="S9" s="11" t="n">
         <f aca="false">S6*(1-Assumptions!$C$11)</f>
-        <v>374625</v>
+        <v>355725</v>
       </c>
       <c r="T9" s="11" t="n">
         <f aca="false">T6*(1-Assumptions!$C$11)</f>
-        <v>374625</v>
+        <v>355725</v>
       </c>
       <c r="U9" s="11" t="n">
         <f aca="false">U6*(1-Assumptions!$C$11)</f>
-        <v>395437.5</v>
+        <v>375487.5</v>
       </c>
       <c r="V9" s="11" t="n">
         <f aca="false">V6*(1-Assumptions!$C$11)</f>
-        <v>416250</v>
+        <v>395250</v>
       </c>
       <c r="W9" s="11" t="n">
         <f aca="false">W6*(1-Assumptions!$C$11)</f>
-        <v>395437.5</v>
+        <v>375487.5</v>
       </c>
       <c r="X9" s="11" t="n">
         <f aca="false">X6*(1-Assumptions!$C$11)</f>
-        <v>374625</v>
+        <v>355725</v>
       </c>
       <c r="Y9" s="11" t="n">
         <f aca="false">Y6*(1-Assumptions!$C$11)</f>
-        <v>416250</v>
+        <v>395250</v>
       </c>
       <c r="Z9" s="11" t="n">
         <f aca="false">Z6*(1-Assumptions!$C$11)</f>
-        <v>437062.5</v>
+        <v>415012.5</v>
       </c>
       <c r="AA9" s="11" t="n">
         <f aca="false">AA6*(1-Assumptions!$C$11)</f>
-        <v>541125</v>
+        <v>513825</v>
       </c>
       <c r="AB9" s="11" t="n">
         <f aca="false">AB6*(1-Assumptions!$C$11)</f>
-        <v>561937.5</v>
+        <v>533587.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1880,107 +1880,107 @@
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(D11:O11)</f>
-        <v>3493250</v>
+        <v>3713050</v>
       </c>
       <c r="D11" s="7" t="n">
         <f aca="false">D6-D9</f>
-        <v>247438.541666667</v>
+        <v>263007.708333333</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">E6-E9</f>
-        <v>247438.541666667</v>
+        <v>263007.708333333</v>
       </c>
       <c r="F11" s="7" t="n">
         <f aca="false">F6-F9</f>
-        <v>261993.75</v>
+        <v>278478.75</v>
       </c>
       <c r="G11" s="7" t="n">
         <f aca="false">G6-G9</f>
-        <v>261993.75</v>
+        <v>278478.75</v>
       </c>
       <c r="H11" s="7" t="n">
         <f aca="false">H6-H9</f>
-        <v>276548.958333333</v>
+        <v>293949.791666667</v>
       </c>
       <c r="I11" s="7" t="n">
         <f aca="false">I6-I9</f>
-        <v>291104.166666667</v>
+        <v>309420.833333333</v>
       </c>
       <c r="J11" s="7" t="n">
         <f aca="false">J6-J9</f>
-        <v>276548.958333333</v>
+        <v>293949.791666667</v>
       </c>
       <c r="K11" s="7" t="n">
         <f aca="false">K6-K9</f>
-        <v>261993.75</v>
+        <v>278478.75</v>
       </c>
       <c r="L11" s="7" t="n">
         <f aca="false">L6-L9</f>
-        <v>291104.166666667</v>
+        <v>309420.833333333</v>
       </c>
       <c r="M11" s="7" t="n">
         <f aca="false">M6-M9</f>
-        <v>305659.375</v>
+        <v>324891.875</v>
       </c>
       <c r="N11" s="7" t="n">
         <f aca="false">N6-N9</f>
-        <v>378435.416666667</v>
+        <v>402247.083333333</v>
       </c>
       <c r="O11" s="7" t="n">
         <f aca="false">O6-O9</f>
-        <v>392990.625</v>
+        <v>417718.125</v>
       </c>
       <c r="P11" s="5" t="n">
         <f aca="false">SUM(Q11:AB11)</f>
-        <v>4005000</v>
+        <v>4257000</v>
       </c>
       <c r="Q11" s="7" t="n">
         <f aca="false">Q6-Q9</f>
-        <v>283687.5</v>
+        <v>301537.5</v>
       </c>
       <c r="R11" s="7" t="n">
         <f aca="false">R6-R9</f>
-        <v>283687.5</v>
+        <v>301537.5</v>
       </c>
       <c r="S11" s="7" t="n">
         <f aca="false">S6-S9</f>
-        <v>300375</v>
+        <v>319275</v>
       </c>
       <c r="T11" s="7" t="n">
         <f aca="false">T6-T9</f>
-        <v>300375</v>
+        <v>319275</v>
       </c>
       <c r="U11" s="7" t="n">
         <f aca="false">U6-U9</f>
-        <v>317062.5</v>
+        <v>337012.5</v>
       </c>
       <c r="V11" s="7" t="n">
         <f aca="false">V6-V9</f>
-        <v>333750</v>
+        <v>354750</v>
       </c>
       <c r="W11" s="7" t="n">
         <f aca="false">W6-W9</f>
-        <v>317062.5</v>
+        <v>337012.5</v>
       </c>
       <c r="X11" s="7" t="n">
         <f aca="false">X6-X9</f>
-        <v>300375</v>
+        <v>319275</v>
       </c>
       <c r="Y11" s="7" t="n">
         <f aca="false">Y6-Y9</f>
-        <v>333750</v>
+        <v>354750</v>
       </c>
       <c r="Z11" s="7" t="n">
         <f aca="false">Z6-Z9</f>
-        <v>350437.5</v>
+        <v>372487.5</v>
       </c>
       <c r="AA11" s="7" t="n">
         <f aca="false">AA6-AA9</f>
-        <v>433875</v>
+        <v>461175</v>
       </c>
       <c r="AB11" s="7" t="n">
         <f aca="false">AB6-AB9</f>
-        <v>450562.5</v>
+        <v>478912.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1989,107 +1989,107 @@
       </c>
       <c r="C12" s="13" t="n">
         <f aca="false">IF(C6=0,0,C11/C6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">IF(D6=0,0,D11/D6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">IF(E6=0,0,E11/E6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">IF(F6=0,0,F11/F6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="G12" s="13" t="n">
         <f aca="false">IF(G6=0,0,G11/G6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">IF(H6=0,0,H11/H6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="I12" s="13" t="n">
         <f aca="false">IF(I6=0,0,I11/I6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="J12" s="13" t="n">
         <f aca="false">IF(J6=0,0,J11/J6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="K12" s="13" t="n">
         <f aca="false">IF(K6=0,0,K11/K6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="L12" s="13" t="n">
         <f aca="false">IF(L6=0,0,L11/L6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="M12" s="13" t="n">
         <f aca="false">IF(M6=0,0,M11/M6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="N12" s="13" t="n">
         <f aca="false">IF(N6=0,0,N11/N6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="O12" s="13" t="n">
         <f aca="false">IF(O6=0,0,O11/O6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="P12" s="13" t="n">
         <f aca="false">IF(P6=0,0,P11/P6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="Q12" s="13" t="n">
         <f aca="false">IF(Q6=0,0,Q11/Q6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="R12" s="13" t="n">
         <f aca="false">IF(R6=0,0,R11/R6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="S12" s="13" t="n">
         <f aca="false">IF(S6=0,0,S11/S6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="T12" s="13" t="n">
         <f aca="false">IF(T6=0,0,T11/T6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="U12" s="13" t="n">
         <f aca="false">IF(U6=0,0,U11/U6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="V12" s="13" t="n">
         <f aca="false">IF(V6=0,0,V11/V6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="W12" s="13" t="n">
         <f aca="false">IF(W6=0,0,W11/W6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="X12" s="13" t="n">
         <f aca="false">IF(X6=0,0,X11/X6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="Y12" s="13" t="n">
         <f aca="false">IF(Y6=0,0,Y11/Y6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="Z12" s="13" t="n">
         <f aca="false">IF(Z6=0,0,Z11/Z6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="AA12" s="13" t="n">
         <f aca="false">IF(AA6=0,0,AA11/AA6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="AB12" s="13" t="n">
         <f aca="false">IF(AB6=0,0,AB11/AB6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3084,107 +3084,107 @@
       </c>
       <c r="C25" s="5" t="n">
         <f aca="false">SUM(D25:O25)</f>
-        <v>300000</v>
+        <v>519800</v>
       </c>
       <c r="D25" s="5" t="n">
         <f aca="false">D11-D23</f>
-        <v>-16703.125</v>
+        <v>-1133.95833333337</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">E11-E23</f>
-        <v>-16703.125</v>
+        <v>-1133.95833333337</v>
       </c>
       <c r="F25" s="5" t="n">
         <f aca="false">F11-F23</f>
-        <v>-2802.08333333331</v>
+        <v>13682.9166666666</v>
       </c>
       <c r="G25" s="5" t="n">
         <f aca="false">G11-G23</f>
-        <v>-2802.08333333331</v>
+        <v>13682.9166666666</v>
       </c>
       <c r="H25" s="5" t="n">
         <f aca="false">H11-H23</f>
-        <v>11098.9583333334</v>
+        <v>28499.7916666667</v>
       </c>
       <c r="I25" s="5" t="n">
         <f aca="false">I11-I23</f>
-        <v>25000</v>
+        <v>43316.6666666666</v>
       </c>
       <c r="J25" s="5" t="n">
         <f aca="false">J11-J23</f>
-        <v>11098.9583333334</v>
+        <v>28499.7916666667</v>
       </c>
       <c r="K25" s="5" t="n">
         <f aca="false">K11-K23</f>
-        <v>-2802.08333333331</v>
+        <v>13682.9166666666</v>
       </c>
       <c r="L25" s="5" t="n">
         <f aca="false">L11-L23</f>
-        <v>25000</v>
+        <v>43316.6666666666</v>
       </c>
       <c r="M25" s="5" t="n">
         <f aca="false">M11-M23</f>
-        <v>38901.0416666667</v>
+        <v>58133.5416666666</v>
       </c>
       <c r="N25" s="5" t="n">
         <f aca="false">N11-N23</f>
-        <v>108406.25</v>
+        <v>132217.916666667</v>
       </c>
       <c r="O25" s="5" t="n">
         <f aca="false">O11-O23</f>
-        <v>122307.291666667</v>
+        <v>147034.791666667</v>
       </c>
       <c r="P25" s="5" t="n">
         <f aca="false">SUM(Q25:AB25)</f>
-        <v>682481.250000002</v>
+        <v>934481.250000001</v>
       </c>
       <c r="Q25" s="5" t="n">
         <f aca="false">Q11-Q23</f>
-        <v>9060.93750000012</v>
+        <v>26910.9375000001</v>
       </c>
       <c r="R25" s="5" t="n">
         <f aca="false">R11-R23</f>
-        <v>9060.93750000012</v>
+        <v>26910.9375000001</v>
       </c>
       <c r="S25" s="5" t="n">
         <f aca="false">S11-S23</f>
-        <v>24998.4375000001</v>
+        <v>43898.4375000001</v>
       </c>
       <c r="T25" s="5" t="n">
         <f aca="false">T11-T23</f>
-        <v>24998.4375000001</v>
+        <v>43898.4375000001</v>
       </c>
       <c r="U25" s="5" t="n">
         <f aca="false">U11-U23</f>
-        <v>40935.9375000001</v>
+        <v>60885.9375000001</v>
       </c>
       <c r="V25" s="5" t="n">
         <f aca="false">V11-V23</f>
-        <v>56873.4375000001</v>
+        <v>77873.4375000001</v>
       </c>
       <c r="W25" s="5" t="n">
         <f aca="false">W11-W23</f>
-        <v>40935.9375000001</v>
+        <v>60885.9375000001</v>
       </c>
       <c r="X25" s="5" t="n">
         <f aca="false">X11-X23</f>
-        <v>24998.4375000001</v>
+        <v>43898.4375000001</v>
       </c>
       <c r="Y25" s="5" t="n">
         <f aca="false">Y11-Y23</f>
-        <v>56873.4375000001</v>
+        <v>77873.4375000001</v>
       </c>
       <c r="Z25" s="5" t="n">
         <f aca="false">Z11-Z23</f>
-        <v>72810.9375000001</v>
+        <v>94860.9375000001</v>
       </c>
       <c r="AA25" s="5" t="n">
         <f aca="false">AA11-AA23</f>
-        <v>152498.4375</v>
+        <v>179798.4375</v>
       </c>
       <c r="AB25" s="5" t="n">
         <f aca="false">AB11-AB23</f>
-        <v>168435.9375</v>
+        <v>196785.9375</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3193,107 +3193,107 @@
       </c>
       <c r="C26" s="13" t="n">
         <f aca="false">IF(C6=0,0,C25/C6)</f>
-        <v>0.0382165605095542</v>
+        <v>0.0662165605095541</v>
       </c>
       <c r="D26" s="13" t="n">
         <f aca="false">IF(D6=0,0,D25/D6)</f>
-        <v>-0.0300393405769951</v>
+        <v>-0.0020393405769952</v>
       </c>
       <c r="E26" s="13" t="n">
         <f aca="false">IF(E6=0,0,E25/E6)</f>
-        <v>-0.0300393405769951</v>
+        <v>-0.0020393405769952</v>
       </c>
       <c r="F26" s="13" t="n">
         <f aca="false">IF(F6=0,0,F25/F6)</f>
-        <v>-0.00475937721160648</v>
+        <v>0.0232406227883934</v>
       </c>
       <c r="G26" s="13" t="n">
         <f aca="false">IF(G6=0,0,G25/G6)</f>
-        <v>-0.00475937721160648</v>
+        <v>0.0232406227883934</v>
       </c>
       <c r="H26" s="13" t="n">
         <f aca="false">IF(H6=0,0,H25/H6)</f>
-        <v>0.0178595373784781</v>
+        <v>0.0458595373784781</v>
       </c>
       <c r="I26" s="13" t="n">
         <f aca="false">IF(I6=0,0,I25/I6)</f>
-        <v>0.0382165605095541</v>
+        <v>0.0662165605095541</v>
       </c>
       <c r="J26" s="13" t="n">
         <f aca="false">IF(J6=0,0,J25/J6)</f>
-        <v>0.0178595373784781</v>
+        <v>0.0458595373784781</v>
       </c>
       <c r="K26" s="13" t="n">
         <f aca="false">IF(K6=0,0,K25/K6)</f>
-        <v>-0.00475937721160648</v>
+        <v>0.0232406227883934</v>
       </c>
       <c r="L26" s="13" t="n">
         <f aca="false">IF(L6=0,0,L25/L6)</f>
-        <v>0.0382165605095541</v>
+        <v>0.0662165605095541</v>
       </c>
       <c r="M26" s="13" t="n">
         <f aca="false">IF(M6=0,0,M25/M6)</f>
-        <v>0.0566348195329087</v>
+        <v>0.0846348195329087</v>
       </c>
       <c r="N26" s="13" t="n">
         <f aca="false">IF(N6=0,0,N25/N6)</f>
-        <v>0.127474277315042</v>
+        <v>0.155474277315042</v>
       </c>
       <c r="O26" s="13" t="n">
         <f aca="false">IF(O6=0,0,O25/O6)</f>
-        <v>0.138493748525596</v>
+        <v>0.166493748525596</v>
       </c>
       <c r="P26" s="13" t="n">
         <f aca="false">IF(P6=0,0,P25/P6)</f>
-        <v>0.0758312500000002</v>
+        <v>0.10383125</v>
       </c>
       <c r="Q26" s="13" t="n">
         <f aca="false">IF(Q6=0,0,Q25/Q6)</f>
-        <v>0.0142132352941178</v>
+        <v>0.0422132352941177</v>
       </c>
       <c r="R26" s="13" t="n">
         <f aca="false">IF(R6=0,0,R25/R6)</f>
-        <v>0.0142132352941178</v>
+        <v>0.0422132352941177</v>
       </c>
       <c r="S26" s="13" t="n">
         <f aca="false">IF(S6=0,0,S25/S6)</f>
-        <v>0.0370347222222224</v>
+        <v>0.0650347222222223</v>
       </c>
       <c r="T26" s="13" t="n">
         <f aca="false">IF(T6=0,0,T25/T6)</f>
-        <v>0.0370347222222224</v>
+        <v>0.0650347222222223</v>
       </c>
       <c r="U26" s="13" t="n">
         <f aca="false">IF(U6=0,0,U25/U6)</f>
-        <v>0.0574539473684212</v>
+        <v>0.0854539473684211</v>
       </c>
       <c r="V26" s="13" t="n">
         <f aca="false">IF(V6=0,0,V25/V6)</f>
-        <v>0.0758312500000002</v>
+        <v>0.10383125</v>
       </c>
       <c r="W26" s="13" t="n">
         <f aca="false">IF(W6=0,0,W25/W6)</f>
-        <v>0.0574539473684212</v>
+        <v>0.0854539473684211</v>
       </c>
       <c r="X26" s="13" t="n">
         <f aca="false">IF(X6=0,0,X25/X6)</f>
-        <v>0.0370347222222224</v>
+        <v>0.0650347222222223</v>
       </c>
       <c r="Y26" s="13" t="n">
         <f aca="false">IF(Y6=0,0,Y25/Y6)</f>
-        <v>0.0758312500000002</v>
+        <v>0.10383125</v>
       </c>
       <c r="Z26" s="13" t="n">
         <f aca="false">IF(Z6=0,0,Z25/Z6)</f>
-        <v>0.0924583333333335</v>
+        <v>0.120458333333333</v>
       </c>
       <c r="AA26" s="13" t="n">
         <f aca="false">IF(AA6=0,0,AA25/AA6)</f>
-        <v>0.156408653846154</v>
+        <v>0.184408653846154</v>
       </c>
       <c r="AB26" s="13" t="n">
         <f aca="false">IF(AB6=0,0,AB25/AB6)</f>
-        <v>0.166356481481482</v>
+        <v>0.194356481481482</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3411,107 +3411,107 @@
       </c>
       <c r="C30" s="5" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>260000</v>
+        <v>479800</v>
       </c>
       <c r="D30" s="5" t="n">
         <f aca="false">D25-D28</f>
-        <v>-20036.4583333333</v>
+        <v>-4467.29166666671</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">E25-E28</f>
-        <v>-20036.4583333333</v>
+        <v>-4467.29166666671</v>
       </c>
       <c r="F30" s="5" t="n">
         <f aca="false">F25-F28</f>
-        <v>-6135.41666666665</v>
+        <v>10349.5833333333</v>
       </c>
       <c r="G30" s="5" t="n">
         <f aca="false">G25-G28</f>
-        <v>-6135.41666666665</v>
+        <v>10349.5833333333</v>
       </c>
       <c r="H30" s="5" t="n">
         <f aca="false">H25-H28</f>
-        <v>7765.62500000004</v>
+        <v>25166.4583333334</v>
       </c>
       <c r="I30" s="5" t="n">
         <f aca="false">I25-I28</f>
-        <v>21666.6666666667</v>
+        <v>39983.3333333333</v>
       </c>
       <c r="J30" s="5" t="n">
         <f aca="false">J25-J28</f>
-        <v>7765.62500000004</v>
+        <v>25166.4583333334</v>
       </c>
       <c r="K30" s="5" t="n">
         <f aca="false">K25-K28</f>
-        <v>-6135.41666666665</v>
+        <v>10349.5833333333</v>
       </c>
       <c r="L30" s="5" t="n">
         <f aca="false">L25-L28</f>
-        <v>21666.6666666667</v>
+        <v>39983.3333333333</v>
       </c>
       <c r="M30" s="5" t="n">
         <f aca="false">M25-M28</f>
-        <v>35567.7083333334</v>
+        <v>54800.2083333333</v>
       </c>
       <c r="N30" s="5" t="n">
         <f aca="false">N25-N28</f>
-        <v>105072.916666667</v>
+        <v>128884.583333333</v>
       </c>
       <c r="O30" s="5" t="n">
         <f aca="false">O25-O28</f>
-        <v>118973.958333333</v>
+        <v>143701.458333333</v>
       </c>
       <c r="P30" s="5" t="n">
         <f aca="false">SUM(Q30:AB30)</f>
-        <v>642481.250000002</v>
+        <v>894481.250000001</v>
       </c>
       <c r="Q30" s="5" t="n">
         <f aca="false">Q25-Q28</f>
-        <v>5727.60416666678</v>
+        <v>23577.6041666667</v>
       </c>
       <c r="R30" s="5" t="n">
         <f aca="false">R25-R28</f>
-        <v>5727.60416666678</v>
+        <v>23577.6041666667</v>
       </c>
       <c r="S30" s="5" t="n">
         <f aca="false">S25-S28</f>
-        <v>21665.1041666668</v>
+        <v>40565.1041666667</v>
       </c>
       <c r="T30" s="5" t="n">
         <f aca="false">T25-T28</f>
-        <v>21665.1041666668</v>
+        <v>40565.1041666667</v>
       </c>
       <c r="U30" s="5" t="n">
         <f aca="false">U25-U28</f>
-        <v>37602.6041666668</v>
+        <v>57552.6041666667</v>
       </c>
       <c r="V30" s="5" t="n">
         <f aca="false">V25-V28</f>
-        <v>53540.1041666668</v>
+        <v>74540.1041666667</v>
       </c>
       <c r="W30" s="5" t="n">
         <f aca="false">W25-W28</f>
-        <v>37602.6041666668</v>
+        <v>57552.6041666667</v>
       </c>
       <c r="X30" s="5" t="n">
         <f aca="false">X25-X28</f>
-        <v>21665.1041666668</v>
+        <v>40565.1041666667</v>
       </c>
       <c r="Y30" s="5" t="n">
         <f aca="false">Y25-Y28</f>
-        <v>53540.1041666668</v>
+        <v>74540.1041666667</v>
       </c>
       <c r="Z30" s="5" t="n">
         <f aca="false">Z25-Z28</f>
-        <v>69477.6041666668</v>
+        <v>91527.6041666667</v>
       </c>
       <c r="AA30" s="5" t="n">
         <f aca="false">AA25-AA28</f>
-        <v>149165.104166667</v>
+        <v>176465.104166667</v>
       </c>
       <c r="AB30" s="5" t="n">
         <f aca="false">AB25-AB28</f>
-        <v>165102.604166667</v>
+        <v>193452.604166667</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3520,107 +3520,107 @@
       </c>
       <c r="C31" s="13" t="n">
         <f aca="false">IF(C6=0,0,C30/C6)</f>
-        <v>0.0331210191082803</v>
+        <v>0.0611210191082802</v>
       </c>
       <c r="D31" s="13" t="n">
         <f aca="false">IF(D6=0,0,D30/D6)</f>
-        <v>-0.0360340951667291</v>
+        <v>-0.00803409516672918</v>
       </c>
       <c r="E31" s="13" t="n">
         <f aca="false">IF(E6=0,0,E30/E6)</f>
-        <v>-0.0360340951667291</v>
+        <v>-0.00803409516672918</v>
       </c>
       <c r="F31" s="13" t="n">
         <f aca="false">IF(F6=0,0,F30/F6)</f>
-        <v>-0.0104210898796886</v>
+        <v>0.0175789101203113</v>
       </c>
       <c r="G31" s="13" t="n">
         <f aca="false">IF(G6=0,0,G30/G6)</f>
-        <v>-0.0104210898796886</v>
+        <v>0.0175789101203113</v>
       </c>
       <c r="H31" s="13" t="n">
         <f aca="false">IF(H6=0,0,H30/H6)</f>
-        <v>0.0124958095876635</v>
+        <v>0.0404958095876635</v>
       </c>
       <c r="I31" s="13" t="n">
         <f aca="false">IF(I6=0,0,I30/I6)</f>
-        <v>0.0331210191082803</v>
+        <v>0.0611210191082802</v>
       </c>
       <c r="J31" s="13" t="n">
         <f aca="false">IF(J6=0,0,J30/J6)</f>
-        <v>0.0124958095876635</v>
+        <v>0.0404958095876635</v>
       </c>
       <c r="K31" s="13" t="n">
         <f aca="false">IF(K6=0,0,K30/K6)</f>
-        <v>-0.0104210898796886</v>
+        <v>0.0175789101203113</v>
       </c>
       <c r="L31" s="13" t="n">
         <f aca="false">IF(L6=0,0,L30/L6)</f>
-        <v>0.0331210191082803</v>
+        <v>0.0611210191082802</v>
       </c>
       <c r="M31" s="13" t="n">
         <f aca="false">IF(M6=0,0,M30/M6)</f>
-        <v>0.0517819229602669</v>
+        <v>0.0797819229602668</v>
       </c>
       <c r="N31" s="13" t="n">
         <f aca="false">IF(N6=0,0,N30/N6)</f>
-        <v>0.123554630083293</v>
+        <v>0.151554630083292</v>
       </c>
       <c r="O31" s="13" t="n">
         <f aca="false">IF(O6=0,0,O30/O6)</f>
-        <v>0.134719273413541</v>
+        <v>0.162719273413541</v>
       </c>
       <c r="P31" s="13" t="n">
         <f aca="false">IF(P6=0,0,P30/P6)</f>
-        <v>0.0713868055555557</v>
+        <v>0.0993868055555556</v>
       </c>
       <c r="Q31" s="13" t="n">
         <f aca="false">IF(Q6=0,0,Q30/Q6)</f>
-        <v>0.00898447712418319</v>
+        <v>0.0369844771241831</v>
       </c>
       <c r="R31" s="13" t="n">
         <f aca="false">IF(R6=0,0,R30/R6)</f>
-        <v>0.00898447712418319</v>
+        <v>0.0369844771241831</v>
       </c>
       <c r="S31" s="13" t="n">
         <f aca="false">IF(S6=0,0,S30/S6)</f>
-        <v>0.0320964506172841</v>
+        <v>0.060096450617284</v>
       </c>
       <c r="T31" s="13" t="n">
         <f aca="false">IF(T6=0,0,T30/T6)</f>
-        <v>0.0320964506172841</v>
+        <v>0.060096450617284</v>
       </c>
       <c r="U31" s="13" t="n">
         <f aca="false">IF(U6=0,0,U30/U6)</f>
-        <v>0.0527755847953218</v>
+        <v>0.0807755847953217</v>
       </c>
       <c r="V31" s="13" t="n">
         <f aca="false">IF(V6=0,0,V30/V6)</f>
-        <v>0.0713868055555557</v>
+        <v>0.0993868055555556</v>
       </c>
       <c r="W31" s="13" t="n">
         <f aca="false">IF(W6=0,0,W30/W6)</f>
-        <v>0.0527755847953218</v>
+        <v>0.0807755847953217</v>
       </c>
       <c r="X31" s="13" t="n">
         <f aca="false">IF(X6=0,0,X30/X6)</f>
-        <v>0.0320964506172841</v>
+        <v>0.060096450617284</v>
       </c>
       <c r="Y31" s="13" t="n">
         <f aca="false">IF(Y6=0,0,Y30/Y6)</f>
-        <v>0.0713868055555557</v>
+        <v>0.0993868055555556</v>
       </c>
       <c r="Z31" s="13" t="n">
         <f aca="false">IF(Z6=0,0,Z30/Z6)</f>
-        <v>0.0882255291005293</v>
+        <v>0.116225529100529</v>
       </c>
       <c r="AA31" s="13" t="n">
         <f aca="false">IF(AA6=0,0,AA30/AA6)</f>
-        <v>0.152989850427351</v>
+        <v>0.18098985042735</v>
       </c>
       <c r="AB31" s="13" t="n">
         <f aca="false">IF(AB6=0,0,AB30/AB6)</f>
-        <v>0.163064300411523</v>
+        <v>0.191064300411523</v>
       </c>
     </row>
   </sheetData>
@@ -3855,107 +3855,107 @@
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">SUM(D9:O9)</f>
-        <v>2830500</v>
+        <v>2687700</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">D6*(1-Assumptions!$C$11)</f>
-        <v>200493.75</v>
+        <v>190378.75</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">E6*(1-Assumptions!$C$11)</f>
-        <v>200493.75</v>
+        <v>190378.75</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">F6*(1-Assumptions!$C$11)</f>
-        <v>212287.5</v>
+        <v>201577.5</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">G6*(1-Assumptions!$C$11)</f>
-        <v>212287.5</v>
+        <v>201577.5</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">H6*(1-Assumptions!$C$11)</f>
-        <v>224081.25</v>
+        <v>212776.25</v>
       </c>
       <c r="I9" s="11" t="n">
         <f aca="false">I6*(1-Assumptions!$C$11)</f>
-        <v>235875</v>
+        <v>223975</v>
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">J6*(1-Assumptions!$C$11)</f>
-        <v>224081.25</v>
+        <v>212776.25</v>
       </c>
       <c r="K9" s="11" t="n">
         <f aca="false">K6*(1-Assumptions!$C$11)</f>
-        <v>212287.5</v>
+        <v>201577.5</v>
       </c>
       <c r="L9" s="11" t="n">
         <f aca="false">L6*(1-Assumptions!$C$11)</f>
-        <v>235875</v>
+        <v>223975</v>
       </c>
       <c r="M9" s="11" t="n">
         <f aca="false">M6*(1-Assumptions!$C$11)</f>
-        <v>247668.75</v>
+        <v>235173.75</v>
       </c>
       <c r="N9" s="11" t="n">
         <f aca="false">N6*(1-Assumptions!$C$11)</f>
-        <v>306637.5</v>
+        <v>291167.5</v>
       </c>
       <c r="O9" s="11" t="n">
         <f aca="false">O6*(1-Assumptions!$C$11)</f>
-        <v>318431.25</v>
+        <v>302366.25</v>
       </c>
       <c r="P9" s="7" t="n">
         <f aca="false">SUM(Q9:AB9)</f>
-        <v>3330000</v>
+        <v>3162000</v>
       </c>
       <c r="Q9" s="11" t="n">
         <f aca="false">Q6*(1-Assumptions!$C$11)</f>
-        <v>235875</v>
+        <v>223975</v>
       </c>
       <c r="R9" s="11" t="n">
         <f aca="false">R6*(1-Assumptions!$C$11)</f>
-        <v>235875</v>
+        <v>223975</v>
       </c>
       <c r="S9" s="11" t="n">
         <f aca="false">S6*(1-Assumptions!$C$11)</f>
-        <v>249750</v>
+        <v>237150</v>
       </c>
       <c r="T9" s="11" t="n">
         <f aca="false">T6*(1-Assumptions!$C$11)</f>
-        <v>249750</v>
+        <v>237150</v>
       </c>
       <c r="U9" s="11" t="n">
         <f aca="false">U6*(1-Assumptions!$C$11)</f>
-        <v>263625</v>
+        <v>250325</v>
       </c>
       <c r="V9" s="11" t="n">
         <f aca="false">V6*(1-Assumptions!$C$11)</f>
-        <v>277500</v>
+        <v>263500</v>
       </c>
       <c r="W9" s="11" t="n">
         <f aca="false">W6*(1-Assumptions!$C$11)</f>
-        <v>263625</v>
+        <v>250325</v>
       </c>
       <c r="X9" s="11" t="n">
         <f aca="false">X6*(1-Assumptions!$C$11)</f>
-        <v>249750</v>
+        <v>237150</v>
       </c>
       <c r="Y9" s="11" t="n">
         <f aca="false">Y6*(1-Assumptions!$C$11)</f>
-        <v>277500</v>
+        <v>263500</v>
       </c>
       <c r="Z9" s="11" t="n">
         <f aca="false">Z6*(1-Assumptions!$C$11)</f>
-        <v>291375</v>
+        <v>276675</v>
       </c>
       <c r="AA9" s="11" t="n">
         <f aca="false">AA6*(1-Assumptions!$C$11)</f>
-        <v>360750</v>
+        <v>342550</v>
       </c>
       <c r="AB9" s="11" t="n">
         <f aca="false">AB6*(1-Assumptions!$C$11)</f>
-        <v>374625</v>
+        <v>355725</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3964,107 +3964,107 @@
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(D11:O11)</f>
-        <v>2269500</v>
+        <v>2412300</v>
       </c>
       <c r="D11" s="7" t="n">
         <f aca="false">D6-D9</f>
-        <v>160756.25</v>
+        <v>170871.25</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">E6-E9</f>
-        <v>160756.25</v>
+        <v>170871.25</v>
       </c>
       <c r="F11" s="7" t="n">
         <f aca="false">F6-F9</f>
-        <v>170212.5</v>
+        <v>180922.5</v>
       </c>
       <c r="G11" s="7" t="n">
         <f aca="false">G6-G9</f>
-        <v>170212.5</v>
+        <v>180922.5</v>
       </c>
       <c r="H11" s="7" t="n">
         <f aca="false">H6-H9</f>
-        <v>179668.75</v>
+        <v>190973.75</v>
       </c>
       <c r="I11" s="7" t="n">
         <f aca="false">I6-I9</f>
-        <v>189125</v>
+        <v>201025</v>
       </c>
       <c r="J11" s="7" t="n">
         <f aca="false">J6-J9</f>
-        <v>179668.75</v>
+        <v>190973.75</v>
       </c>
       <c r="K11" s="7" t="n">
         <f aca="false">K6-K9</f>
-        <v>170212.5</v>
+        <v>180922.5</v>
       </c>
       <c r="L11" s="7" t="n">
         <f aca="false">L6-L9</f>
-        <v>189125</v>
+        <v>201025</v>
       </c>
       <c r="M11" s="7" t="n">
         <f aca="false">M6-M9</f>
-        <v>198581.25</v>
+        <v>211076.25</v>
       </c>
       <c r="N11" s="7" t="n">
         <f aca="false">N6-N9</f>
-        <v>245862.5</v>
+        <v>261332.5</v>
       </c>
       <c r="O11" s="7" t="n">
         <f aca="false">O6-O9</f>
-        <v>255318.75</v>
+        <v>271383.75</v>
       </c>
       <c r="P11" s="5" t="n">
         <f aca="false">SUM(Q11:AB11)</f>
-        <v>2670000</v>
+        <v>2838000</v>
       </c>
       <c r="Q11" s="7" t="n">
         <f aca="false">Q6-Q9</f>
-        <v>189125</v>
+        <v>201025</v>
       </c>
       <c r="R11" s="7" t="n">
         <f aca="false">R6-R9</f>
-        <v>189125</v>
+        <v>201025</v>
       </c>
       <c r="S11" s="7" t="n">
         <f aca="false">S6-S9</f>
-        <v>200250</v>
+        <v>212850</v>
       </c>
       <c r="T11" s="7" t="n">
         <f aca="false">T6-T9</f>
-        <v>200250</v>
+        <v>212850</v>
       </c>
       <c r="U11" s="7" t="n">
         <f aca="false">U6-U9</f>
-        <v>211375</v>
+        <v>224675</v>
       </c>
       <c r="V11" s="7" t="n">
         <f aca="false">V6-V9</f>
-        <v>222500</v>
+        <v>236500</v>
       </c>
       <c r="W11" s="7" t="n">
         <f aca="false">W6-W9</f>
-        <v>211375</v>
+        <v>224675</v>
       </c>
       <c r="X11" s="7" t="n">
         <f aca="false">X6-X9</f>
-        <v>200250</v>
+        <v>212850</v>
       </c>
       <c r="Y11" s="7" t="n">
         <f aca="false">Y6-Y9</f>
-        <v>222500</v>
+        <v>236500</v>
       </c>
       <c r="Z11" s="7" t="n">
         <f aca="false">Z6-Z9</f>
-        <v>233625</v>
+        <v>248325</v>
       </c>
       <c r="AA11" s="7" t="n">
         <f aca="false">AA6-AA9</f>
-        <v>289250</v>
+        <v>307450</v>
       </c>
       <c r="AB11" s="7" t="n">
         <f aca="false">AB6-AB9</f>
-        <v>300375</v>
+        <v>319275</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4073,107 +4073,107 @@
       </c>
       <c r="C12" s="13" t="n">
         <f aca="false">IF(C6=0,0,C11/C6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">IF(D6=0,0,D11/D6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">IF(E6=0,0,E11/E6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">IF(F6=0,0,F11/F6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="G12" s="13" t="n">
         <f aca="false">IF(G6=0,0,G11/G6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">IF(H6=0,0,H11/H6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="I12" s="13" t="n">
         <f aca="false">IF(I6=0,0,I11/I6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="J12" s="13" t="n">
         <f aca="false">IF(J6=0,0,J11/J6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="K12" s="13" t="n">
         <f aca="false">IF(K6=0,0,K11/K6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="L12" s="13" t="n">
         <f aca="false">IF(L6=0,0,L11/L6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="M12" s="13" t="n">
         <f aca="false">IF(M6=0,0,M11/M6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="N12" s="13" t="n">
         <f aca="false">IF(N6=0,0,N11/N6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="O12" s="13" t="n">
         <f aca="false">IF(O6=0,0,O11/O6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="P12" s="13" t="n">
         <f aca="false">IF(P6=0,0,P11/P6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="Q12" s="13" t="n">
         <f aca="false">IF(Q6=0,0,Q11/Q6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="R12" s="13" t="n">
         <f aca="false">IF(R6=0,0,R11/R6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="S12" s="13" t="n">
         <f aca="false">IF(S6=0,0,S11/S6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="T12" s="13" t="n">
         <f aca="false">IF(T6=0,0,T11/T6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="U12" s="13" t="n">
         <f aca="false">IF(U6=0,0,U11/U6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="V12" s="13" t="n">
         <f aca="false">IF(V6=0,0,V11/V6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="W12" s="13" t="n">
         <f aca="false">IF(W6=0,0,W11/W6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="X12" s="13" t="n">
         <f aca="false">IF(X6=0,0,X11/X6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="Y12" s="13" t="n">
         <f aca="false">IF(Y6=0,0,Y11/Y6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="Z12" s="13" t="n">
         <f aca="false">IF(Z6=0,0,Z11/Z6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="AA12" s="13" t="n">
         <f aca="false">IF(AA6=0,0,AA11/AA6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="AB12" s="13" t="n">
         <f aca="false">IF(AB6=0,0,AB11/AB6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5168,107 +5168,107 @@
       </c>
       <c r="C25" s="5" t="n">
         <f aca="false">SUM(D25:O25)</f>
-        <v>1051250</v>
+        <v>1194050</v>
       </c>
       <c r="D25" s="5" t="n">
         <f aca="false">D11-D23</f>
-        <v>60510.4166666667</v>
+        <v>70625.4166666667</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">E11-E23</f>
-        <v>60510.4166666667</v>
+        <v>70625.4166666667</v>
       </c>
       <c r="F25" s="5" t="n">
         <f aca="false">F11-F23</f>
-        <v>69541.6666666667</v>
+        <v>80251.6666666667</v>
       </c>
       <c r="G25" s="5" t="n">
         <f aca="false">G11-G23</f>
-        <v>69541.6666666667</v>
+        <v>80251.6666666667</v>
       </c>
       <c r="H25" s="5" t="n">
         <f aca="false">H11-H23</f>
-        <v>78572.9166666667</v>
+        <v>89877.9166666667</v>
       </c>
       <c r="I25" s="5" t="n">
         <f aca="false">I11-I23</f>
-        <v>87604.1666666667</v>
+        <v>99504.1666666667</v>
       </c>
       <c r="J25" s="5" t="n">
         <f aca="false">J11-J23</f>
-        <v>78572.9166666667</v>
+        <v>89877.9166666667</v>
       </c>
       <c r="K25" s="5" t="n">
         <f aca="false">K11-K23</f>
-        <v>69541.6666666667</v>
+        <v>80251.6666666667</v>
       </c>
       <c r="L25" s="5" t="n">
         <f aca="false">L11-L23</f>
-        <v>87604.1666666667</v>
+        <v>99504.1666666667</v>
       </c>
       <c r="M25" s="5" t="n">
         <f aca="false">M11-M23</f>
-        <v>96635.4166666667</v>
+        <v>109130.416666667</v>
       </c>
       <c r="N25" s="5" t="n">
         <f aca="false">N11-N23</f>
-        <v>141791.666666667</v>
+        <v>157261.666666667</v>
       </c>
       <c r="O25" s="5" t="n">
         <f aca="false">O11-O23</f>
-        <v>150822.916666667</v>
+        <v>166887.916666667</v>
       </c>
       <c r="P25" s="5" t="n">
         <f aca="false">SUM(Q25:AB25)</f>
-        <v>1394681.25</v>
+        <v>1562681.25</v>
       </c>
       <c r="Q25" s="5" t="n">
         <f aca="false">Q11-Q23</f>
-        <v>84348.4375</v>
+        <v>96248.4375</v>
       </c>
       <c r="R25" s="5" t="n">
         <f aca="false">R11-R23</f>
-        <v>84348.4375</v>
+        <v>96248.4375</v>
       </c>
       <c r="S25" s="5" t="n">
         <f aca="false">S11-S23</f>
-        <v>94973.4375</v>
+        <v>107573.4375</v>
       </c>
       <c r="T25" s="5" t="n">
         <f aca="false">T11-T23</f>
-        <v>94973.4375</v>
+        <v>107573.4375</v>
       </c>
       <c r="U25" s="5" t="n">
         <f aca="false">U11-U23</f>
-        <v>105598.4375</v>
+        <v>118898.4375</v>
       </c>
       <c r="V25" s="5" t="n">
         <f aca="false">V11-V23</f>
-        <v>116223.4375</v>
+        <v>130223.4375</v>
       </c>
       <c r="W25" s="5" t="n">
         <f aca="false">W11-W23</f>
-        <v>105598.4375</v>
+        <v>118898.4375</v>
       </c>
       <c r="X25" s="5" t="n">
         <f aca="false">X11-X23</f>
-        <v>94973.4375</v>
+        <v>107573.4375</v>
       </c>
       <c r="Y25" s="5" t="n">
         <f aca="false">Y11-Y23</f>
-        <v>116223.4375</v>
+        <v>130223.4375</v>
       </c>
       <c r="Z25" s="5" t="n">
         <f aca="false">Z11-Z23</f>
-        <v>126848.4375</v>
+        <v>141548.4375</v>
       </c>
       <c r="AA25" s="5" t="n">
         <f aca="false">AA11-AA23</f>
-        <v>179973.4375</v>
+        <v>198173.4375</v>
       </c>
       <c r="AB25" s="5" t="n">
         <f aca="false">AB11-AB23</f>
-        <v>190598.4375</v>
+        <v>209498.4375</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5277,107 +5277,107 @@
       </c>
       <c r="C26" s="13" t="n">
         <f aca="false">IF(C6=0,0,C25/C6)</f>
-        <v>0.206127450980392</v>
+        <v>0.234127450980392</v>
       </c>
       <c r="D26" s="13" t="n">
         <f aca="false">IF(D6=0,0,D25/D6)</f>
-        <v>0.167502883506344</v>
+        <v>0.195502883506344</v>
       </c>
       <c r="E26" s="13" t="n">
         <f aca="false">IF(E6=0,0,E25/E6)</f>
-        <v>0.167502883506344</v>
+        <v>0.195502883506344</v>
       </c>
       <c r="F26" s="13" t="n">
         <f aca="false">IF(F6=0,0,F25/F6)</f>
-        <v>0.181808278867102</v>
+        <v>0.209808278867102</v>
       </c>
       <c r="G26" s="13" t="n">
         <f aca="false">IF(G6=0,0,G25/G6)</f>
-        <v>0.181808278867102</v>
+        <v>0.209808278867102</v>
       </c>
       <c r="H26" s="13" t="n">
         <f aca="false">IF(H6=0,0,H25/H6)</f>
-        <v>0.194607843137255</v>
+        <v>0.222607843137255</v>
       </c>
       <c r="I26" s="13" t="n">
         <f aca="false">IF(I6=0,0,I25/I6)</f>
-        <v>0.206127450980392</v>
+        <v>0.234127450980392</v>
       </c>
       <c r="J26" s="13" t="n">
         <f aca="false">IF(J6=0,0,J25/J6)</f>
-        <v>0.194607843137255</v>
+        <v>0.222607843137255</v>
       </c>
       <c r="K26" s="13" t="n">
         <f aca="false">IF(K6=0,0,K25/K6)</f>
-        <v>0.181808278867102</v>
+        <v>0.209808278867102</v>
       </c>
       <c r="L26" s="13" t="n">
         <f aca="false">IF(L6=0,0,L25/L6)</f>
-        <v>0.206127450980392</v>
+        <v>0.234127450980392</v>
       </c>
       <c r="M26" s="13" t="n">
         <f aca="false">IF(M6=0,0,M25/M6)</f>
-        <v>0.216549953314659</v>
+        <v>0.244549953314659</v>
       </c>
       <c r="N26" s="13" t="n">
         <f aca="false">IF(N6=0,0,N25/N6)</f>
-        <v>0.256636500754148</v>
+        <v>0.284636500754148</v>
       </c>
       <c r="O26" s="13" t="n">
         <f aca="false">IF(O6=0,0,O25/O6)</f>
-        <v>0.262872185911402</v>
+        <v>0.290872185911402</v>
       </c>
       <c r="P26" s="13" t="n">
         <f aca="false">IF(P6=0,0,P25/P6)</f>
-        <v>0.232446875</v>
+        <v>0.260446875</v>
       </c>
       <c r="Q26" s="13" t="n">
         <f aca="false">IF(Q6=0,0,Q25/Q6)</f>
-        <v>0.198466911764706</v>
+        <v>0.226466911764706</v>
       </c>
       <c r="R26" s="13" t="n">
         <f aca="false">IF(R6=0,0,R25/R6)</f>
-        <v>0.198466911764706</v>
+        <v>0.226466911764706</v>
       </c>
       <c r="S26" s="13" t="n">
         <f aca="false">IF(S6=0,0,S25/S6)</f>
-        <v>0.211052083333333</v>
+        <v>0.239052083333333</v>
       </c>
       <c r="T26" s="13" t="n">
         <f aca="false">IF(T6=0,0,T25/T6)</f>
-        <v>0.211052083333333</v>
+        <v>0.239052083333333</v>
       </c>
       <c r="U26" s="13" t="n">
         <f aca="false">IF(U6=0,0,U25/U6)</f>
-        <v>0.2223125</v>
+        <v>0.2503125</v>
       </c>
       <c r="V26" s="13" t="n">
         <f aca="false">IF(V6=0,0,V25/V6)</f>
-        <v>0.232446875</v>
+        <v>0.260446875</v>
       </c>
       <c r="W26" s="13" t="n">
         <f aca="false">IF(W6=0,0,W25/W6)</f>
-        <v>0.2223125</v>
+        <v>0.2503125</v>
       </c>
       <c r="X26" s="13" t="n">
         <f aca="false">IF(X6=0,0,X25/X6)</f>
-        <v>0.211052083333333</v>
+        <v>0.239052083333333</v>
       </c>
       <c r="Y26" s="13" t="n">
         <f aca="false">IF(Y6=0,0,Y25/Y6)</f>
-        <v>0.232446875</v>
+        <v>0.260446875</v>
       </c>
       <c r="Z26" s="13" t="n">
         <f aca="false">IF(Z6=0,0,Z25/Z6)</f>
-        <v>0.241616071428572</v>
+        <v>0.269616071428571</v>
       </c>
       <c r="AA26" s="13" t="n">
         <f aca="false">IF(AA6=0,0,AA25/AA6)</f>
-        <v>0.276882211538462</v>
+        <v>0.304882211538462</v>
       </c>
       <c r="AB26" s="13" t="n">
         <f aca="false">IF(AB6=0,0,AB25/AB6)</f>
-        <v>0.282368055555556</v>
+        <v>0.310368055555556</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5495,107 +5495,107 @@
       </c>
       <c r="C30" s="5" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>1031250</v>
+        <v>1174050</v>
       </c>
       <c r="D30" s="5" t="n">
         <f aca="false">D25-D28</f>
-        <v>58843.75</v>
+        <v>68958.75</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">E25-E28</f>
-        <v>58843.75</v>
+        <v>68958.75</v>
       </c>
       <c r="F30" s="5" t="n">
         <f aca="false">F25-F28</f>
-        <v>67875</v>
+        <v>78585</v>
       </c>
       <c r="G30" s="5" t="n">
         <f aca="false">G25-G28</f>
-        <v>67875</v>
+        <v>78585</v>
       </c>
       <c r="H30" s="5" t="n">
         <f aca="false">H25-H28</f>
-        <v>76906.25</v>
+        <v>88211.25</v>
       </c>
       <c r="I30" s="5" t="n">
         <f aca="false">I25-I28</f>
-        <v>85937.5</v>
+        <v>97837.5</v>
       </c>
       <c r="J30" s="5" t="n">
         <f aca="false">J25-J28</f>
-        <v>76906.25</v>
+        <v>88211.25</v>
       </c>
       <c r="K30" s="5" t="n">
         <f aca="false">K25-K28</f>
-        <v>67875</v>
+        <v>78585</v>
       </c>
       <c r="L30" s="5" t="n">
         <f aca="false">L25-L28</f>
-        <v>85937.5</v>
+        <v>97837.5</v>
       </c>
       <c r="M30" s="5" t="n">
         <f aca="false">M25-M28</f>
-        <v>94968.75</v>
+        <v>107463.75</v>
       </c>
       <c r="N30" s="5" t="n">
         <f aca="false">N25-N28</f>
-        <v>140125</v>
+        <v>155595</v>
       </c>
       <c r="O30" s="5" t="n">
         <f aca="false">O25-O28</f>
-        <v>149156.25</v>
+        <v>165221.25</v>
       </c>
       <c r="P30" s="5" t="n">
         <f aca="false">SUM(Q30:AB30)</f>
-        <v>1374681.25</v>
+        <v>1542681.25</v>
       </c>
       <c r="Q30" s="5" t="n">
         <f aca="false">Q25-Q28</f>
-        <v>82681.7708333334</v>
+        <v>94581.7708333333</v>
       </c>
       <c r="R30" s="5" t="n">
         <f aca="false">R25-R28</f>
-        <v>82681.7708333334</v>
+        <v>94581.7708333333</v>
       </c>
       <c r="S30" s="5" t="n">
         <f aca="false">S25-S28</f>
-        <v>93306.7708333334</v>
+        <v>105906.770833333</v>
       </c>
       <c r="T30" s="5" t="n">
         <f aca="false">T25-T28</f>
-        <v>93306.7708333334</v>
+        <v>105906.770833333</v>
       </c>
       <c r="U30" s="5" t="n">
         <f aca="false">U25-U28</f>
-        <v>103931.770833333</v>
+        <v>117231.770833333</v>
       </c>
       <c r="V30" s="5" t="n">
         <f aca="false">V25-V28</f>
-        <v>114556.770833333</v>
+        <v>128556.770833333</v>
       </c>
       <c r="W30" s="5" t="n">
         <f aca="false">W25-W28</f>
-        <v>103931.770833333</v>
+        <v>117231.770833333</v>
       </c>
       <c r="X30" s="5" t="n">
         <f aca="false">X25-X28</f>
-        <v>93306.7708333334</v>
+        <v>105906.770833333</v>
       </c>
       <c r="Y30" s="5" t="n">
         <f aca="false">Y25-Y28</f>
-        <v>114556.770833333</v>
+        <v>128556.770833333</v>
       </c>
       <c r="Z30" s="5" t="n">
         <f aca="false">Z25-Z28</f>
-        <v>125181.770833333</v>
+        <v>139881.770833333</v>
       </c>
       <c r="AA30" s="5" t="n">
         <f aca="false">AA25-AA28</f>
-        <v>178306.770833333</v>
+        <v>196506.770833333</v>
       </c>
       <c r="AB30" s="5" t="n">
         <f aca="false">AB25-AB28</f>
-        <v>188931.770833333</v>
+        <v>207831.770833333</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5604,107 +5604,107 @@
       </c>
       <c r="C31" s="13" t="n">
         <f aca="false">IF(C6=0,0,C30/C6)</f>
-        <v>0.202205882352941</v>
+        <v>0.230205882352941</v>
       </c>
       <c r="D31" s="13" t="n">
         <f aca="false">IF(D6=0,0,D30/D6)</f>
-        <v>0.162889273356401</v>
+        <v>0.190889273356401</v>
       </c>
       <c r="E31" s="13" t="n">
         <f aca="false">IF(E6=0,0,E30/E6)</f>
-        <v>0.162889273356401</v>
+        <v>0.190889273356401</v>
       </c>
       <c r="F31" s="13" t="n">
         <f aca="false">IF(F6=0,0,F30/F6)</f>
-        <v>0.177450980392157</v>
+        <v>0.205450980392157</v>
       </c>
       <c r="G31" s="13" t="n">
         <f aca="false">IF(G6=0,0,G30/G6)</f>
-        <v>0.177450980392157</v>
+        <v>0.205450980392157</v>
       </c>
       <c r="H31" s="13" t="n">
         <f aca="false">IF(H6=0,0,H30/H6)</f>
-        <v>0.190479876160991</v>
+        <v>0.218479876160991</v>
       </c>
       <c r="I31" s="13" t="n">
         <f aca="false">IF(I6=0,0,I30/I6)</f>
-        <v>0.202205882352941</v>
+        <v>0.230205882352941</v>
       </c>
       <c r="J31" s="13" t="n">
         <f aca="false">IF(J6=0,0,J30/J6)</f>
-        <v>0.190479876160991</v>
+        <v>0.218479876160991</v>
       </c>
       <c r="K31" s="13" t="n">
         <f aca="false">IF(K6=0,0,K30/K6)</f>
-        <v>0.177450980392157</v>
+        <v>0.205450980392157</v>
       </c>
       <c r="L31" s="13" t="n">
         <f aca="false">IF(L6=0,0,L30/L6)</f>
-        <v>0.202205882352941</v>
+        <v>0.230205882352941</v>
       </c>
       <c r="M31" s="13" t="n">
         <f aca="false">IF(M6=0,0,M30/M6)</f>
-        <v>0.21281512605042</v>
+        <v>0.24081512605042</v>
       </c>
       <c r="N31" s="13" t="n">
         <f aca="false">IF(N6=0,0,N30/N6)</f>
-        <v>0.253619909502263</v>
+        <v>0.281619909502262</v>
       </c>
       <c r="O31" s="13" t="n">
         <f aca="false">IF(O6=0,0,O30/O6)</f>
-        <v>0.259967320261438</v>
+        <v>0.287967320261438</v>
       </c>
       <c r="P31" s="13" t="n">
         <f aca="false">IF(P6=0,0,P30/P6)</f>
-        <v>0.229113541666667</v>
+        <v>0.257113541666667</v>
       </c>
       <c r="Q31" s="13" t="n">
         <f aca="false">IF(Q6=0,0,Q30/Q6)</f>
-        <v>0.194545343137255</v>
+        <v>0.222545343137255</v>
       </c>
       <c r="R31" s="13" t="n">
         <f aca="false">IF(R6=0,0,R30/R6)</f>
-        <v>0.194545343137255</v>
+        <v>0.222545343137255</v>
       </c>
       <c r="S31" s="13" t="n">
         <f aca="false">IF(S6=0,0,S30/S6)</f>
-        <v>0.20734837962963</v>
+        <v>0.23534837962963</v>
       </c>
       <c r="T31" s="13" t="n">
         <f aca="false">IF(T6=0,0,T30/T6)</f>
-        <v>0.20734837962963</v>
+        <v>0.23534837962963</v>
       </c>
       <c r="U31" s="13" t="n">
         <f aca="false">IF(U6=0,0,U30/U6)</f>
-        <v>0.218803728070176</v>
+        <v>0.246803728070175</v>
       </c>
       <c r="V31" s="13" t="n">
         <f aca="false">IF(V6=0,0,V30/V6)</f>
-        <v>0.229113541666667</v>
+        <v>0.257113541666667</v>
       </c>
       <c r="W31" s="13" t="n">
         <f aca="false">IF(W6=0,0,W30/W6)</f>
-        <v>0.218803728070176</v>
+        <v>0.246803728070175</v>
       </c>
       <c r="X31" s="13" t="n">
         <f aca="false">IF(X6=0,0,X30/X6)</f>
-        <v>0.20734837962963</v>
+        <v>0.23534837962963</v>
       </c>
       <c r="Y31" s="13" t="n">
         <f aca="false">IF(Y6=0,0,Y30/Y6)</f>
-        <v>0.229113541666667</v>
+        <v>0.257113541666667</v>
       </c>
       <c r="Z31" s="13" t="n">
         <f aca="false">IF(Z6=0,0,Z30/Z6)</f>
-        <v>0.238441468253968</v>
+        <v>0.266441468253968</v>
       </c>
       <c r="AA31" s="13" t="n">
         <f aca="false">IF(AA6=0,0,AA30/AA6)</f>
-        <v>0.274318108974359</v>
+        <v>0.302318108974359</v>
       </c>
       <c r="AB31" s="13" t="n">
         <f aca="false">IF(AB6=0,0,AB30/AB6)</f>
-        <v>0.279898919753087</v>
+        <v>0.307898919753087</v>
       </c>
     </row>
   </sheetData>
@@ -5942,107 +5942,107 @@
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">'USA PL'!C9+'Nigeria PL'!C9</f>
-        <v>7187250</v>
+        <v>6824650</v>
       </c>
       <c r="D9" s="7" t="n">
         <f aca="false">'USA PL'!D9+'Nigeria PL'!D9</f>
-        <v>509096.875</v>
+        <v>483412.708333333</v>
       </c>
       <c r="E9" s="7" t="n">
         <f aca="false">'USA PL'!E9+'Nigeria PL'!E9</f>
-        <v>509096.875</v>
+        <v>483412.708333333</v>
       </c>
       <c r="F9" s="7" t="n">
         <f aca="false">'USA PL'!F9+'Nigeria PL'!F9</f>
-        <v>539043.75</v>
+        <v>511848.75</v>
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">'USA PL'!G9+'Nigeria PL'!G9</f>
-        <v>539043.75</v>
+        <v>511848.75</v>
       </c>
       <c r="H9" s="7" t="n">
         <f aca="false">'USA PL'!H9+'Nigeria PL'!H9</f>
-        <v>568990.625</v>
+        <v>540284.791666667</v>
       </c>
       <c r="I9" s="7" t="n">
         <f aca="false">'USA PL'!I9+'Nigeria PL'!I9</f>
-        <v>598937.5</v>
+        <v>568720.833333333</v>
       </c>
       <c r="J9" s="7" t="n">
         <f aca="false">'USA PL'!J9+'Nigeria PL'!J9</f>
-        <v>568990.625</v>
+        <v>540284.791666667</v>
       </c>
       <c r="K9" s="7" t="n">
         <f aca="false">'USA PL'!K9+'Nigeria PL'!K9</f>
-        <v>539043.75</v>
+        <v>511848.75</v>
       </c>
       <c r="L9" s="7" t="n">
         <f aca="false">'USA PL'!L9+'Nigeria PL'!L9</f>
-        <v>598937.5</v>
+        <v>568720.833333333</v>
       </c>
       <c r="M9" s="7" t="n">
         <f aca="false">'USA PL'!M9+'Nigeria PL'!M9</f>
-        <v>628884.375</v>
+        <v>597156.875</v>
       </c>
       <c r="N9" s="7" t="n">
         <f aca="false">'USA PL'!N9+'Nigeria PL'!N9</f>
-        <v>778618.75</v>
+        <v>739337.083333333</v>
       </c>
       <c r="O9" s="7" t="n">
         <f aca="false">'USA PL'!O9+'Nigeria PL'!O9</f>
-        <v>808565.625</v>
+        <v>767773.125</v>
       </c>
       <c r="P9" s="7" t="n">
         <f aca="false">'USA PL'!P9+'Nigeria PL'!P9</f>
-        <v>8325000</v>
+        <v>7905000</v>
       </c>
       <c r="Q9" s="7" t="n">
         <f aca="false">'USA PL'!Q9+'Nigeria PL'!Q9</f>
-        <v>589687.5</v>
+        <v>559937.5</v>
       </c>
       <c r="R9" s="7" t="n">
         <f aca="false">'USA PL'!R9+'Nigeria PL'!R9</f>
-        <v>589687.5</v>
+        <v>559937.5</v>
       </c>
       <c r="S9" s="7" t="n">
         <f aca="false">'USA PL'!S9+'Nigeria PL'!S9</f>
-        <v>624375</v>
+        <v>592875</v>
       </c>
       <c r="T9" s="7" t="n">
         <f aca="false">'USA PL'!T9+'Nigeria PL'!T9</f>
-        <v>624375</v>
+        <v>592875</v>
       </c>
       <c r="U9" s="7" t="n">
         <f aca="false">'USA PL'!U9+'Nigeria PL'!U9</f>
-        <v>659062.5</v>
+        <v>625812.5</v>
       </c>
       <c r="V9" s="7" t="n">
         <f aca="false">'USA PL'!V9+'Nigeria PL'!V9</f>
-        <v>693750</v>
+        <v>658750</v>
       </c>
       <c r="W9" s="7" t="n">
         <f aca="false">'USA PL'!W9+'Nigeria PL'!W9</f>
-        <v>659062.5</v>
+        <v>625812.5</v>
       </c>
       <c r="X9" s="7" t="n">
         <f aca="false">'USA PL'!X9+'Nigeria PL'!X9</f>
-        <v>624375</v>
+        <v>592875</v>
       </c>
       <c r="Y9" s="7" t="n">
         <f aca="false">'USA PL'!Y9+'Nigeria PL'!Y9</f>
-        <v>693750</v>
+        <v>658750</v>
       </c>
       <c r="Z9" s="7" t="n">
         <f aca="false">'USA PL'!Z9+'Nigeria PL'!Z9</f>
-        <v>728437.5</v>
+        <v>691687.5</v>
       </c>
       <c r="AA9" s="7" t="n">
         <f aca="false">'USA PL'!AA9+'Nigeria PL'!AA9</f>
-        <v>901875</v>
+        <v>856375</v>
       </c>
       <c r="AB9" s="7" t="n">
         <f aca="false">'USA PL'!AB9+'Nigeria PL'!AB9</f>
-        <v>936562.5</v>
+        <v>889312.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6051,107 +6051,107 @@
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">'USA PL'!C11+'Nigeria PL'!C11</f>
-        <v>5762750</v>
+        <v>6125350</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">'USA PL'!D11+'Nigeria PL'!D11</f>
-        <v>408194.791666667</v>
+        <v>433878.958333333</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">'USA PL'!E11+'Nigeria PL'!E11</f>
-        <v>408194.791666667</v>
+        <v>433878.958333333</v>
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">'USA PL'!F11+'Nigeria PL'!F11</f>
-        <v>432206.25</v>
+        <v>459401.25</v>
       </c>
       <c r="G11" s="5" t="n">
         <f aca="false">'USA PL'!G11+'Nigeria PL'!G11</f>
-        <v>432206.25</v>
+        <v>459401.25</v>
       </c>
       <c r="H11" s="5" t="n">
         <f aca="false">'USA PL'!H11+'Nigeria PL'!H11</f>
-        <v>456217.708333333</v>
+        <v>484923.541666667</v>
       </c>
       <c r="I11" s="5" t="n">
         <f aca="false">'USA PL'!I11+'Nigeria PL'!I11</f>
-        <v>480229.166666667</v>
+        <v>510445.833333333</v>
       </c>
       <c r="J11" s="5" t="n">
         <f aca="false">'USA PL'!J11+'Nigeria PL'!J11</f>
-        <v>456217.708333333</v>
+        <v>484923.541666667</v>
       </c>
       <c r="K11" s="5" t="n">
         <f aca="false">'USA PL'!K11+'Nigeria PL'!K11</f>
-        <v>432206.25</v>
+        <v>459401.25</v>
       </c>
       <c r="L11" s="5" t="n">
         <f aca="false">'USA PL'!L11+'Nigeria PL'!L11</f>
-        <v>480229.166666667</v>
+        <v>510445.833333333</v>
       </c>
       <c r="M11" s="5" t="n">
         <f aca="false">'USA PL'!M11+'Nigeria PL'!M11</f>
-        <v>504240.625</v>
+        <v>535968.125</v>
       </c>
       <c r="N11" s="5" t="n">
         <f aca="false">'USA PL'!N11+'Nigeria PL'!N11</f>
-        <v>624297.916666667</v>
+        <v>663579.583333333</v>
       </c>
       <c r="O11" s="5" t="n">
         <f aca="false">'USA PL'!O11+'Nigeria PL'!O11</f>
-        <v>648309.375</v>
+        <v>689101.875</v>
       </c>
       <c r="P11" s="5" t="n">
         <f aca="false">'USA PL'!P11+'Nigeria PL'!P11</f>
-        <v>6675000</v>
+        <v>7095000</v>
       </c>
       <c r="Q11" s="5" t="n">
         <f aca="false">'USA PL'!Q11+'Nigeria PL'!Q11</f>
-        <v>472812.5</v>
+        <v>502562.5</v>
       </c>
       <c r="R11" s="5" t="n">
         <f aca="false">'USA PL'!R11+'Nigeria PL'!R11</f>
-        <v>472812.5</v>
+        <v>502562.5</v>
       </c>
       <c r="S11" s="5" t="n">
         <f aca="false">'USA PL'!S11+'Nigeria PL'!S11</f>
-        <v>500625</v>
+        <v>532125</v>
       </c>
       <c r="T11" s="5" t="n">
         <f aca="false">'USA PL'!T11+'Nigeria PL'!T11</f>
-        <v>500625</v>
+        <v>532125</v>
       </c>
       <c r="U11" s="5" t="n">
         <f aca="false">'USA PL'!U11+'Nigeria PL'!U11</f>
-        <v>528437.5</v>
+        <v>561687.5</v>
       </c>
       <c r="V11" s="5" t="n">
         <f aca="false">'USA PL'!V11+'Nigeria PL'!V11</f>
-        <v>556250</v>
+        <v>591250</v>
       </c>
       <c r="W11" s="5" t="n">
         <f aca="false">'USA PL'!W11+'Nigeria PL'!W11</f>
-        <v>528437.5</v>
+        <v>561687.5</v>
       </c>
       <c r="X11" s="5" t="n">
         <f aca="false">'USA PL'!X11+'Nigeria PL'!X11</f>
-        <v>500625</v>
+        <v>532125</v>
       </c>
       <c r="Y11" s="5" t="n">
         <f aca="false">'USA PL'!Y11+'Nigeria PL'!Y11</f>
-        <v>556250</v>
+        <v>591250</v>
       </c>
       <c r="Z11" s="5" t="n">
         <f aca="false">'USA PL'!Z11+'Nigeria PL'!Z11</f>
-        <v>584062.5</v>
+        <v>620812.5</v>
       </c>
       <c r="AA11" s="5" t="n">
         <f aca="false">'USA PL'!AA11+'Nigeria PL'!AA11</f>
-        <v>723125</v>
+        <v>768625</v>
       </c>
       <c r="AB11" s="5" t="n">
         <f aca="false">'USA PL'!AB11+'Nigeria PL'!AB11</f>
-        <v>750937.5</v>
+        <v>798187.5</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6160,107 +6160,107 @@
       </c>
       <c r="C12" s="13" t="n">
         <f aca="false">IF(C6=0,0,C11/C6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="D12" s="13" t="n">
         <f aca="false">IF(D6=0,0,D11/D6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">IF(E6=0,0,E11/E6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="F12" s="13" t="n">
         <f aca="false">IF(F6=0,0,F11/F6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="G12" s="13" t="n">
         <f aca="false">IF(G6=0,0,G11/G6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="H12" s="13" t="n">
         <f aca="false">IF(H6=0,0,H11/H6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="I12" s="13" t="n">
         <f aca="false">IF(I6=0,0,I11/I6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="J12" s="13" t="n">
         <f aca="false">IF(J6=0,0,J11/J6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="K12" s="13" t="n">
         <f aca="false">IF(K6=0,0,K11/K6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="L12" s="13" t="n">
         <f aca="false">IF(L6=0,0,L11/L6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="M12" s="13" t="n">
         <f aca="false">IF(M6=0,0,M11/M6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="N12" s="13" t="n">
         <f aca="false">IF(N6=0,0,N11/N6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="O12" s="13" t="n">
         <f aca="false">IF(O6=0,0,O11/O6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="P12" s="13" t="n">
         <f aca="false">IF(P6=0,0,P11/P6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="Q12" s="13" t="n">
         <f aca="false">IF(Q6=0,0,Q11/Q6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="R12" s="13" t="n">
         <f aca="false">IF(R6=0,0,R11/R6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="S12" s="13" t="n">
         <f aca="false">IF(S6=0,0,S11/S6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="T12" s="13" t="n">
         <f aca="false">IF(T6=0,0,T11/T6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="U12" s="13" t="n">
         <f aca="false">IF(U6=0,0,U11/U6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="V12" s="13" t="n">
         <f aca="false">IF(V6=0,0,V11/V6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="W12" s="13" t="n">
         <f aca="false">IF(W6=0,0,W11/W6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="X12" s="13" t="n">
         <f aca="false">IF(X6=0,0,X11/X6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="Y12" s="13" t="n">
         <f aca="false">IF(Y6=0,0,Y11/Y6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="Z12" s="13" t="n">
         <f aca="false">IF(Z6=0,0,Z11/Z6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="AA12" s="13" t="n">
         <f aca="false">IF(AA6=0,0,AA11/AA6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
       <c r="AB12" s="13" t="n">
         <f aca="false">IF(AB6=0,0,AB11/AB6)</f>
-        <v>0.445</v>
+        <v>0.473</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7255,107 +7255,107 @@
       </c>
       <c r="C25" s="5" t="n">
         <f aca="false">'USA PL'!C25+'Nigeria PL'!C25</f>
-        <v>1351250</v>
+        <v>1713850</v>
       </c>
       <c r="D25" s="5" t="n">
         <f aca="false">'USA PL'!D25+'Nigeria PL'!D25</f>
-        <v>43807.2916666667</v>
+        <v>69491.4583333333</v>
       </c>
       <c r="E25" s="5" t="n">
         <f aca="false">'USA PL'!E25+'Nigeria PL'!E25</f>
-        <v>43807.2916666667</v>
+        <v>69491.4583333333</v>
       </c>
       <c r="F25" s="5" t="n">
         <f aca="false">'USA PL'!F25+'Nigeria PL'!F25</f>
-        <v>66739.5833333334</v>
+        <v>93934.5833333333</v>
       </c>
       <c r="G25" s="5" t="n">
         <f aca="false">'USA PL'!G25+'Nigeria PL'!G25</f>
-        <v>66739.5833333334</v>
+        <v>93934.5833333333</v>
       </c>
       <c r="H25" s="5" t="n">
         <f aca="false">'USA PL'!H25+'Nigeria PL'!H25</f>
-        <v>89671.8750000001</v>
+        <v>118377.708333333</v>
       </c>
       <c r="I25" s="5" t="n">
         <f aca="false">'USA PL'!I25+'Nigeria PL'!I25</f>
-        <v>112604.166666667</v>
+        <v>142820.833333333</v>
       </c>
       <c r="J25" s="5" t="n">
         <f aca="false">'USA PL'!J25+'Nigeria PL'!J25</f>
-        <v>89671.8750000001</v>
+        <v>118377.708333333</v>
       </c>
       <c r="K25" s="5" t="n">
         <f aca="false">'USA PL'!K25+'Nigeria PL'!K25</f>
-        <v>66739.5833333334</v>
+        <v>93934.5833333333</v>
       </c>
       <c r="L25" s="5" t="n">
         <f aca="false">'USA PL'!L25+'Nigeria PL'!L25</f>
-        <v>112604.166666667</v>
+        <v>142820.833333333</v>
       </c>
       <c r="M25" s="5" t="n">
         <f aca="false">'USA PL'!M25+'Nigeria PL'!M25</f>
-        <v>135536.458333333</v>
+        <v>167263.958333333</v>
       </c>
       <c r="N25" s="5" t="n">
         <f aca="false">'USA PL'!N25+'Nigeria PL'!N25</f>
-        <v>250197.916666667</v>
+        <v>289479.583333333</v>
       </c>
       <c r="O25" s="5" t="n">
         <f aca="false">'USA PL'!O25+'Nigeria PL'!O25</f>
-        <v>273130.208333333</v>
+        <v>313922.708333333</v>
       </c>
       <c r="P25" s="5" t="n">
         <f aca="false">'USA PL'!P25+'Nigeria PL'!P25</f>
-        <v>2077162.5</v>
+        <v>2497162.5</v>
       </c>
       <c r="Q25" s="5" t="n">
         <f aca="false">'USA PL'!Q25+'Nigeria PL'!Q25</f>
-        <v>93409.3750000002</v>
+        <v>123159.375</v>
       </c>
       <c r="R25" s="5" t="n">
         <f aca="false">'USA PL'!R25+'Nigeria PL'!R25</f>
-        <v>93409.3750000002</v>
+        <v>123159.375</v>
       </c>
       <c r="S25" s="5" t="n">
         <f aca="false">'USA PL'!S25+'Nigeria PL'!S25</f>
-        <v>119971.875</v>
+        <v>151471.875</v>
       </c>
       <c r="T25" s="5" t="n">
         <f aca="false">'USA PL'!T25+'Nigeria PL'!T25</f>
-        <v>119971.875</v>
+        <v>151471.875</v>
       </c>
       <c r="U25" s="5" t="n">
         <f aca="false">'USA PL'!U25+'Nigeria PL'!U25</f>
-        <v>146534.375</v>
+        <v>179784.375</v>
       </c>
       <c r="V25" s="5" t="n">
         <f aca="false">'USA PL'!V25+'Nigeria PL'!V25</f>
-        <v>173096.875</v>
+        <v>208096.875</v>
       </c>
       <c r="W25" s="5" t="n">
         <f aca="false">'USA PL'!W25+'Nigeria PL'!W25</f>
-        <v>146534.375</v>
+        <v>179784.375</v>
       </c>
       <c r="X25" s="5" t="n">
         <f aca="false">'USA PL'!X25+'Nigeria PL'!X25</f>
-        <v>119971.875</v>
+        <v>151471.875</v>
       </c>
       <c r="Y25" s="5" t="n">
         <f aca="false">'USA PL'!Y25+'Nigeria PL'!Y25</f>
-        <v>173096.875</v>
+        <v>208096.875</v>
       </c>
       <c r="Z25" s="5" t="n">
         <f aca="false">'USA PL'!Z25+'Nigeria PL'!Z25</f>
-        <v>199659.375</v>
+        <v>236409.375</v>
       </c>
       <c r="AA25" s="5" t="n">
         <f aca="false">'USA PL'!AA25+'Nigeria PL'!AA25</f>
-        <v>332471.875</v>
+        <v>377971.875</v>
       </c>
       <c r="AB25" s="5" t="n">
         <f aca="false">'USA PL'!AB25+'Nigeria PL'!AB25</f>
-        <v>359034.375</v>
+        <v>406284.375</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7364,107 +7364,107 @@
       </c>
       <c r="C26" s="13" t="n">
         <f aca="false">IF(C6=0,0,C25/C6)</f>
-        <v>0.104343629343629</v>
+        <v>0.132343629343629</v>
       </c>
       <c r="D26" s="13" t="n">
         <f aca="false">IF(D6=0,0,D25/D6)</f>
-        <v>0.0477572109925051</v>
+        <v>0.0757572109925051</v>
       </c>
       <c r="E26" s="13" t="n">
         <f aca="false">IF(E6=0,0,E25/E6)</f>
-        <v>0.0477572109925051</v>
+        <v>0.0757572109925051</v>
       </c>
       <c r="F26" s="13" t="n">
         <f aca="false">IF(F6=0,0,F25/F6)</f>
-        <v>0.0687151437151438</v>
+        <v>0.0967151437151437</v>
       </c>
       <c r="G26" s="13" t="n">
         <f aca="false">IF(G6=0,0,G25/G6)</f>
-        <v>0.0687151437151438</v>
+        <v>0.0967151437151437</v>
       </c>
       <c r="H26" s="13" t="n">
         <f aca="false">IF(H6=0,0,H25/H6)</f>
-        <v>0.087466978256452</v>
+        <v>0.115466978256452</v>
       </c>
       <c r="I26" s="13" t="n">
         <f aca="false">IF(I6=0,0,I25/I6)</f>
-        <v>0.104343629343629</v>
+        <v>0.132343629343629</v>
       </c>
       <c r="J26" s="13" t="n">
         <f aca="false">IF(J6=0,0,J25/J6)</f>
-        <v>0.087466978256452</v>
+        <v>0.115466978256452</v>
       </c>
       <c r="K26" s="13" t="n">
         <f aca="false">IF(K6=0,0,K25/K6)</f>
-        <v>0.0687151437151438</v>
+        <v>0.0967151437151437</v>
       </c>
       <c r="L26" s="13" t="n">
         <f aca="false">IF(L6=0,0,L25/L6)</f>
-        <v>0.104343629343629</v>
+        <v>0.132343629343629</v>
       </c>
       <c r="M26" s="13" t="n">
         <f aca="false">IF(M6=0,0,M25/M6)</f>
-        <v>0.119612980327266</v>
+        <v>0.147612980327266</v>
       </c>
       <c r="N26" s="13" t="n">
         <f aca="false">IF(N6=0,0,N25/N6)</f>
-        <v>0.178341253341253</v>
+        <v>0.206341253341253</v>
       </c>
       <c r="O26" s="13" t="n">
         <f aca="false">IF(O6=0,0,O25/O6)</f>
-        <v>0.187476762476763</v>
+        <v>0.215476762476762</v>
       </c>
       <c r="P26" s="13" t="n">
         <f aca="false">IF(P6=0,0,P25/P6)</f>
-        <v>0.1384775</v>
+        <v>0.1664775</v>
       </c>
       <c r="Q26" s="13" t="n">
         <f aca="false">IF(Q6=0,0,Q25/Q6)</f>
-        <v>0.0879147058823531</v>
+        <v>0.115914705882353</v>
       </c>
       <c r="R26" s="13" t="n">
         <f aca="false">IF(R6=0,0,R25/R6)</f>
-        <v>0.0879147058823531</v>
+        <v>0.115914705882353</v>
       </c>
       <c r="S26" s="13" t="n">
         <f aca="false">IF(S6=0,0,S25/S6)</f>
-        <v>0.106641666666667</v>
+        <v>0.134641666666667</v>
       </c>
       <c r="T26" s="13" t="n">
         <f aca="false">IF(T6=0,0,T25/T6)</f>
-        <v>0.106641666666667</v>
+        <v>0.134641666666667</v>
       </c>
       <c r="U26" s="13" t="n">
         <f aca="false">IF(U6=0,0,U25/U6)</f>
-        <v>0.123397368421053</v>
+        <v>0.151397368421053</v>
       </c>
       <c r="V26" s="13" t="n">
         <f aca="false">IF(V6=0,0,V25/V6)</f>
-        <v>0.1384775</v>
+        <v>0.1664775</v>
       </c>
       <c r="W26" s="13" t="n">
         <f aca="false">IF(W6=0,0,W25/W6)</f>
-        <v>0.123397368421053</v>
+        <v>0.151397368421053</v>
       </c>
       <c r="X26" s="13" t="n">
         <f aca="false">IF(X6=0,0,X25/X6)</f>
-        <v>0.106641666666667</v>
+        <v>0.134641666666667</v>
       </c>
       <c r="Y26" s="13" t="n">
         <f aca="false">IF(Y6=0,0,Y25/Y6)</f>
-        <v>0.1384775</v>
+        <v>0.1664775</v>
       </c>
       <c r="Z26" s="13" t="n">
         <f aca="false">IF(Z6=0,0,Z25/Z6)</f>
-        <v>0.152121428571429</v>
+        <v>0.180121428571429</v>
       </c>
       <c r="AA26" s="13" t="n">
         <f aca="false">IF(AA6=0,0,AA25/AA6)</f>
-        <v>0.204598076923077</v>
+        <v>0.232598076923077</v>
       </c>
       <c r="AB26" s="13" t="n">
         <f aca="false">IF(AB6=0,0,AB25/AB6)</f>
-        <v>0.212761111111111</v>
+        <v>0.240761111111111</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7582,107 +7582,107 @@
       </c>
       <c r="C30" s="5" t="n">
         <f aca="false">'USA PL'!C30+'Nigeria PL'!C30</f>
-        <v>1291250</v>
+        <v>1653850</v>
       </c>
       <c r="D30" s="5" t="n">
         <f aca="false">'USA PL'!D30+'Nigeria PL'!D30</f>
-        <v>38807.2916666667</v>
+        <v>64491.4583333333</v>
       </c>
       <c r="E30" s="5" t="n">
         <f aca="false">'USA PL'!E30+'Nigeria PL'!E30</f>
-        <v>38807.2916666667</v>
+        <v>64491.4583333333</v>
       </c>
       <c r="F30" s="5" t="n">
         <f aca="false">'USA PL'!F30+'Nigeria PL'!F30</f>
-        <v>61739.5833333334</v>
+        <v>88934.5833333333</v>
       </c>
       <c r="G30" s="5" t="n">
         <f aca="false">'USA PL'!G30+'Nigeria PL'!G30</f>
-        <v>61739.5833333334</v>
+        <v>88934.5833333333</v>
       </c>
       <c r="H30" s="5" t="n">
         <f aca="false">'USA PL'!H30+'Nigeria PL'!H30</f>
-        <v>84671.8750000001</v>
+        <v>113377.708333333</v>
       </c>
       <c r="I30" s="5" t="n">
         <f aca="false">'USA PL'!I30+'Nigeria PL'!I30</f>
-        <v>107604.166666667</v>
+        <v>137820.833333333</v>
       </c>
       <c r="J30" s="5" t="n">
         <f aca="false">'USA PL'!J30+'Nigeria PL'!J30</f>
-        <v>84671.8750000001</v>
+        <v>113377.708333333</v>
       </c>
       <c r="K30" s="5" t="n">
         <f aca="false">'USA PL'!K30+'Nigeria PL'!K30</f>
-        <v>61739.5833333334</v>
+        <v>88934.5833333333</v>
       </c>
       <c r="L30" s="5" t="n">
         <f aca="false">'USA PL'!L30+'Nigeria PL'!L30</f>
-        <v>107604.166666667</v>
+        <v>137820.833333333</v>
       </c>
       <c r="M30" s="5" t="n">
         <f aca="false">'USA PL'!M30+'Nigeria PL'!M30</f>
-        <v>130536.458333333</v>
+        <v>162263.958333333</v>
       </c>
       <c r="N30" s="5" t="n">
         <f aca="false">'USA PL'!N30+'Nigeria PL'!N30</f>
-        <v>245197.916666667</v>
+        <v>284479.583333333</v>
       </c>
       <c r="O30" s="5" t="n">
         <f aca="false">'USA PL'!O30+'Nigeria PL'!O30</f>
-        <v>268130.208333333</v>
+        <v>308922.708333333</v>
       </c>
       <c r="P30" s="5" t="n">
         <f aca="false">'USA PL'!P30+'Nigeria PL'!P30</f>
-        <v>2017162.5</v>
+        <v>2437162.5</v>
       </c>
       <c r="Q30" s="5" t="n">
         <f aca="false">'USA PL'!Q30+'Nigeria PL'!Q30</f>
-        <v>88409.3750000002</v>
+        <v>118159.375</v>
       </c>
       <c r="R30" s="5" t="n">
         <f aca="false">'USA PL'!R30+'Nigeria PL'!R30</f>
-        <v>88409.3750000002</v>
+        <v>118159.375</v>
       </c>
       <c r="S30" s="5" t="n">
         <f aca="false">'USA PL'!S30+'Nigeria PL'!S30</f>
-        <v>114971.875</v>
+        <v>146471.875</v>
       </c>
       <c r="T30" s="5" t="n">
         <f aca="false">'USA PL'!T30+'Nigeria PL'!T30</f>
-        <v>114971.875</v>
+        <v>146471.875</v>
       </c>
       <c r="U30" s="5" t="n">
         <f aca="false">'USA PL'!U30+'Nigeria PL'!U30</f>
-        <v>141534.375</v>
+        <v>174784.375</v>
       </c>
       <c r="V30" s="5" t="n">
         <f aca="false">'USA PL'!V30+'Nigeria PL'!V30</f>
-        <v>168096.875</v>
+        <v>203096.875</v>
       </c>
       <c r="W30" s="5" t="n">
         <f aca="false">'USA PL'!W30+'Nigeria PL'!W30</f>
-        <v>141534.375</v>
+        <v>174784.375</v>
       </c>
       <c r="X30" s="5" t="n">
         <f aca="false">'USA PL'!X30+'Nigeria PL'!X30</f>
-        <v>114971.875</v>
+        <v>146471.875</v>
       </c>
       <c r="Y30" s="5" t="n">
         <f aca="false">'USA PL'!Y30+'Nigeria PL'!Y30</f>
-        <v>168096.875</v>
+        <v>203096.875</v>
       </c>
       <c r="Z30" s="5" t="n">
         <f aca="false">'USA PL'!Z30+'Nigeria PL'!Z30</f>
-        <v>194659.375</v>
+        <v>231409.375</v>
       </c>
       <c r="AA30" s="5" t="n">
         <f aca="false">'USA PL'!AA30+'Nigeria PL'!AA30</f>
-        <v>327471.875</v>
+        <v>372971.875</v>
       </c>
       <c r="AB30" s="5" t="n">
         <f aca="false">'USA PL'!AB30+'Nigeria PL'!AB30</f>
-        <v>354034.375</v>
+        <v>401284.375</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7691,107 +7691,107 @@
       </c>
       <c r="C31" s="13" t="n">
         <f aca="false">IF(C6=0,0,C30/C6)</f>
-        <v>0.0997104247104248</v>
+        <v>0.127710424710425</v>
       </c>
       <c r="D31" s="13" t="n">
         <f aca="false">IF(D6=0,0,D30/D6)</f>
-        <v>0.0423063820122644</v>
+        <v>0.0703063820122643</v>
       </c>
       <c r="E31" s="13" t="n">
         <f aca="false">IF(E6=0,0,E30/E6)</f>
-        <v>0.0423063820122644</v>
+        <v>0.0703063820122643</v>
       </c>
       <c r="F31" s="13" t="n">
         <f aca="false">IF(F6=0,0,F30/F6)</f>
-        <v>0.0635671385671386</v>
+        <v>0.0915671385671385</v>
       </c>
       <c r="G31" s="13" t="n">
         <f aca="false">IF(G6=0,0,G30/G6)</f>
-        <v>0.0635671385671386</v>
+        <v>0.0915671385671385</v>
       </c>
       <c r="H31" s="13" t="n">
         <f aca="false">IF(H6=0,0,H30/H6)</f>
-        <v>0.0825899207478155</v>
+        <v>0.110589920747815</v>
       </c>
       <c r="I31" s="13" t="n">
         <f aca="false">IF(I6=0,0,I30/I6)</f>
-        <v>0.0997104247104247</v>
+        <v>0.127710424710425</v>
       </c>
       <c r="J31" s="13" t="n">
         <f aca="false">IF(J6=0,0,J30/J6)</f>
-        <v>0.0825899207478155</v>
+        <v>0.110589920747815</v>
       </c>
       <c r="K31" s="13" t="n">
         <f aca="false">IF(K6=0,0,K30/K6)</f>
-        <v>0.0635671385671386</v>
+        <v>0.0915671385671385</v>
       </c>
       <c r="L31" s="13" t="n">
         <f aca="false">IF(L6=0,0,L30/L6)</f>
-        <v>0.0997104247104247</v>
+        <v>0.127710424710425</v>
       </c>
       <c r="M31" s="13" t="n">
         <f aca="false">IF(M6=0,0,M30/M6)</f>
-        <v>0.115200404486119</v>
+        <v>0.143200404486119</v>
       </c>
       <c r="N31" s="13" t="n">
         <f aca="false">IF(N6=0,0,N30/N6)</f>
-        <v>0.17477724977725</v>
+        <v>0.20277724977725</v>
       </c>
       <c r="O31" s="13" t="n">
         <f aca="false">IF(O6=0,0,O30/O6)</f>
-        <v>0.184044759044759</v>
+        <v>0.212044759044759</v>
       </c>
       <c r="P31" s="13" t="n">
         <f aca="false">IF(P6=0,0,P30/P6)</f>
-        <v>0.1344775</v>
+        <v>0.1624775</v>
       </c>
       <c r="Q31" s="13" t="n">
         <f aca="false">IF(Q6=0,0,Q30/Q6)</f>
-        <v>0.0832088235294119</v>
+        <v>0.111208823529412</v>
       </c>
       <c r="R31" s="13" t="n">
         <f aca="false">IF(R6=0,0,R30/R6)</f>
-        <v>0.0832088235294119</v>
+        <v>0.111208823529412</v>
       </c>
       <c r="S31" s="13" t="n">
         <f aca="false">IF(S6=0,0,S30/S6)</f>
-        <v>0.102197222222222</v>
+        <v>0.130197222222222</v>
       </c>
       <c r="T31" s="13" t="n">
         <f aca="false">IF(T6=0,0,T30/T6)</f>
-        <v>0.102197222222222</v>
+        <v>0.130197222222222</v>
       </c>
       <c r="U31" s="13" t="n">
         <f aca="false">IF(U6=0,0,U30/U6)</f>
-        <v>0.119186842105263</v>
+        <v>0.147186842105263</v>
       </c>
       <c r="V31" s="13" t="n">
         <f aca="false">IF(V6=0,0,V30/V6)</f>
-        <v>0.1344775</v>
+        <v>0.1624775</v>
       </c>
       <c r="W31" s="13" t="n">
         <f aca="false">IF(W6=0,0,W30/W6)</f>
-        <v>0.119186842105263</v>
+        <v>0.147186842105263</v>
       </c>
       <c r="X31" s="13" t="n">
         <f aca="false">IF(X6=0,0,X30/X6)</f>
-        <v>0.102197222222222</v>
+        <v>0.130197222222222</v>
       </c>
       <c r="Y31" s="13" t="n">
         <f aca="false">IF(Y6=0,0,Y30/Y6)</f>
-        <v>0.1344775</v>
+        <v>0.1624775</v>
       </c>
       <c r="Z31" s="13" t="n">
         <f aca="false">IF(Z6=0,0,Z30/Z6)</f>
-        <v>0.148311904761905</v>
+        <v>0.176311904761905</v>
       </c>
       <c r="AA31" s="13" t="n">
         <f aca="false">IF(AA6=0,0,AA30/AA6)</f>
-        <v>0.201521153846154</v>
+        <v>0.229521153846154</v>
       </c>
       <c r="AB31" s="13" t="n">
         <f aca="false">IF(AB6=0,0,AB30/AB6)</f>
-        <v>0.209798148148148</v>
+        <v>0.237798148148148</v>
       </c>
     </row>
   </sheetData>
@@ -7917,95 +7917,95 @@
       </c>
       <c r="D6" s="7" t="n">
         <f aca="false">C11</f>
-        <v>2183296.875</v>
+        <v>2198866.04166667</v>
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">D11</f>
-        <v>2166593.75</v>
+        <v>2197732.08333333</v>
       </c>
       <c r="F6" s="7" t="n">
         <f aca="false">E11</f>
-        <v>2131083.33333333</v>
+        <v>2178706.66666667</v>
       </c>
       <c r="G6" s="7" t="n">
         <f aca="false">F11</f>
-        <v>2128281.25</v>
+        <v>2192389.58333333</v>
       </c>
       <c r="H6" s="7" t="n">
         <f aca="false">G11</f>
-        <v>2106671.875</v>
+        <v>2188181.04166667</v>
       </c>
       <c r="I6" s="7" t="n">
         <f aca="false">H11</f>
-        <v>2098963.54166667</v>
+        <v>2198789.375</v>
       </c>
       <c r="J6" s="7" t="n">
         <f aca="false">I11</f>
-        <v>2142770.83333333</v>
+        <v>2259997.5</v>
       </c>
       <c r="K6" s="7" t="n">
         <f aca="false">J11</f>
-        <v>2172677.08333333</v>
+        <v>2306388.75</v>
       </c>
       <c r="L6" s="7" t="n">
         <f aca="false">K11</f>
-        <v>2132260.41666667</v>
+        <v>2284288.75</v>
       </c>
       <c r="M6" s="7" t="n">
         <f aca="false">L11</f>
-        <v>2138453.125</v>
+        <v>2309713.95833333</v>
       </c>
       <c r="N6" s="7" t="n">
         <f aca="false">M11</f>
-        <v>2083317.70833333</v>
+        <v>2278390.20833333</v>
       </c>
       <c r="O6" s="7" t="n">
         <f aca="false">N11</f>
-        <v>2172916.66666667</v>
+        <v>2392716.66666667</v>
       </c>
       <c r="P6" s="7" t="n">
         <f aca="false">O11</f>
-        <v>2427602.60416667</v>
+        <v>2665252.60416667</v>
       </c>
       <c r="Q6" s="7" t="n">
         <f aca="false">P11</f>
-        <v>2436663.54166667</v>
+        <v>2692163.54166667</v>
       </c>
       <c r="R6" s="7" t="n">
         <f aca="false">Q11</f>
-        <v>2424161.97916667</v>
+        <v>2698561.97916667</v>
       </c>
       <c r="S6" s="7" t="n">
         <f aca="false">R11</f>
-        <v>2449160.41666667</v>
+        <v>2742460.41666667</v>
       </c>
       <c r="T6" s="7" t="n">
         <f aca="false">S11</f>
-        <v>2452596.35416667</v>
+        <v>2765846.35416667</v>
       </c>
       <c r="U6" s="7" t="n">
         <f aca="false">T11</f>
-        <v>2471969.79166667</v>
+        <v>2806219.79166667</v>
       </c>
       <c r="V6" s="7" t="n">
         <f aca="false">U11</f>
-        <v>2550405.72916667</v>
+        <v>2904605.72916667</v>
       </c>
       <c r="W6" s="7" t="n">
         <f aca="false">V11</f>
-        <v>2612904.16666667</v>
+        <v>2986004.16666667</v>
       </c>
       <c r="X6" s="7" t="n">
         <f aca="false">W11</f>
-        <v>2594777.60416667</v>
+        <v>2988877.60416667</v>
       </c>
       <c r="Y6" s="7" t="n">
         <f aca="false">X11</f>
-        <v>2630088.54166667</v>
+        <v>3046238.54166667</v>
       </c>
       <c r="Z6" s="7" t="n">
         <f aca="false">Y11</f>
-        <v>2595086.97916667</v>
+        <v>3038536.97916667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8115,99 +8115,99 @@
       </c>
       <c r="C8" s="11" t="n">
         <f aca="false">'USA PL'!D9</f>
-        <v>308603.125</v>
+        <v>293033.958333333</v>
       </c>
       <c r="D8" s="11" t="n">
         <f aca="false">'USA PL'!E9</f>
-        <v>308603.125</v>
+        <v>293033.958333333</v>
       </c>
       <c r="E8" s="11" t="n">
         <f aca="false">'USA PL'!F9</f>
-        <v>326756.25</v>
+        <v>310271.25</v>
       </c>
       <c r="F8" s="11" t="n">
         <f aca="false">'USA PL'!G9</f>
-        <v>326756.25</v>
+        <v>310271.25</v>
       </c>
       <c r="G8" s="11" t="n">
         <f aca="false">'USA PL'!H9</f>
-        <v>344909.375</v>
+        <v>327508.541666667</v>
       </c>
       <c r="H8" s="11" t="n">
         <f aca="false">'USA PL'!I9</f>
-        <v>363062.5</v>
+        <v>344745.833333333</v>
       </c>
       <c r="I8" s="11" t="n">
         <f aca="false">'USA PL'!J9</f>
-        <v>344909.375</v>
+        <v>327508.541666667</v>
       </c>
       <c r="J8" s="11" t="n">
         <f aca="false">'USA PL'!K9</f>
-        <v>326756.25</v>
+        <v>310271.25</v>
       </c>
       <c r="K8" s="11" t="n">
         <f aca="false">'USA PL'!L9</f>
-        <v>363062.5</v>
+        <v>344745.833333333</v>
       </c>
       <c r="L8" s="11" t="n">
         <f aca="false">'USA PL'!M9</f>
-        <v>381215.625</v>
+        <v>361983.125</v>
       </c>
       <c r="M8" s="11" t="n">
         <f aca="false">'USA PL'!N9</f>
-        <v>471981.25</v>
+        <v>448169.583333333</v>
       </c>
       <c r="N8" s="11" t="n">
         <f aca="false">'USA PL'!O9</f>
-        <v>490134.375</v>
+        <v>465406.875</v>
       </c>
       <c r="O8" s="11" t="n">
         <f aca="false">'USA PL'!Q9</f>
-        <v>353812.5</v>
+        <v>335962.5</v>
       </c>
       <c r="P8" s="11" t="n">
         <f aca="false">'USA PL'!R9</f>
-        <v>353812.5</v>
+        <v>335962.5</v>
       </c>
       <c r="Q8" s="11" t="n">
         <f aca="false">'USA PL'!S9</f>
-        <v>374625</v>
+        <v>355725</v>
       </c>
       <c r="R8" s="11" t="n">
         <f aca="false">'USA PL'!T9</f>
-        <v>374625</v>
+        <v>355725</v>
       </c>
       <c r="S8" s="11" t="n">
         <f aca="false">'USA PL'!U9</f>
-        <v>395437.5</v>
+        <v>375487.5</v>
       </c>
       <c r="T8" s="11" t="n">
         <f aca="false">'USA PL'!V9</f>
-        <v>416250</v>
+        <v>395250</v>
       </c>
       <c r="U8" s="11" t="n">
         <f aca="false">'USA PL'!W9</f>
-        <v>395437.5</v>
+        <v>375487.5</v>
       </c>
       <c r="V8" s="11" t="n">
         <f aca="false">'USA PL'!X9</f>
-        <v>374625</v>
+        <v>355725</v>
       </c>
       <c r="W8" s="11" t="n">
         <f aca="false">'USA PL'!Y9</f>
-        <v>416250</v>
+        <v>395250</v>
       </c>
       <c r="X8" s="11" t="n">
         <f aca="false">'USA PL'!Z9</f>
-        <v>437062.5</v>
+        <v>415012.5</v>
       </c>
       <c r="Y8" s="11" t="n">
         <f aca="false">'USA PL'!AA9</f>
-        <v>541125</v>
+        <v>513825</v>
       </c>
       <c r="Z8" s="11" t="n">
         <f aca="false">'USA PL'!AB9</f>
-        <v>561937.5</v>
+        <v>533587.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8317,99 +8317,99 @@
       </c>
       <c r="C10" s="5" t="n">
         <f aca="false">C7-C8-C9</f>
-        <v>-16703.125</v>
+        <v>-1133.95833333337</v>
       </c>
       <c r="D10" s="5" t="n">
         <f aca="false">D7-D8-D9</f>
-        <v>-16703.125</v>
+        <v>-1133.95833333337</v>
       </c>
       <c r="E10" s="5" t="n">
         <f aca="false">E7-E8-E9</f>
-        <v>-35510.4166666667</v>
+        <v>-19025.4166666667</v>
       </c>
       <c r="F10" s="5" t="n">
         <f aca="false">F7-F8-F9</f>
-        <v>-2802.08333333331</v>
+        <v>13682.9166666666</v>
       </c>
       <c r="G10" s="5" t="n">
         <f aca="false">G7-G8-G9</f>
-        <v>-21609.375</v>
+        <v>-4208.54166666669</v>
       </c>
       <c r="H10" s="5" t="n">
         <f aca="false">H7-H8-H9</f>
-        <v>-7708.33333333326</v>
+        <v>10608.3333333334</v>
       </c>
       <c r="I10" s="5" t="n">
         <f aca="false">I7-I8-I9</f>
-        <v>43807.2916666666</v>
+        <v>61208.1249999999</v>
       </c>
       <c r="J10" s="5" t="n">
         <f aca="false">J7-J8-J9</f>
-        <v>29906.2500000001</v>
+        <v>46391.25</v>
       </c>
       <c r="K10" s="5" t="n">
         <f aca="false">K7-K8-K9</f>
-        <v>-40416.6666666666</v>
+        <v>-22100</v>
       </c>
       <c r="L10" s="5" t="n">
         <f aca="false">L7-L8-L9</f>
-        <v>6192.70833333331</v>
+        <v>25425.2083333333</v>
       </c>
       <c r="M10" s="5" t="n">
         <f aca="false">M7-M8-M9</f>
-        <v>-55135.4166666666</v>
+        <v>-31323.75</v>
       </c>
       <c r="N10" s="5" t="n">
         <f aca="false">N7-N8-N9</f>
-        <v>89598.9583333333</v>
+        <v>114326.458333333</v>
       </c>
       <c r="O10" s="5" t="n">
         <f aca="false">O7-O8-O9</f>
-        <v>254685.9375</v>
+        <v>272535.9375</v>
       </c>
       <c r="P10" s="5" t="n">
         <f aca="false">P7-P8-P9</f>
-        <v>9060.93750000012</v>
+        <v>26910.9375000001</v>
       </c>
       <c r="Q10" s="5" t="n">
         <f aca="false">Q7-Q8-Q9</f>
-        <v>-12501.5624999999</v>
+        <v>6398.43750000006</v>
       </c>
       <c r="R10" s="5" t="n">
         <f aca="false">R7-R8-R9</f>
-        <v>24998.4375000001</v>
+        <v>43898.4375000001</v>
       </c>
       <c r="S10" s="5" t="n">
         <f aca="false">S7-S8-S9</f>
-        <v>3435.93750000012</v>
+        <v>23385.9375000001</v>
       </c>
       <c r="T10" s="5" t="n">
         <f aca="false">T7-T8-T9</f>
-        <v>19373.4375000001</v>
+        <v>40373.4375000001</v>
       </c>
       <c r="U10" s="5" t="n">
         <f aca="false">U7-U8-U9</f>
-        <v>78435.9375000001</v>
+        <v>98385.9375000001</v>
       </c>
       <c r="V10" s="5" t="n">
         <f aca="false">V7-V8-V9</f>
-        <v>62498.4375000001</v>
+        <v>81398.4375000001</v>
       </c>
       <c r="W10" s="5" t="n">
         <f aca="false">W7-W8-W9</f>
-        <v>-18126.5624999999</v>
+        <v>2873.43750000006</v>
       </c>
       <c r="X10" s="5" t="n">
         <f aca="false">X7-X8-X9</f>
-        <v>35310.9375000001</v>
+        <v>57360.9375000001</v>
       </c>
       <c r="Y10" s="5" t="n">
         <f aca="false">Y7-Y8-Y9</f>
-        <v>-35001.5624999998</v>
+        <v>-7701.56249999994</v>
       </c>
       <c r="Z10" s="5" t="n">
         <f aca="false">Z7-Z8-Z9</f>
-        <v>130935.9375</v>
+        <v>159285.9375</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8418,99 +8418,99 @@
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">C6+C10</f>
-        <v>2183296.875</v>
+        <v>2198866.04166667</v>
       </c>
       <c r="D11" s="5" t="n">
         <f aca="false">D6+D10</f>
-        <v>2166593.75</v>
+        <v>2197732.08333333</v>
       </c>
       <c r="E11" s="5" t="n">
         <f aca="false">E6+E10</f>
-        <v>2131083.33333333</v>
+        <v>2178706.66666667</v>
       </c>
       <c r="F11" s="5" t="n">
         <f aca="false">F6+F10</f>
-        <v>2128281.25</v>
+        <v>2192389.58333333</v>
       </c>
       <c r="G11" s="5" t="n">
         <f aca="false">G6+G10</f>
-        <v>2106671.875</v>
+        <v>2188181.04166667</v>
       </c>
       <c r="H11" s="5" t="n">
         <f aca="false">H6+H10</f>
-        <v>2098963.54166667</v>
+        <v>2198789.375</v>
       </c>
       <c r="I11" s="5" t="n">
         <f aca="false">I6+I10</f>
-        <v>2142770.83333333</v>
+        <v>2259997.5</v>
       </c>
       <c r="J11" s="5" t="n">
         <f aca="false">J6+J10</f>
-        <v>2172677.08333333</v>
+        <v>2306388.75</v>
       </c>
       <c r="K11" s="5" t="n">
         <f aca="false">K6+K10</f>
-        <v>2132260.41666667</v>
+        <v>2284288.75</v>
       </c>
       <c r="L11" s="5" t="n">
         <f aca="false">L6+L10</f>
-        <v>2138453.125</v>
+        <v>2309713.95833333</v>
       </c>
       <c r="M11" s="5" t="n">
         <f aca="false">M6+M10</f>
-        <v>2083317.70833333</v>
+        <v>2278390.20833333</v>
       </c>
       <c r="N11" s="5" t="n">
         <f aca="false">N6+N10</f>
-        <v>2172916.66666667</v>
+        <v>2392716.66666667</v>
       </c>
       <c r="O11" s="5" t="n">
         <f aca="false">O6+O10</f>
-        <v>2427602.60416667</v>
+        <v>2665252.60416667</v>
       </c>
       <c r="P11" s="5" t="n">
         <f aca="false">P6+P10</f>
-        <v>2436663.54166667</v>
+        <v>2692163.54166667</v>
       </c>
       <c r="Q11" s="5" t="n">
         <f aca="false">Q6+Q10</f>
-        <v>2424161.97916667</v>
+        <v>2698561.97916667</v>
       </c>
       <c r="R11" s="5" t="n">
         <f aca="false">R6+R10</f>
-        <v>2449160.41666667</v>
+        <v>2742460.41666667</v>
       </c>
       <c r="S11" s="5" t="n">
         <f aca="false">S6+S10</f>
-        <v>2452596.35416667</v>
+        <v>2765846.35416667</v>
       </c>
       <c r="T11" s="5" t="n">
         <f aca="false">T6+T10</f>
-        <v>2471969.79166667</v>
+        <v>2806219.79166667</v>
       </c>
       <c r="U11" s="5" t="n">
         <f aca="false">U6+U10</f>
-        <v>2550405.72916667</v>
+        <v>2904605.72916667</v>
       </c>
       <c r="V11" s="5" t="n">
         <f aca="false">V6+V10</f>
-        <v>2612904.16666667</v>
+        <v>2986004.16666667</v>
       </c>
       <c r="W11" s="5" t="n">
         <f aca="false">W6+W10</f>
-        <v>2594777.60416667</v>
+        <v>2988877.60416667</v>
       </c>
       <c r="X11" s="5" t="n">
         <f aca="false">X6+X10</f>
-        <v>2630088.54166667</v>
+        <v>3046238.54166667</v>
       </c>
       <c r="Y11" s="5" t="n">
         <f aca="false">Y6+Y10</f>
-        <v>2595086.97916667</v>
+        <v>3038536.97916667</v>
       </c>
       <c r="Z11" s="5" t="n">
         <f aca="false">Z6+Z10</f>
-        <v>2726022.91666667</v>
+        <v>3197822.91666667</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8528,95 +8528,95 @@
       </c>
       <c r="D14" s="7" t="n">
         <f aca="false">C19</f>
-        <v>2260510.41666667</v>
+        <v>2270625.41666667</v>
       </c>
       <c r="E14" s="7" t="n">
         <f aca="false">D19</f>
-        <v>2321020.83333333</v>
+        <v>2341250.83333333</v>
       </c>
       <c r="F14" s="7" t="n">
         <f aca="false">E19</f>
-        <v>2369312.5</v>
+        <v>2400252.5</v>
       </c>
       <c r="G14" s="7" t="n">
         <f aca="false">F19</f>
-        <v>2438854.16666667</v>
+        <v>2480504.16666667</v>
       </c>
       <c r="H14" s="7" t="n">
         <f aca="false">G19</f>
-        <v>2496177.08333333</v>
+        <v>2549132.08333333</v>
       </c>
       <c r="I14" s="7" t="n">
         <f aca="false">H19</f>
-        <v>2562531.25</v>
+        <v>2627386.25</v>
       </c>
       <c r="J14" s="7" t="n">
         <f aca="false">I19</f>
-        <v>2662354.16666667</v>
+        <v>2738514.16666667</v>
       </c>
       <c r="K14" s="7" t="n">
         <f aca="false">J19</f>
-        <v>2753145.83333333</v>
+        <v>2840015.83333333</v>
       </c>
       <c r="L14" s="7" t="n">
         <f aca="false">K19</f>
-        <v>2798250</v>
+        <v>2897020</v>
       </c>
       <c r="M14" s="7" t="n">
         <f aca="false">L19</f>
-        <v>2873635.41666667</v>
+        <v>2984900.41666667</v>
       </c>
       <c r="N14" s="7" t="n">
         <f aca="false">M19</f>
-        <v>2909177.08333333</v>
+        <v>3035912.08333333</v>
       </c>
       <c r="O14" s="7" t="n">
         <f aca="false">N19</f>
-        <v>3038750</v>
+        <v>3181550</v>
       </c>
       <c r="P14" s="7" t="n">
         <f aca="false">O19</f>
-        <v>3271848.4375</v>
+        <v>3426548.4375</v>
       </c>
       <c r="Q14" s="7" t="n">
         <f aca="false">P19</f>
-        <v>3356196.875</v>
+        <v>3522796.875</v>
       </c>
       <c r="R14" s="7" t="n">
         <f aca="false">Q19</f>
-        <v>3426170.3125</v>
+        <v>3605370.3125</v>
       </c>
       <c r="S14" s="7" t="n">
         <f aca="false">R19</f>
-        <v>3521143.75</v>
+        <v>3712943.75</v>
       </c>
       <c r="T14" s="7" t="n">
         <f aca="false">S19</f>
-        <v>3601742.1875</v>
+        <v>3806842.1875</v>
       </c>
       <c r="U14" s="7" t="n">
         <f aca="false">T19</f>
-        <v>3692965.625</v>
+        <v>3912065.625</v>
       </c>
       <c r="V14" s="7" t="n">
         <f aca="false">U19</f>
-        <v>3823564.0625</v>
+        <v>4055964.0625</v>
       </c>
       <c r="W14" s="7" t="n">
         <f aca="false">V19</f>
-        <v>3943537.5</v>
+        <v>4188537.5</v>
       </c>
       <c r="X14" s="7" t="n">
         <f aca="false">W19</f>
-        <v>4009760.9375</v>
+        <v>4268760.9375</v>
       </c>
       <c r="Y14" s="7" t="n">
         <f aca="false">X19</f>
-        <v>4111609.375</v>
+        <v>4385309.375</v>
       </c>
       <c r="Z14" s="7" t="n">
         <f aca="false">Y19</f>
-        <v>4166582.8125</v>
+        <v>4458482.8125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8726,99 +8726,99 @@
       </c>
       <c r="C16" s="11" t="n">
         <f aca="false">'Nigeria PL'!D9</f>
-        <v>200493.75</v>
+        <v>190378.75</v>
       </c>
       <c r="D16" s="11" t="n">
         <f aca="false">'Nigeria PL'!E9</f>
-        <v>200493.75</v>
+        <v>190378.75</v>
       </c>
       <c r="E16" s="11" t="n">
         <f aca="false">'Nigeria PL'!F9</f>
-        <v>212287.5</v>
+        <v>201577.5</v>
       </c>
       <c r="F16" s="11" t="n">
         <f aca="false">'Nigeria PL'!G9</f>
-        <v>212287.5</v>
+        <v>201577.5</v>
       </c>
       <c r="G16" s="11" t="n">
         <f aca="false">'Nigeria PL'!H9</f>
-        <v>224081.25</v>
+        <v>212776.25</v>
       </c>
       <c r="H16" s="11" t="n">
         <f aca="false">'Nigeria PL'!I9</f>
-        <v>235875</v>
+        <v>223975</v>
       </c>
       <c r="I16" s="11" t="n">
         <f aca="false">'Nigeria PL'!J9</f>
-        <v>224081.25</v>
+        <v>212776.25</v>
       </c>
       <c r="J16" s="11" t="n">
         <f aca="false">'Nigeria PL'!K9</f>
-        <v>212287.5</v>
+        <v>201577.5</v>
       </c>
       <c r="K16" s="11" t="n">
         <f aca="false">'Nigeria PL'!L9</f>
-        <v>235875</v>
+        <v>223975</v>
       </c>
       <c r="L16" s="11" t="n">
         <f aca="false">'Nigeria PL'!M9</f>
-        <v>247668.75</v>
+        <v>235173.75</v>
       </c>
       <c r="M16" s="11" t="n">
         <f aca="false">'Nigeria PL'!N9</f>
-        <v>306637.5</v>
+        <v>291167.5</v>
       </c>
       <c r="N16" s="11" t="n">
         <f aca="false">'Nigeria PL'!O9</f>
-        <v>318431.25</v>
+        <v>302366.25</v>
       </c>
       <c r="O16" s="11" t="n">
         <f aca="false">'Nigeria PL'!Q9</f>
-        <v>235875</v>
+        <v>223975</v>
       </c>
       <c r="P16" s="11" t="n">
         <f aca="false">'Nigeria PL'!R9</f>
-        <v>235875</v>
+        <v>223975</v>
       </c>
       <c r="Q16" s="11" t="n">
         <f aca="false">'Nigeria PL'!S9</f>
-        <v>249750</v>
+        <v>237150</v>
       </c>
       <c r="R16" s="11" t="n">
         <f aca="false">'Nigeria PL'!T9</f>
-        <v>249750</v>
+        <v>237150</v>
       </c>
       <c r="S16" s="11" t="n">
         <f aca="false">'Nigeria PL'!U9</f>
-        <v>263625</v>
+        <v>250325</v>
       </c>
       <c r="T16" s="11" t="n">
         <f aca="false">'Nigeria PL'!V9</f>
-        <v>277500</v>
+        <v>263500</v>
       </c>
       <c r="U16" s="11" t="n">
         <f aca="false">'Nigeria PL'!W9</f>
-        <v>263625</v>
+        <v>250325</v>
       </c>
       <c r="V16" s="11" t="n">
         <f aca="false">'Nigeria PL'!X9</f>
-        <v>249750</v>
+        <v>237150</v>
       </c>
       <c r="W16" s="11" t="n">
         <f aca="false">'Nigeria PL'!Y9</f>
-        <v>277500</v>
+        <v>263500</v>
       </c>
       <c r="X16" s="11" t="n">
         <f aca="false">'Nigeria PL'!Z9</f>
-        <v>291375</v>
+        <v>276675</v>
       </c>
       <c r="Y16" s="11" t="n">
         <f aca="false">'Nigeria PL'!AA9</f>
-        <v>360750</v>
+        <v>342550</v>
       </c>
       <c r="Z16" s="11" t="n">
         <f aca="false">'Nigeria PL'!AB9</f>
-        <v>374625</v>
+        <v>355725</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8928,99 +8928,99 @@
       </c>
       <c r="C18" s="5" t="n">
         <f aca="false">C15-C16-C17</f>
-        <v>60510.4166666667</v>
+        <v>70625.4166666667</v>
       </c>
       <c r="D18" s="5" t="n">
         <f aca="false">D15-D16-D17</f>
-        <v>60510.4166666667</v>
+        <v>70625.4166666667</v>
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">E15-E16-E17</f>
-        <v>48291.6666666667</v>
+        <v>59001.6666666667</v>
       </c>
       <c r="F18" s="5" t="n">
         <f aca="false">F15-F16-F17</f>
-        <v>69541.6666666667</v>
+        <v>80251.6666666667</v>
       </c>
       <c r="G18" s="5" t="n">
         <f aca="false">G15-G16-G17</f>
-        <v>57322.9166666667</v>
+        <v>68627.9166666667</v>
       </c>
       <c r="H18" s="5" t="n">
         <f aca="false">H15-H16-H17</f>
-        <v>66354.1666666667</v>
+        <v>78254.1666666667</v>
       </c>
       <c r="I18" s="5" t="n">
         <f aca="false">I15-I16-I17</f>
-        <v>99822.9166666667</v>
+        <v>111127.916666667</v>
       </c>
       <c r="J18" s="5" t="n">
         <f aca="false">J15-J16-J17</f>
-        <v>90791.6666666667</v>
+        <v>101501.666666667</v>
       </c>
       <c r="K18" s="5" t="n">
         <f aca="false">K15-K16-K17</f>
-        <v>45104.1666666667</v>
+        <v>57004.1666666667</v>
       </c>
       <c r="L18" s="5" t="n">
         <f aca="false">L15-L16-L17</f>
-        <v>75385.4166666667</v>
+        <v>87880.4166666667</v>
       </c>
       <c r="M18" s="5" t="n">
         <f aca="false">M15-M16-M17</f>
-        <v>35541.6666666667</v>
+        <v>51011.6666666667</v>
       </c>
       <c r="N18" s="5" t="n">
         <f aca="false">N15-N16-N17</f>
-        <v>129572.916666667</v>
+        <v>145637.916666667</v>
       </c>
       <c r="O18" s="5" t="n">
         <f aca="false">O15-O16-O17</f>
-        <v>233098.4375</v>
+        <v>244998.4375</v>
       </c>
       <c r="P18" s="5" t="n">
         <f aca="false">P15-P16-P17</f>
-        <v>84348.4375</v>
+        <v>96248.4375</v>
       </c>
       <c r="Q18" s="5" t="n">
         <f aca="false">Q15-Q16-Q17</f>
-        <v>69973.4375</v>
+        <v>82573.4375</v>
       </c>
       <c r="R18" s="5" t="n">
         <f aca="false">R15-R16-R17</f>
-        <v>94973.4375</v>
+        <v>107573.4375</v>
       </c>
       <c r="S18" s="5" t="n">
         <f aca="false">S15-S16-S17</f>
-        <v>80598.4375000001</v>
+        <v>93898.4375</v>
       </c>
       <c r="T18" s="5" t="n">
         <f aca="false">T15-T16-T17</f>
-        <v>91223.4375000001</v>
+        <v>105223.4375</v>
       </c>
       <c r="U18" s="5" t="n">
         <f aca="false">U15-U16-U17</f>
-        <v>130598.4375</v>
+        <v>143898.4375</v>
       </c>
       <c r="V18" s="5" t="n">
         <f aca="false">V15-V16-V17</f>
-        <v>119973.4375</v>
+        <v>132573.4375</v>
       </c>
       <c r="W18" s="5" t="n">
         <f aca="false">W15-W16-W17</f>
-        <v>66223.4375000001</v>
+        <v>80223.4375</v>
       </c>
       <c r="X18" s="5" t="n">
         <f aca="false">X15-X16-X17</f>
-        <v>101848.4375</v>
+        <v>116548.4375</v>
       </c>
       <c r="Y18" s="5" t="n">
         <f aca="false">Y15-Y16-Y17</f>
-        <v>54973.4375000001</v>
+        <v>73173.4375</v>
       </c>
       <c r="Z18" s="5" t="n">
         <f aca="false">Z15-Z16-Z17</f>
-        <v>165598.4375</v>
+        <v>184498.4375</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9029,99 +9029,99 @@
       </c>
       <c r="C19" s="5" t="n">
         <f aca="false">C14+C18</f>
-        <v>2260510.41666667</v>
+        <v>2270625.41666667</v>
       </c>
       <c r="D19" s="5" t="n">
         <f aca="false">D14+D18</f>
-        <v>2321020.83333333</v>
+        <v>2341250.83333333</v>
       </c>
       <c r="E19" s="5" t="n">
         <f aca="false">E14+E18</f>
-        <v>2369312.5</v>
+        <v>2400252.5</v>
       </c>
       <c r="F19" s="5" t="n">
         <f aca="false">F14+F18</f>
-        <v>2438854.16666667</v>
+        <v>2480504.16666667</v>
       </c>
       <c r="G19" s="5" t="n">
         <f aca="false">G14+G18</f>
-        <v>2496177.08333333</v>
+        <v>2549132.08333333</v>
       </c>
       <c r="H19" s="5" t="n">
         <f aca="false">H14+H18</f>
-        <v>2562531.25</v>
+        <v>2627386.25</v>
       </c>
       <c r="I19" s="5" t="n">
         <f aca="false">I14+I18</f>
-        <v>2662354.16666667</v>
+        <v>2738514.16666667</v>
       </c>
       <c r="J19" s="5" t="n">
         <f aca="false">J14+J18</f>
-        <v>2753145.83333333</v>
+        <v>2840015.83333333</v>
       </c>
       <c r="K19" s="5" t="n">
         <f aca="false">K14+K18</f>
-        <v>2798250</v>
+        <v>2897020</v>
       </c>
       <c r="L19" s="5" t="n">
         <f aca="false">L14+L18</f>
-        <v>2873635.41666667</v>
+        <v>2984900.41666667</v>
       </c>
       <c r="M19" s="5" t="n">
         <f aca="false">M14+M18</f>
-        <v>2909177.08333333</v>
+        <v>3035912.08333333</v>
       </c>
       <c r="N19" s="5" t="n">
         <f aca="false">N14+N18</f>
-        <v>3038750</v>
+        <v>3181550</v>
       </c>
       <c r="O19" s="5" t="n">
         <f aca="false">O14+O18</f>
-        <v>3271848.4375</v>
+        <v>3426548.4375</v>
       </c>
       <c r="P19" s="5" t="n">
         <f aca="false">P14+P18</f>
-        <v>3356196.875</v>
+        <v>3522796.875</v>
       </c>
       <c r="Q19" s="5" t="n">
         <f aca="false">Q14+Q18</f>
-        <v>3426170.3125</v>
+        <v>3605370.3125</v>
       </c>
       <c r="R19" s="5" t="n">
         <f aca="false">R14+R18</f>
-        <v>3521143.75</v>
+        <v>3712943.75</v>
       </c>
       <c r="S19" s="5" t="n">
         <f aca="false">S14+S18</f>
-        <v>3601742.1875</v>
+        <v>3806842.1875</v>
       </c>
       <c r="T19" s="5" t="n">
         <f aca="false">T14+T18</f>
-        <v>3692965.625</v>
+        <v>3912065.625</v>
       </c>
       <c r="U19" s="5" t="n">
         <f aca="false">U14+U18</f>
-        <v>3823564.0625</v>
+        <v>4055964.0625</v>
       </c>
       <c r="V19" s="5" t="n">
         <f aca="false">V14+V18</f>
-        <v>3943537.5</v>
+        <v>4188537.5</v>
       </c>
       <c r="W19" s="5" t="n">
         <f aca="false">W14+W18</f>
-        <v>4009760.9375</v>
+        <v>4268760.9375</v>
       </c>
       <c r="X19" s="5" t="n">
         <f aca="false">X14+X18</f>
-        <v>4111609.375</v>
+        <v>4385309.375</v>
       </c>
       <c r="Y19" s="5" t="n">
         <f aca="false">Y14+Y18</f>
-        <v>4166582.8125</v>
+        <v>4458482.8125</v>
       </c>
       <c r="Z19" s="5" t="n">
         <f aca="false">Z14+Z18</f>
-        <v>4332181.25</v>
+        <v>4642981.25</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9139,95 +9139,95 @@
       </c>
       <c r="D22" s="7" t="n">
         <f aca="false">D6+D14</f>
-        <v>4443807.29166667</v>
+        <v>4469491.45833333</v>
       </c>
       <c r="E22" s="7" t="n">
         <f aca="false">E6+E14</f>
-        <v>4487614.58333333</v>
+        <v>4538982.91666667</v>
       </c>
       <c r="F22" s="7" t="n">
         <f aca="false">F6+F14</f>
-        <v>4500395.83333333</v>
+        <v>4578959.16666667</v>
       </c>
       <c r="G22" s="7" t="n">
         <f aca="false">G6+G14</f>
-        <v>4567135.41666667</v>
+        <v>4672893.75</v>
       </c>
       <c r="H22" s="7" t="n">
         <f aca="false">H6+H14</f>
-        <v>4602848.95833333</v>
+        <v>4737313.125</v>
       </c>
       <c r="I22" s="7" t="n">
         <f aca="false">I6+I14</f>
-        <v>4661494.79166667</v>
+        <v>4826175.625</v>
       </c>
       <c r="J22" s="7" t="n">
         <f aca="false">J6+J14</f>
-        <v>4805125</v>
+        <v>4998511.66666667</v>
       </c>
       <c r="K22" s="7" t="n">
         <f aca="false">K6+K14</f>
-        <v>4925822.91666667</v>
+        <v>5146404.58333333</v>
       </c>
       <c r="L22" s="7" t="n">
         <f aca="false">L6+L14</f>
-        <v>4930510.41666667</v>
+        <v>5181308.75</v>
       </c>
       <c r="M22" s="7" t="n">
         <f aca="false">M6+M14</f>
-        <v>5012088.54166667</v>
+        <v>5294614.375</v>
       </c>
       <c r="N22" s="7" t="n">
         <f aca="false">N6+N14</f>
-        <v>4992494.79166667</v>
+        <v>5314302.29166666</v>
       </c>
       <c r="O22" s="7" t="n">
         <f aca="false">O6+O14</f>
-        <v>5211666.66666667</v>
+        <v>5574266.66666666</v>
       </c>
       <c r="P22" s="7" t="n">
         <f aca="false">P6+P14</f>
-        <v>5699451.04166667</v>
+        <v>6091801.04166666</v>
       </c>
       <c r="Q22" s="7" t="n">
         <f aca="false">Q6+Q14</f>
-        <v>5792860.41666667</v>
+        <v>6214960.41666666</v>
       </c>
       <c r="R22" s="7" t="n">
         <f aca="false">R6+R14</f>
-        <v>5850332.29166667</v>
+        <v>6303932.29166666</v>
       </c>
       <c r="S22" s="7" t="n">
         <f aca="false">S6+S14</f>
-        <v>5970304.16666667</v>
+        <v>6455404.16666666</v>
       </c>
       <c r="T22" s="7" t="n">
         <f aca="false">T6+T14</f>
-        <v>6054338.54166667</v>
+        <v>6572688.54166666</v>
       </c>
       <c r="U22" s="7" t="n">
         <f aca="false">U6+U14</f>
-        <v>6164935.41666667</v>
+        <v>6718285.41666666</v>
       </c>
       <c r="V22" s="7" t="n">
         <f aca="false">V6+V14</f>
-        <v>6373969.79166667</v>
+        <v>6960569.79166666</v>
       </c>
       <c r="W22" s="7" t="n">
         <f aca="false">W6+W14</f>
-        <v>6556441.66666667</v>
+        <v>7174541.66666666</v>
       </c>
       <c r="X22" s="7" t="n">
         <f aca="false">X6+X14</f>
-        <v>6604538.54166667</v>
+        <v>7257638.54166666</v>
       </c>
       <c r="Y22" s="7" t="n">
         <f aca="false">Y6+Y14</f>
-        <v>6741697.91666667</v>
+        <v>7431547.91666666</v>
       </c>
       <c r="Z22" s="7" t="n">
         <f aca="false">Z6+Z14</f>
-        <v>6761669.79166667</v>
+        <v>7497019.79166666</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9337,99 +9337,99 @@
       </c>
       <c r="C24" s="7" t="n">
         <f aca="false">C8+C16</f>
-        <v>509096.875</v>
+        <v>483412.708333333</v>
       </c>
       <c r="D24" s="7" t="n">
         <f aca="false">D8+D16</f>
-        <v>509096.875</v>
+        <v>483412.708333333</v>
       </c>
       <c r="E24" s="7" t="n">
         <f aca="false">E8+E16</f>
-        <v>539043.75</v>
+        <v>511848.75</v>
       </c>
       <c r="F24" s="7" t="n">
         <f aca="false">F8+F16</f>
-        <v>539043.75</v>
+        <v>511848.75</v>
       </c>
       <c r="G24" s="7" t="n">
         <f aca="false">G8+G16</f>
-        <v>568990.625</v>
+        <v>540284.791666667</v>
       </c>
       <c r="H24" s="7" t="n">
         <f aca="false">H8+H16</f>
-        <v>598937.5</v>
+        <v>568720.833333333</v>
       </c>
       <c r="I24" s="7" t="n">
         <f aca="false">I8+I16</f>
-        <v>568990.625</v>
+        <v>540284.791666667</v>
       </c>
       <c r="J24" s="7" t="n">
         <f aca="false">J8+J16</f>
-        <v>539043.75</v>
+        <v>511848.75</v>
       </c>
       <c r="K24" s="7" t="n">
         <f aca="false">K8+K16</f>
-        <v>598937.5</v>
+        <v>568720.833333333</v>
       </c>
       <c r="L24" s="7" t="n">
         <f aca="false">L8+L16</f>
-        <v>628884.375</v>
+        <v>597156.875</v>
       </c>
       <c r="M24" s="7" t="n">
         <f aca="false">M8+M16</f>
-        <v>778618.75</v>
+        <v>739337.083333333</v>
       </c>
       <c r="N24" s="7" t="n">
         <f aca="false">N8+N16</f>
-        <v>808565.625</v>
+        <v>767773.125</v>
       </c>
       <c r="O24" s="7" t="n">
         <f aca="false">O8+O16</f>
-        <v>589687.5</v>
+        <v>559937.5</v>
       </c>
       <c r="P24" s="7" t="n">
         <f aca="false">P8+P16</f>
-        <v>589687.5</v>
+        <v>559937.5</v>
       </c>
       <c r="Q24" s="7" t="n">
         <f aca="false">Q8+Q16</f>
-        <v>624375</v>
+        <v>592875</v>
       </c>
       <c r="R24" s="7" t="n">
         <f aca="false">R8+R16</f>
-        <v>624375</v>
+        <v>592875</v>
       </c>
       <c r="S24" s="7" t="n">
         <f aca="false">S8+S16</f>
-        <v>659062.5</v>
+        <v>625812.5</v>
       </c>
       <c r="T24" s="7" t="n">
         <f aca="false">T8+T16</f>
-        <v>693750</v>
+        <v>658750</v>
       </c>
       <c r="U24" s="7" t="n">
         <f aca="false">U8+U16</f>
-        <v>659062.5</v>
+        <v>625812.5</v>
       </c>
       <c r="V24" s="7" t="n">
         <f aca="false">V8+V16</f>
-        <v>624375</v>
+        <v>592875</v>
       </c>
       <c r="W24" s="7" t="n">
         <f aca="false">W8+W16</f>
-        <v>693750</v>
+        <v>658750</v>
       </c>
       <c r="X24" s="7" t="n">
         <f aca="false">X8+X16</f>
-        <v>728437.5</v>
+        <v>691687.5</v>
       </c>
       <c r="Y24" s="7" t="n">
         <f aca="false">Y8+Y16</f>
-        <v>901875</v>
+        <v>856375</v>
       </c>
       <c r="Z24" s="7" t="n">
         <f aca="false">Z8+Z16</f>
-        <v>936562.5</v>
+        <v>889312.5</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9539,99 +9539,99 @@
       </c>
       <c r="C26" s="5" t="n">
         <f aca="false">C10+C18</f>
-        <v>43807.2916666667</v>
+        <v>69491.4583333333</v>
       </c>
       <c r="D26" s="5" t="n">
         <f aca="false">D10+D18</f>
-        <v>43807.2916666667</v>
+        <v>69491.4583333333</v>
       </c>
       <c r="E26" s="5" t="n">
         <f aca="false">E10+E18</f>
-        <v>12781.25</v>
+        <v>39976.2499999999</v>
       </c>
       <c r="F26" s="5" t="n">
         <f aca="false">F10+F18</f>
-        <v>66739.5833333334</v>
+        <v>93934.5833333333</v>
       </c>
       <c r="G26" s="5" t="n">
         <f aca="false">G10+G18</f>
-        <v>35713.5416666667</v>
+        <v>64419.375</v>
       </c>
       <c r="H26" s="5" t="n">
         <f aca="false">H10+H18</f>
-        <v>58645.8333333334</v>
+        <v>88862.5</v>
       </c>
       <c r="I26" s="5" t="n">
         <f aca="false">I10+I18</f>
-        <v>143630.208333333</v>
+        <v>172336.041666667</v>
       </c>
       <c r="J26" s="5" t="n">
         <f aca="false">J10+J18</f>
-        <v>120697.916666667</v>
+        <v>147892.916666667</v>
       </c>
       <c r="K26" s="5" t="n">
         <f aca="false">K10+K18</f>
-        <v>4687.50000000006</v>
+        <v>34904.1666666667</v>
       </c>
       <c r="L26" s="5" t="n">
         <f aca="false">L10+L18</f>
-        <v>81578.125</v>
+        <v>113305.625</v>
       </c>
       <c r="M26" s="5" t="n">
         <f aca="false">M10+M18</f>
-        <v>-19593.7499999999</v>
+        <v>19687.9166666667</v>
       </c>
       <c r="N26" s="5" t="n">
         <f aca="false">N10+N18</f>
-        <v>219171.875</v>
+        <v>259964.375</v>
       </c>
       <c r="O26" s="5" t="n">
         <f aca="false">O10+O18</f>
-        <v>487784.375</v>
+        <v>517534.375</v>
       </c>
       <c r="P26" s="5" t="n">
         <f aca="false">P10+P18</f>
-        <v>93409.3750000002</v>
+        <v>123159.375</v>
       </c>
       <c r="Q26" s="5" t="n">
         <f aca="false">Q10+Q18</f>
-        <v>57471.8750000002</v>
+        <v>88971.8750000001</v>
       </c>
       <c r="R26" s="5" t="n">
         <f aca="false">R10+R18</f>
-        <v>119971.875</v>
+        <v>151471.875</v>
       </c>
       <c r="S26" s="5" t="n">
         <f aca="false">S10+S18</f>
-        <v>84034.3750000002</v>
+        <v>117284.375</v>
       </c>
       <c r="T26" s="5" t="n">
         <f aca="false">T10+T18</f>
-        <v>110596.875</v>
+        <v>145596.875</v>
       </c>
       <c r="U26" s="5" t="n">
         <f aca="false">U10+U18</f>
-        <v>209034.375</v>
+        <v>242284.375</v>
       </c>
       <c r="V26" s="5" t="n">
         <f aca="false">V10+V18</f>
-        <v>182471.875</v>
+        <v>213971.875</v>
       </c>
       <c r="W26" s="5" t="n">
         <f aca="false">W10+W18</f>
-        <v>48096.8750000002</v>
+        <v>83096.8750000001</v>
       </c>
       <c r="X26" s="5" t="n">
         <f aca="false">X10+X18</f>
-        <v>137159.375</v>
+        <v>173909.375</v>
       </c>
       <c r="Y26" s="5" t="n">
         <f aca="false">Y10+Y18</f>
-        <v>19971.8750000002</v>
+        <v>65471.8750000001</v>
       </c>
       <c r="Z26" s="5" t="n">
         <f aca="false">Z10+Z18</f>
-        <v>296534.375</v>
+        <v>343784.375</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9640,99 +9640,99 @@
       </c>
       <c r="C27" s="5" t="n">
         <f aca="false">C11+C19</f>
-        <v>4443807.29166667</v>
+        <v>4469491.45833333</v>
       </c>
       <c r="D27" s="5" t="n">
         <f aca="false">D11+D19</f>
-        <v>4487614.58333333</v>
+        <v>4538982.91666667</v>
       </c>
       <c r="E27" s="5" t="n">
         <f aca="false">E11+E19</f>
-        <v>4500395.83333333</v>
+        <v>4578959.16666667</v>
       </c>
       <c r="F27" s="5" t="n">
         <f aca="false">F11+F19</f>
-        <v>4567135.41666667</v>
+        <v>4672893.75</v>
       </c>
       <c r="G27" s="5" t="n">
         <f aca="false">G11+G19</f>
-        <v>4602848.95833333</v>
+        <v>4737313.125</v>
       </c>
       <c r="H27" s="5" t="n">
         <f aca="false">H11+H19</f>
-        <v>4661494.79166667</v>
+        <v>4826175.625</v>
       </c>
       <c r="I27" s="5" t="n">
         <f aca="false">I11+I19</f>
-        <v>4805125</v>
+        <v>4998511.66666667</v>
       </c>
       <c r="J27" s="5" t="n">
         <f aca="false">J11+J19</f>
-        <v>4925822.91666667</v>
+        <v>5146404.58333333</v>
       </c>
       <c r="K27" s="5" t="n">
         <f aca="false">K11+K19</f>
-        <v>4930510.41666667</v>
+        <v>5181308.75</v>
       </c>
       <c r="L27" s="5" t="n">
         <f aca="false">L11+L19</f>
-        <v>5012088.54166667</v>
+        <v>5294614.375</v>
       </c>
       <c r="M27" s="5" t="n">
         <f aca="false">M11+M19</f>
-        <v>4992494.79166667</v>
+        <v>5314302.29166666</v>
       </c>
       <c r="N27" s="5" t="n">
         <f aca="false">N11+N19</f>
-        <v>5211666.66666667</v>
+        <v>5574266.66666666</v>
       </c>
       <c r="O27" s="5" t="n">
         <f aca="false">O11+O19</f>
-        <v>5699451.04166667</v>
+        <v>6091801.04166666</v>
       </c>
       <c r="P27" s="5" t="n">
         <f aca="false">P11+P19</f>
-        <v>5792860.41666667</v>
+        <v>6214960.41666666</v>
       </c>
       <c r="Q27" s="5" t="n">
         <f aca="false">Q11+Q19</f>
-        <v>5850332.29166667</v>
+        <v>6303932.29166666</v>
       </c>
       <c r="R27" s="5" t="n">
         <f aca="false">R11+R19</f>
-        <v>5970304.16666667</v>
+        <v>6455404.16666666</v>
       </c>
       <c r="S27" s="5" t="n">
         <f aca="false">S11+S19</f>
-        <v>6054338.54166667</v>
+        <v>6572688.54166666</v>
       </c>
       <c r="T27" s="5" t="n">
         <f aca="false">T11+T19</f>
-        <v>6164935.41666667</v>
+        <v>6718285.41666666</v>
       </c>
       <c r="U27" s="5" t="n">
         <f aca="false">U11+U19</f>
-        <v>6373969.79166667</v>
+        <v>6960569.79166666</v>
       </c>
       <c r="V27" s="5" t="n">
         <f aca="false">V11+V19</f>
-        <v>6556441.66666667</v>
+        <v>7174541.66666666</v>
       </c>
       <c r="W27" s="5" t="n">
         <f aca="false">W11+W19</f>
-        <v>6604538.54166667</v>
+        <v>7257638.54166666</v>
       </c>
       <c r="X27" s="5" t="n">
         <f aca="false">X11+X19</f>
-        <v>6741697.91666667</v>
+        <v>7431547.91666666</v>
       </c>
       <c r="Y27" s="5" t="n">
         <f aca="false">Y11+Y19</f>
-        <v>6761669.79166667</v>
+        <v>7497019.79166666</v>
       </c>
       <c r="Z27" s="5" t="n">
         <f aca="false">Z11+Z19</f>
-        <v>7058204.16666667</v>
+        <v>7840804.16666666</v>
       </c>
     </row>
   </sheetData>

--- a/Lumin Light Financial Model - 2025-2026.xlsx
+++ b/Lumin Light Financial Model - 2025-2026.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="131">
   <si>
     <t xml:space="preserve">Lumin Light — 2025-2026 Financial Model — Assumptions</t>
   </si>
@@ -151,6 +151,24 @@
   </si>
   <si>
     <t xml:space="preserve">Check (sums to 12.00 if evenly weighted; doesn't have to — formulas normalize either way)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QUARTERLY REVENUE TARGET SPLIT — 2026 (% of Annual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check (must sum to 100%)</t>
   </si>
   <si>
     <t xml:space="preserve">AR Collection Lag (months) — institutional buyers pay slowly; matches the Python actuals model</t>
@@ -527,7 +545,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -565,6 +583,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -776,7 +798,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:N39"/>
+  <dimension ref="B1:N44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -1123,31 +1145,73 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C35" s="10" t="n">
-        <v>1</v>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="3" t="s">
-        <v>43</v>
+      <c r="C37" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <f aca="false">SUM(C37:F37)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="4" t="n">
+      <c r="C43" s="4" t="n">
         <v>2200000</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="0" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="4" t="n">
+      <c r="C44" s="4" t="n">
         <v>2200000</v>
       </c>
     </row>
@@ -1178,31 +1242,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>6</v>
@@ -1217,7 +1281,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>6</v>
@@ -1232,7 +1296,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>6</v>
@@ -1247,7 +1311,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>6</v>
@@ -1262,7 +1326,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>7</v>
@@ -1277,7 +1341,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>6</v>
@@ -1292,7 +1356,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>6</v>
@@ -1307,7 +1371,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>7</v>
@@ -1322,7 +1386,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>6</v>
@@ -1337,7 +1401,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>6</v>
@@ -1352,7 +1416,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>6</v>
@@ -1367,7 +1431,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>7</v>
@@ -1382,7 +1446,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>6</v>
@@ -1397,7 +1461,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>7</v>
@@ -1412,7 +1476,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>6</v>
@@ -1427,7 +1491,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>7</v>
@@ -1442,7 +1506,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>7</v>
@@ -1457,7 +1521,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>6</v>
@@ -1472,7 +1536,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>7</v>
@@ -1487,7 +1551,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>6</v>
@@ -1502,7 +1566,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D26" s="5" t="n">
         <f aca="false">SUM(D5:D24)</f>
@@ -1515,7 +1579,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D27" s="7" t="n">
         <f aca="false">SUMIF(C5:C24,"Lumin Light USA",D5:D24)</f>
@@ -1528,7 +1592,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D28" s="7" t="n">
         <f aca="false">SUMIF(C5:C24,"Lumin Light Nigeria",D5:D24)</f>
@@ -1565,20 +1629,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -1617,7 +1681,7 @@
         <v>40</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>29</v>
@@ -1658,57 +1722,57 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C6" s="5" t="n">
         <f aca="false">SUM(D6:O6)</f>
         <v>7850000</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$C$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>556041.666666667</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$D$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>556041.666666667</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$E$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>588750</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$F$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>588750</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$G$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>621458.333333333</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$H$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>654166.666666667</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$I$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>621458.333333333</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$J$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>588750</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$K$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>654166.666666667</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$L$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>686875</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$M$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>850416.666666667</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="12" t="n">
         <f aca="false">Assumptions!$C$6*Assumptions!$N$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>883125</v>
       </c>
@@ -1716,108 +1780,108 @@
         <f aca="false">SUM(Q6:AB6)</f>
         <v>9000000</v>
       </c>
-      <c r="Q6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$C$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>637500</v>
-      </c>
-      <c r="R6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$D$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>637500</v>
-      </c>
-      <c r="S6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$E$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>675000</v>
-      </c>
-      <c r="T6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$F$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>675000</v>
-      </c>
-      <c r="U6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$G$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>712500</v>
-      </c>
-      <c r="V6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$H$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>750000</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$I$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>712500</v>
-      </c>
-      <c r="X6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$J$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>675000</v>
-      </c>
-      <c r="Y6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$K$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>750000</v>
-      </c>
-      <c r="Z6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$L$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>787500</v>
-      </c>
-      <c r="AA6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$M$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>975000</v>
-      </c>
-      <c r="AB6" s="11" t="n">
-        <f aca="false">Assumptions!$D$6*Assumptions!$N$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>1012500</v>
+      <c r="Q6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$C$37*Assumptions!$C$32/SUM(Assumptions!$C$32:$E$32)</f>
+        <v>294230.769230769</v>
+      </c>
+      <c r="R6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$C$37*Assumptions!$D$32/SUM(Assumptions!$C$32:$E$32)</f>
+        <v>294230.769230769</v>
+      </c>
+      <c r="S6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$C$37*Assumptions!$E$32/SUM(Assumptions!$C$32:$E$32)</f>
+        <v>311538.461538462</v>
+      </c>
+      <c r="T6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$D$37*Assumptions!$F$32/SUM(Assumptions!$F$32:$H$32)</f>
+        <v>568421.052631579</v>
+      </c>
+      <c r="U6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$D$37*Assumptions!$G$32/SUM(Assumptions!$F$32:$H$32)</f>
+        <v>600000</v>
+      </c>
+      <c r="V6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$D$37*Assumptions!$H$32/SUM(Assumptions!$F$32:$H$32)</f>
+        <v>631578.947368421</v>
+      </c>
+      <c r="W6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$E$37*Assumptions!$I$32/SUM(Assumptions!$I$32:$K$32)</f>
+        <v>900000</v>
+      </c>
+      <c r="X6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$E$37*Assumptions!$J$32/SUM(Assumptions!$I$32:$K$32)</f>
+        <v>852631.578947368</v>
+      </c>
+      <c r="Y6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$E$37*Assumptions!$K$32/SUM(Assumptions!$I$32:$K$32)</f>
+        <v>947368.421052632</v>
+      </c>
+      <c r="Z6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$F$37*Assumptions!$L$32/SUM(Assumptions!$L$32:$N$32)</f>
+        <v>1021621.62162162</v>
+      </c>
+      <c r="AA6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$F$37*Assumptions!$M$32/SUM(Assumptions!$L$32:$N$32)</f>
+        <v>1264864.86486486</v>
+      </c>
+      <c r="AB6" s="12" t="n">
+        <f aca="false">Assumptions!$D$6*Assumptions!$F$37*Assumptions!$N$32/SUM(Assumptions!$L$32:$N$32)</f>
+        <v>1313513.51351351</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">SUM(D9:O9)</f>
         <v>4136950</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <f aca="false">D6*(1-Assumptions!$C$11)</f>
         <v>293033.958333333</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <f aca="false">E6*(1-Assumptions!$C$11)</f>
         <v>293033.958333333</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <f aca="false">F6*(1-Assumptions!$C$11)</f>
         <v>310271.25</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="12" t="n">
         <f aca="false">G6*(1-Assumptions!$C$11)</f>
         <v>310271.25</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="12" t="n">
         <f aca="false">H6*(1-Assumptions!$C$11)</f>
         <v>327508.541666667</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="12" t="n">
         <f aca="false">I6*(1-Assumptions!$C$11)</f>
         <v>344745.833333333</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="12" t="n">
         <f aca="false">J6*(1-Assumptions!$C$11)</f>
         <v>327508.541666667</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="12" t="n">
         <f aca="false">K6*(1-Assumptions!$C$11)</f>
         <v>310271.25</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="12" t="n">
         <f aca="false">L6*(1-Assumptions!$C$11)</f>
         <v>344745.833333333</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="12" t="n">
         <f aca="false">M6*(1-Assumptions!$C$11)</f>
         <v>361983.125</v>
       </c>
-      <c r="N9" s="11" t="n">
+      <c r="N9" s="12" t="n">
         <f aca="false">N6*(1-Assumptions!$C$11)</f>
         <v>448169.583333333</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="12" t="n">
         <f aca="false">O6*(1-Assumptions!$C$11)</f>
         <v>465406.875</v>
       </c>
@@ -1825,58 +1889,58 @@
         <f aca="false">SUM(Q9:AB9)</f>
         <v>4743000</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="12" t="n">
         <f aca="false">Q6*(1-Assumptions!$C$11)</f>
-        <v>335962.5</v>
-      </c>
-      <c r="R9" s="11" t="n">
+        <v>155059.615384615</v>
+      </c>
+      <c r="R9" s="12" t="n">
         <f aca="false">R6*(1-Assumptions!$C$11)</f>
-        <v>335962.5</v>
-      </c>
-      <c r="S9" s="11" t="n">
+        <v>155059.615384615</v>
+      </c>
+      <c r="S9" s="12" t="n">
         <f aca="false">S6*(1-Assumptions!$C$11)</f>
-        <v>355725</v>
-      </c>
-      <c r="T9" s="11" t="n">
+        <v>164180.769230769</v>
+      </c>
+      <c r="T9" s="12" t="n">
         <f aca="false">T6*(1-Assumptions!$C$11)</f>
-        <v>355725</v>
-      </c>
-      <c r="U9" s="11" t="n">
+        <v>299557.894736842</v>
+      </c>
+      <c r="U9" s="12" t="n">
         <f aca="false">U6*(1-Assumptions!$C$11)</f>
-        <v>375487.5</v>
-      </c>
-      <c r="V9" s="11" t="n">
+        <v>316200</v>
+      </c>
+      <c r="V9" s="12" t="n">
         <f aca="false">V6*(1-Assumptions!$C$11)</f>
-        <v>395250</v>
-      </c>
-      <c r="W9" s="11" t="n">
+        <v>332842.105263158</v>
+      </c>
+      <c r="W9" s="12" t="n">
         <f aca="false">W6*(1-Assumptions!$C$11)</f>
-        <v>375487.5</v>
-      </c>
-      <c r="X9" s="11" t="n">
+        <v>474300</v>
+      </c>
+      <c r="X9" s="12" t="n">
         <f aca="false">X6*(1-Assumptions!$C$11)</f>
-        <v>355725</v>
-      </c>
-      <c r="Y9" s="11" t="n">
+        <v>449336.842105263</v>
+      </c>
+      <c r="Y9" s="12" t="n">
         <f aca="false">Y6*(1-Assumptions!$C$11)</f>
-        <v>395250</v>
-      </c>
-      <c r="Z9" s="11" t="n">
+        <v>499263.157894737</v>
+      </c>
+      <c r="Z9" s="12" t="n">
         <f aca="false">Z6*(1-Assumptions!$C$11)</f>
-        <v>415012.5</v>
-      </c>
-      <c r="AA9" s="11" t="n">
+        <v>538394.594594595</v>
+      </c>
+      <c r="AA9" s="12" t="n">
         <f aca="false">AA6*(1-Assumptions!$C$11)</f>
-        <v>513825</v>
-      </c>
-      <c r="AB9" s="11" t="n">
+        <v>666583.783783784</v>
+      </c>
+      <c r="AB9" s="12" t="n">
         <f aca="false">AB6*(1-Assumptions!$C$11)</f>
-        <v>533587.5</v>
+        <v>692221.621621622</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(D11:O11)</f>
@@ -1936,220 +2000,220 @@
       </c>
       <c r="Q11" s="7" t="n">
         <f aca="false">Q6-Q9</f>
-        <v>301537.5</v>
+        <v>139171.153846154</v>
       </c>
       <c r="R11" s="7" t="n">
         <f aca="false">R6-R9</f>
-        <v>301537.5</v>
+        <v>139171.153846154</v>
       </c>
       <c r="S11" s="7" t="n">
         <f aca="false">S6-S9</f>
-        <v>319275</v>
+        <v>147357.692307692</v>
       </c>
       <c r="T11" s="7" t="n">
         <f aca="false">T6-T9</f>
-        <v>319275</v>
+        <v>268863.157894737</v>
       </c>
       <c r="U11" s="7" t="n">
         <f aca="false">U6-U9</f>
-        <v>337012.5</v>
+        <v>283800</v>
       </c>
       <c r="V11" s="7" t="n">
         <f aca="false">V6-V9</f>
-        <v>354750</v>
+        <v>298736.842105263</v>
       </c>
       <c r="W11" s="7" t="n">
         <f aca="false">W6-W9</f>
-        <v>337012.5</v>
+        <v>425700</v>
       </c>
       <c r="X11" s="7" t="n">
         <f aca="false">X6-X9</f>
-        <v>319275</v>
+        <v>403294.736842105</v>
       </c>
       <c r="Y11" s="7" t="n">
         <f aca="false">Y6-Y9</f>
-        <v>354750</v>
+        <v>448105.263157895</v>
       </c>
       <c r="Z11" s="7" t="n">
         <f aca="false">Z6-Z9</f>
-        <v>372487.5</v>
+        <v>483227.027027027</v>
       </c>
       <c r="AA11" s="7" t="n">
         <f aca="false">AA6-AA9</f>
-        <v>461175</v>
+        <v>598281.081081081</v>
       </c>
       <c r="AB11" s="7" t="n">
         <f aca="false">AB6-AB9</f>
-        <v>478912.5</v>
+        <v>621291.891891892</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="13" t="n">
+      <c r="B12" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="14" t="n">
         <f aca="false">IF(C6=0,0,C11/C6)</f>
         <v>0.473</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <f aca="false">IF(D6=0,0,D11/D6)</f>
         <v>0.473</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <f aca="false">IF(E6=0,0,E11/E6)</f>
         <v>0.473</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="14" t="n">
         <f aca="false">IF(F6=0,0,F11/F6)</f>
         <v>0.473</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="14" t="n">
         <f aca="false">IF(G6=0,0,G11/G6)</f>
         <v>0.473</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="14" t="n">
         <f aca="false">IF(H6=0,0,H11/H6)</f>
         <v>0.473</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="14" t="n">
         <f aca="false">IF(I6=0,0,I11/I6)</f>
         <v>0.473</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="14" t="n">
         <f aca="false">IF(J6=0,0,J11/J6)</f>
         <v>0.473</v>
       </c>
-      <c r="K12" s="13" t="n">
+      <c r="K12" s="14" t="n">
         <f aca="false">IF(K6=0,0,K11/K6)</f>
         <v>0.473</v>
       </c>
-      <c r="L12" s="13" t="n">
+      <c r="L12" s="14" t="n">
         <f aca="false">IF(L6=0,0,L11/L6)</f>
         <v>0.473</v>
       </c>
-      <c r="M12" s="13" t="n">
+      <c r="M12" s="14" t="n">
         <f aca="false">IF(M6=0,0,M11/M6)</f>
         <v>0.473</v>
       </c>
-      <c r="N12" s="13" t="n">
+      <c r="N12" s="14" t="n">
         <f aca="false">IF(N6=0,0,N11/N6)</f>
         <v>0.473</v>
       </c>
-      <c r="O12" s="13" t="n">
+      <c r="O12" s="14" t="n">
         <f aca="false">IF(O6=0,0,O11/O6)</f>
         <v>0.473</v>
       </c>
-      <c r="P12" s="13" t="n">
+      <c r="P12" s="14" t="n">
         <f aca="false">IF(P6=0,0,P11/P6)</f>
         <v>0.473</v>
       </c>
-      <c r="Q12" s="13" t="n">
+      <c r="Q12" s="14" t="n">
         <f aca="false">IF(Q6=0,0,Q11/Q6)</f>
         <v>0.473</v>
       </c>
-      <c r="R12" s="13" t="n">
+      <c r="R12" s="14" t="n">
         <f aca="false">IF(R6=0,0,R11/R6)</f>
         <v>0.473</v>
       </c>
-      <c r="S12" s="13" t="n">
+      <c r="S12" s="14" t="n">
         <f aca="false">IF(S6=0,0,S11/S6)</f>
         <v>0.473</v>
       </c>
-      <c r="T12" s="13" t="n">
+      <c r="T12" s="14" t="n">
         <f aca="false">IF(T6=0,0,T11/T6)</f>
         <v>0.473</v>
       </c>
-      <c r="U12" s="13" t="n">
+      <c r="U12" s="14" t="n">
         <f aca="false">IF(U6=0,0,U11/U6)</f>
         <v>0.473</v>
       </c>
-      <c r="V12" s="13" t="n">
+      <c r="V12" s="14" t="n">
         <f aca="false">IF(V6=0,0,V11/V6)</f>
         <v>0.473</v>
       </c>
-      <c r="W12" s="13" t="n">
+      <c r="W12" s="14" t="n">
         <f aca="false">IF(W6=0,0,W11/W6)</f>
         <v>0.473</v>
       </c>
-      <c r="X12" s="13" t="n">
+      <c r="X12" s="14" t="n">
         <f aca="false">IF(X6=0,0,X11/X6)</f>
         <v>0.473</v>
       </c>
-      <c r="Y12" s="13" t="n">
+      <c r="Y12" s="14" t="n">
         <f aca="false">IF(Y6=0,0,Y11/Y6)</f>
         <v>0.473</v>
       </c>
-      <c r="Z12" s="13" t="n">
+      <c r="Z12" s="14" t="n">
         <f aca="false">IF(Z6=0,0,Z11/Z6)</f>
         <v>0.473</v>
       </c>
-      <c r="AA12" s="13" t="n">
+      <c r="AA12" s="14" t="n">
         <f aca="false">IF(AA6=0,0,AA11/AA6)</f>
         <v>0.473</v>
       </c>
-      <c r="AB12" s="13" t="n">
+      <c r="AB12" s="14" t="n">
         <f aca="false">IF(AB6=0,0,AB11/AB6)</f>
         <v>0.473</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">SUM(D15:O15)</f>
         <v>2106250</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="H15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="I15" s="11" t="n">
+      <c r="I15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="N15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="O15" s="12" t="n">
         <f aca="false">Headcount!$D$27*(1+Assumptions!$C$15)/12</f>
         <v>175520.833333333</v>
       </c>
@@ -2157,108 +2221,108 @@
         <f aca="false">SUM(Q15:AB15)</f>
         <v>2179968.75</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="S15" s="11" t="n">
+      <c r="S15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="T15" s="11" t="n">
+      <c r="T15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="U15" s="11" t="n">
+      <c r="U15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="V15" s="11" t="n">
+      <c r="V15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="W15" s="11" t="n">
+      <c r="W15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="X15" s="11" t="n">
+      <c r="X15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="Y15" s="11" t="n">
+      <c r="Y15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="Z15" s="11" t="n">
+      <c r="Z15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="AA15" s="11" t="n">
+      <c r="AA15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
-      <c r="AB15" s="11" t="n">
+      <c r="AB15" s="12" t="n">
         <f aca="false">Headcount!$E$27*(1+Assumptions!$C$15)/12</f>
         <v>181664.0625</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">SUM(D16:O16)</f>
         <v>157000</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <f aca="false">D6*Assumptions!$C$16</f>
         <v>11120.8333333333</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <f aca="false">E6*Assumptions!$C$16</f>
         <v>11120.8333333333</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <f aca="false">F6*Assumptions!$C$16</f>
         <v>11775</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="12" t="n">
         <f aca="false">G6*Assumptions!$C$16</f>
         <v>11775</v>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="12" t="n">
         <f aca="false">H6*Assumptions!$C$16</f>
         <v>12429.1666666667</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" s="12" t="n">
         <f aca="false">I6*Assumptions!$C$16</f>
         <v>13083.3333333333</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="12" t="n">
         <f aca="false">J6*Assumptions!$C$16</f>
         <v>12429.1666666667</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="12" t="n">
         <f aca="false">K6*Assumptions!$C$16</f>
         <v>11775</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" s="12" t="n">
         <f aca="false">L6*Assumptions!$C$16</f>
         <v>13083.3333333333</v>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="M16" s="12" t="n">
         <f aca="false">M6*Assumptions!$C$16</f>
         <v>13737.5</v>
       </c>
-      <c r="N16" s="11" t="n">
+      <c r="N16" s="12" t="n">
         <f aca="false">N6*Assumptions!$C$16</f>
         <v>17008.3333333333</v>
       </c>
-      <c r="O16" s="11" t="n">
+      <c r="O16" s="12" t="n">
         <f aca="false">O6*Assumptions!$C$16</f>
         <v>17662.5</v>
       </c>
@@ -2266,53 +2330,53 @@
         <f aca="false">SUM(Q16:AB16)</f>
         <v>180000</v>
       </c>
-      <c r="Q16" s="11" t="n">
+      <c r="Q16" s="12" t="n">
         <f aca="false">Q6*Assumptions!$C$16</f>
-        <v>12750</v>
-      </c>
-      <c r="R16" s="11" t="n">
+        <v>5884.61538461539</v>
+      </c>
+      <c r="R16" s="12" t="n">
         <f aca="false">R6*Assumptions!$C$16</f>
-        <v>12750</v>
-      </c>
-      <c r="S16" s="11" t="n">
+        <v>5884.61538461539</v>
+      </c>
+      <c r="S16" s="12" t="n">
         <f aca="false">S6*Assumptions!$C$16</f>
-        <v>13500</v>
-      </c>
-      <c r="T16" s="11" t="n">
+        <v>6230.76923076923</v>
+      </c>
+      <c r="T16" s="12" t="n">
         <f aca="false">T6*Assumptions!$C$16</f>
-        <v>13500</v>
-      </c>
-      <c r="U16" s="11" t="n">
+        <v>11368.4210526316</v>
+      </c>
+      <c r="U16" s="12" t="n">
         <f aca="false">U6*Assumptions!$C$16</f>
-        <v>14250</v>
-      </c>
-      <c r="V16" s="11" t="n">
+        <v>12000</v>
+      </c>
+      <c r="V16" s="12" t="n">
         <f aca="false">V6*Assumptions!$C$16</f>
-        <v>15000</v>
-      </c>
-      <c r="W16" s="11" t="n">
+        <v>12631.5789473684</v>
+      </c>
+      <c r="W16" s="12" t="n">
         <f aca="false">W6*Assumptions!$C$16</f>
-        <v>14250</v>
-      </c>
-      <c r="X16" s="11" t="n">
+        <v>18000</v>
+      </c>
+      <c r="X16" s="12" t="n">
         <f aca="false">X6*Assumptions!$C$16</f>
-        <v>13500</v>
-      </c>
-      <c r="Y16" s="11" t="n">
+        <v>17052.6315789474</v>
+      </c>
+      <c r="Y16" s="12" t="n">
         <f aca="false">Y6*Assumptions!$C$16</f>
-        <v>15000</v>
-      </c>
-      <c r="Z16" s="11" t="n">
+        <v>18947.3684210526</v>
+      </c>
+      <c r="Z16" s="12" t="n">
         <f aca="false">Z6*Assumptions!$C$16</f>
-        <v>15750</v>
-      </c>
-      <c r="AA16" s="11" t="n">
+        <v>20432.4324324324</v>
+      </c>
+      <c r="AA16" s="12" t="n">
         <f aca="false">AA6*Assumptions!$C$16</f>
-        <v>19500</v>
-      </c>
-      <c r="AB16" s="11" t="n">
+        <v>25297.2972972973</v>
+      </c>
+      <c r="AB16" s="12" t="n">
         <f aca="false">AB6*Assumptions!$C$16</f>
-        <v>20250</v>
+        <v>26270.2702702703</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2323,51 +2387,51 @@
         <f aca="false">SUM(D17:O17)</f>
         <v>150000</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="I17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="N17" s="11" t="n">
+      <c r="N17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="O17" s="12" t="n">
         <f aca="false">Assumptions!$C$23/12</f>
         <v>12500</v>
       </c>
@@ -2375,51 +2439,51 @@
         <f aca="false">SUM(Q17:AB17)</f>
         <v>155250</v>
       </c>
-      <c r="Q17" s="11" t="n">
+      <c r="Q17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="R17" s="11" t="n">
+      <c r="R17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="S17" s="11" t="n">
+      <c r="S17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="T17" s="11" t="n">
+      <c r="T17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="U17" s="11" t="n">
+      <c r="U17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="V17" s="11" t="n">
+      <c r="V17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="W17" s="11" t="n">
+      <c r="W17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="X17" s="11" t="n">
+      <c r="X17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="Y17" s="11" t="n">
+      <c r="Y17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="Z17" s="11" t="n">
+      <c r="Z17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="AA17" s="11" t="n">
+      <c r="AA17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
-      <c r="AB17" s="11" t="n">
+      <c r="AB17" s="12" t="n">
         <f aca="false">Assumptions!$C$23*(1+Assumptions!$C$17)/12</f>
         <v>12937.5</v>
       </c>
@@ -2432,51 +2496,51 @@
         <f aca="false">SUM(D18:O18)</f>
         <v>230000</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="H18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="K18" s="11" t="n">
+      <c r="K18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="N18" s="11" t="n">
+      <c r="N18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
-      <c r="O18" s="11" t="n">
+      <c r="O18" s="12" t="n">
         <f aca="false">Assumptions!$C$24/12</f>
         <v>19166.6666666667</v>
       </c>
@@ -2484,51 +2548,51 @@
         <f aca="false">SUM(Q18:AB18)</f>
         <v>238050</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="S18" s="11" t="n">
+      <c r="S18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="T18" s="11" t="n">
+      <c r="T18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="U18" s="11" t="n">
+      <c r="U18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="V18" s="11" t="n">
+      <c r="V18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="W18" s="11" t="n">
+      <c r="W18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="X18" s="11" t="n">
+      <c r="X18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="Y18" s="11" t="n">
+      <c r="Y18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="Z18" s="11" t="n">
+      <c r="Z18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="AA18" s="11" t="n">
+      <c r="AA18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
-      <c r="AB18" s="11" t="n">
+      <c r="AB18" s="12" t="n">
         <f aca="false">Assumptions!$C$24*(1+Assumptions!$C$17)/12</f>
         <v>19837.5</v>
       </c>
@@ -2541,51 +2605,51 @@
         <f aca="false">SUM(D19:O19)</f>
         <v>140000</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="N19" s="11" t="n">
+      <c r="N19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="O19" s="12" t="n">
         <f aca="false">Assumptions!$C$25/12</f>
         <v>11666.6666666667</v>
       </c>
@@ -2593,51 +2657,51 @@
         <f aca="false">SUM(Q19:AB19)</f>
         <v>144900</v>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="S19" s="11" t="n">
+      <c r="S19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="T19" s="11" t="n">
+      <c r="T19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="U19" s="11" t="n">
+      <c r="U19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="W19" s="11" t="n">
+      <c r="W19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="X19" s="11" t="n">
+      <c r="X19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="Y19" s="11" t="n">
+      <c r="Y19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="Z19" s="11" t="n">
+      <c r="Z19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="AA19" s="11" t="n">
+      <c r="AA19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="AB19" s="11" t="n">
+      <c r="AB19" s="12" t="n">
         <f aca="false">Assumptions!$C$25*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
@@ -2650,51 +2714,51 @@
         <f aca="false">SUM(D20:O20)</f>
         <v>90000</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="H20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="K20" s="11" t="n">
+      <c r="K20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="L20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="M20" s="11" t="n">
+      <c r="M20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="N20" s="11" t="n">
+      <c r="N20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
-      <c r="O20" s="11" t="n">
+      <c r="O20" s="12" t="n">
         <f aca="false">Assumptions!$C$26/12</f>
         <v>7500</v>
       </c>
@@ -2702,51 +2766,51 @@
         <f aca="false">SUM(Q20:AB20)</f>
         <v>93150</v>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="S20" s="11" t="n">
+      <c r="S20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="T20" s="11" t="n">
+      <c r="T20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="U20" s="11" t="n">
+      <c r="U20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="V20" s="11" t="n">
+      <c r="V20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="W20" s="11" t="n">
+      <c r="W20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="X20" s="11" t="n">
+      <c r="X20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="Y20" s="11" t="n">
+      <c r="Y20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="Z20" s="11" t="n">
+      <c r="Z20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="AA20" s="11" t="n">
+      <c r="AA20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="AB20" s="11" t="n">
+      <c r="AB20" s="12" t="n">
         <f aca="false">Assumptions!$C$26*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
@@ -2759,51 +2823,51 @@
         <f aca="false">SUM(D21:O21)</f>
         <v>180000</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="H21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="N21" s="11" t="n">
+      <c r="N21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
-      <c r="O21" s="11" t="n">
+      <c r="O21" s="12" t="n">
         <f aca="false">Assumptions!$C$27/12</f>
         <v>15000</v>
       </c>
@@ -2811,51 +2875,51 @@
         <f aca="false">SUM(Q21:AB21)</f>
         <v>186300</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="S21" s="11" t="n">
+      <c r="S21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="T21" s="11" t="n">
+      <c r="T21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="U21" s="11" t="n">
+      <c r="U21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="V21" s="11" t="n">
+      <c r="V21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="W21" s="11" t="n">
+      <c r="W21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="X21" s="11" t="n">
+      <c r="X21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="Y21" s="11" t="n">
+      <c r="Y21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="Z21" s="11" t="n">
+      <c r="Z21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="AA21" s="11" t="n">
+      <c r="AA21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
-      <c r="AB21" s="11" t="n">
+      <c r="AB21" s="12" t="n">
         <f aca="false">Assumptions!$C$27*(1+Assumptions!$C$17)/12</f>
         <v>15525</v>
       </c>
@@ -2868,51 +2932,51 @@
         <f aca="false">SUM(D22:O22)</f>
         <v>140000</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="H22" s="11" t="n">
+      <c r="H22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="K22" s="11" t="n">
+      <c r="K22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="M22" s="11" t="n">
+      <c r="M22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="N22" s="11" t="n">
+      <c r="N22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="O22" s="11" t="n">
+      <c r="O22" s="12" t="n">
         <f aca="false">Assumptions!$C$28/12</f>
         <v>11666.6666666667</v>
       </c>
@@ -2920,58 +2984,58 @@
         <f aca="false">SUM(Q22:AB22)</f>
         <v>144900</v>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="S22" s="11" t="n">
+      <c r="S22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="T22" s="11" t="n">
+      <c r="T22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="U22" s="11" t="n">
+      <c r="U22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="V22" s="11" t="n">
+      <c r="V22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="W22" s="11" t="n">
+      <c r="W22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="X22" s="11" t="n">
+      <c r="X22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="Y22" s="11" t="n">
+      <c r="Y22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="Z22" s="11" t="n">
+      <c r="Z22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="AA22" s="11" t="n">
+      <c r="AA22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="AB22" s="11" t="n">
+      <c r="AB22" s="12" t="n">
         <f aca="false">Assumptions!$C$28*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C23" s="5" t="n">
         <f aca="false">SUM(D23:O23)</f>
@@ -3031,56 +3095,56 @@
       </c>
       <c r="Q23" s="5" t="n">
         <f aca="false">SUM(Q15:Q22)</f>
-        <v>274626.5625</v>
+        <v>267761.177884615</v>
       </c>
       <c r="R23" s="5" t="n">
         <f aca="false">SUM(R15:R22)</f>
-        <v>274626.5625</v>
+        <v>267761.177884615</v>
       </c>
       <c r="S23" s="5" t="n">
         <f aca="false">SUM(S15:S22)</f>
-        <v>275376.5625</v>
+        <v>268107.331730769</v>
       </c>
       <c r="T23" s="5" t="n">
         <f aca="false">SUM(T15:T22)</f>
-        <v>275376.5625</v>
+        <v>273244.983552632</v>
       </c>
       <c r="U23" s="5" t="n">
         <f aca="false">SUM(U15:U22)</f>
-        <v>276126.5625</v>
+        <v>273876.5625</v>
       </c>
       <c r="V23" s="5" t="n">
         <f aca="false">SUM(V15:V22)</f>
-        <v>276876.5625</v>
+        <v>274508.141447368</v>
       </c>
       <c r="W23" s="5" t="n">
         <f aca="false">SUM(W15:W22)</f>
-        <v>276126.5625</v>
+        <v>279876.5625</v>
       </c>
       <c r="X23" s="5" t="n">
         <f aca="false">SUM(X15:X22)</f>
-        <v>275376.5625</v>
+        <v>278929.194078947</v>
       </c>
       <c r="Y23" s="5" t="n">
         <f aca="false">SUM(Y15:Y22)</f>
-        <v>276876.5625</v>
+        <v>280823.930921053</v>
       </c>
       <c r="Z23" s="5" t="n">
         <f aca="false">SUM(Z15:Z22)</f>
-        <v>277626.5625</v>
+        <v>282308.994932432</v>
       </c>
       <c r="AA23" s="5" t="n">
         <f aca="false">SUM(AA15:AA22)</f>
-        <v>281376.5625</v>
+        <v>287173.859797297</v>
       </c>
       <c r="AB23" s="5" t="n">
         <f aca="false">SUM(AB15:AB22)</f>
-        <v>282126.5625</v>
+        <v>288146.83277027</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C25" s="5" t="n">
         <f aca="false">SUM(D25:O25)</f>
@@ -3136,219 +3200,219 @@
       </c>
       <c r="P25" s="5" t="n">
         <f aca="false">SUM(Q25:AB25)</f>
-        <v>934481.250000001</v>
+        <v>934481.25</v>
       </c>
       <c r="Q25" s="5" t="n">
         <f aca="false">Q11-Q23</f>
-        <v>26910.9375000001</v>
+        <v>-128590.024038462</v>
       </c>
       <c r="R25" s="5" t="n">
         <f aca="false">R11-R23</f>
-        <v>26910.9375000001</v>
+        <v>-128590.024038462</v>
       </c>
       <c r="S25" s="5" t="n">
         <f aca="false">S11-S23</f>
-        <v>43898.4375000001</v>
+        <v>-120749.639423077</v>
       </c>
       <c r="T25" s="5" t="n">
         <f aca="false">T11-T23</f>
-        <v>43898.4375000001</v>
+        <v>-4381.82565789478</v>
       </c>
       <c r="U25" s="5" t="n">
         <f aca="false">U11-U23</f>
-        <v>60885.9375000001</v>
+        <v>9923.43750000006</v>
       </c>
       <c r="V25" s="5" t="n">
         <f aca="false">V11-V23</f>
-        <v>77873.4375000001</v>
+        <v>24228.7006578948</v>
       </c>
       <c r="W25" s="5" t="n">
         <f aca="false">W11-W23</f>
-        <v>60885.9375000001</v>
+        <v>145823.4375</v>
       </c>
       <c r="X25" s="5" t="n">
         <f aca="false">X11-X23</f>
-        <v>43898.4375000001</v>
+        <v>124365.542763158</v>
       </c>
       <c r="Y25" s="5" t="n">
         <f aca="false">Y11-Y23</f>
-        <v>77873.4375000001</v>
+        <v>167281.332236842</v>
       </c>
       <c r="Z25" s="5" t="n">
         <f aca="false">Z11-Z23</f>
-        <v>94860.9375000001</v>
+        <v>200918.032094595</v>
       </c>
       <c r="AA25" s="5" t="n">
         <f aca="false">AA11-AA23</f>
-        <v>179798.4375</v>
+        <v>311107.221283784</v>
       </c>
       <c r="AB25" s="5" t="n">
         <f aca="false">AB11-AB23</f>
-        <v>196785.9375</v>
+        <v>333145.059121622</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="13" t="n">
+      <c r="B26" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="14" t="n">
         <f aca="false">IF(C6=0,0,C25/C6)</f>
         <v>0.0662165605095541</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <f aca="false">IF(D6=0,0,D25/D6)</f>
         <v>-0.0020393405769952</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="14" t="n">
         <f aca="false">IF(E6=0,0,E25/E6)</f>
         <v>-0.0020393405769952</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="14" t="n">
         <f aca="false">IF(F6=0,0,F25/F6)</f>
         <v>0.0232406227883934</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="G26" s="14" t="n">
         <f aca="false">IF(G6=0,0,G25/G6)</f>
         <v>0.0232406227883934</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="H26" s="14" t="n">
         <f aca="false">IF(H6=0,0,H25/H6)</f>
         <v>0.0458595373784781</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="I26" s="14" t="n">
         <f aca="false">IF(I6=0,0,I25/I6)</f>
         <v>0.0662165605095541</v>
       </c>
-      <c r="J26" s="13" t="n">
+      <c r="J26" s="14" t="n">
         <f aca="false">IF(J6=0,0,J25/J6)</f>
         <v>0.0458595373784781</v>
       </c>
-      <c r="K26" s="13" t="n">
+      <c r="K26" s="14" t="n">
         <f aca="false">IF(K6=0,0,K25/K6)</f>
         <v>0.0232406227883934</v>
       </c>
-      <c r="L26" s="13" t="n">
+      <c r="L26" s="14" t="n">
         <f aca="false">IF(L6=0,0,L25/L6)</f>
         <v>0.0662165605095541</v>
       </c>
-      <c r="M26" s="13" t="n">
+      <c r="M26" s="14" t="n">
         <f aca="false">IF(M6=0,0,M25/M6)</f>
         <v>0.0846348195329087</v>
       </c>
-      <c r="N26" s="13" t="n">
+      <c r="N26" s="14" t="n">
         <f aca="false">IF(N6=0,0,N25/N6)</f>
         <v>0.155474277315042</v>
       </c>
-      <c r="O26" s="13" t="n">
+      <c r="O26" s="14" t="n">
         <f aca="false">IF(O6=0,0,O25/O6)</f>
         <v>0.166493748525596</v>
       </c>
-      <c r="P26" s="13" t="n">
+      <c r="P26" s="14" t="n">
         <f aca="false">IF(P6=0,0,P25/P6)</f>
         <v>0.10383125</v>
       </c>
-      <c r="Q26" s="13" t="n">
+      <c r="Q26" s="14" t="n">
         <f aca="false">IF(Q6=0,0,Q25/Q6)</f>
-        <v>0.0422132352941177</v>
-      </c>
-      <c r="R26" s="13" t="n">
+        <v>-0.437037990196078</v>
+      </c>
+      <c r="R26" s="14" t="n">
         <f aca="false">IF(R6=0,0,R25/R6)</f>
-        <v>0.0422132352941177</v>
-      </c>
-      <c r="S26" s="13" t="n">
+        <v>-0.437037990196078</v>
+      </c>
+      <c r="S26" s="14" t="n">
         <f aca="false">IF(S6=0,0,S25/S6)</f>
-        <v>0.0650347222222223</v>
-      </c>
-      <c r="T26" s="13" t="n">
+        <v>-0.387591435185185</v>
+      </c>
+      <c r="T26" s="14" t="n">
         <f aca="false">IF(T6=0,0,T25/T6)</f>
-        <v>0.0650347222222223</v>
-      </c>
-      <c r="U26" s="13" t="n">
+        <v>-0.00770876736111118</v>
+      </c>
+      <c r="U26" s="14" t="n">
         <f aca="false">IF(U6=0,0,U25/U6)</f>
-        <v>0.0854539473684211</v>
-      </c>
-      <c r="V26" s="13" t="n">
+        <v>0.0165390625000001</v>
+      </c>
+      <c r="V26" s="14" t="n">
         <f aca="false">IF(V6=0,0,V25/V6)</f>
-        <v>0.10383125</v>
-      </c>
-      <c r="W26" s="13" t="n">
+        <v>0.0383621093750001</v>
+      </c>
+      <c r="W26" s="14" t="n">
         <f aca="false">IF(W6=0,0,W25/W6)</f>
-        <v>0.0854539473684211</v>
-      </c>
-      <c r="X26" s="13" t="n">
+        <v>0.162026041666667</v>
+      </c>
+      <c r="X26" s="14" t="n">
         <f aca="false">IF(X6=0,0,X25/X6)</f>
-        <v>0.0650347222222223</v>
-      </c>
-      <c r="Y26" s="13" t="n">
+        <v>0.145860821759259</v>
+      </c>
+      <c r="Y26" s="14" t="n">
         <f aca="false">IF(Y6=0,0,Y25/Y6)</f>
-        <v>0.10383125</v>
-      </c>
-      <c r="Z26" s="13" t="n">
+        <v>0.176574739583333</v>
+      </c>
+      <c r="Z26" s="14" t="n">
         <f aca="false">IF(Z6=0,0,Z25/Z6)</f>
-        <v>0.120458333333333</v>
-      </c>
-      <c r="AA26" s="13" t="n">
+        <v>0.196665798611111</v>
+      </c>
+      <c r="AA26" s="14" t="n">
         <f aca="false">IF(AA6=0,0,AA25/AA6)</f>
-        <v>0.184408653846154</v>
-      </c>
-      <c r="AB26" s="13" t="n">
+        <v>0.245960837339744</v>
+      </c>
+      <c r="AB26" s="14" t="n">
         <f aca="false">IF(AB6=0,0,AB25/AB6)</f>
-        <v>0.194356481481482</v>
+        <v>0.253628954475309</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C28" s="7" t="n">
         <f aca="false">SUM(D28:O28)</f>
         <v>40000</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="H28" s="11" t="n">
+      <c r="H28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="I28" s="11" t="n">
+      <c r="I28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="J28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="M28" s="11" t="n">
+      <c r="M28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="N28" s="11" t="n">
+      <c r="N28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="O28" s="11" t="n">
+      <c r="O28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
@@ -3356,58 +3420,58 @@
         <f aca="false">SUM(Q28:AB28)</f>
         <v>40000</v>
       </c>
-      <c r="Q28" s="11" t="n">
+      <c r="Q28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="S28" s="11" t="n">
+      <c r="S28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="T28" s="11" t="n">
+      <c r="T28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="U28" s="11" t="n">
+      <c r="U28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="X28" s="11" t="n">
+      <c r="X28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="Y28" s="11" t="n">
+      <c r="Y28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="Z28" s="11" t="n">
+      <c r="Z28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="AA28" s="11" t="n">
+      <c r="AA28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="AB28" s="11" t="n">
+      <c r="AB28" s="12" t="n">
         <f aca="false">Assumptions!$C$18/12</f>
         <v>3333.33333333333</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C30" s="5" t="n">
         <f aca="false">SUM(D30:O30)</f>
@@ -3463,164 +3527,164 @@
       </c>
       <c r="P30" s="5" t="n">
         <f aca="false">SUM(Q30:AB30)</f>
-        <v>894481.250000001</v>
+        <v>894481.25</v>
       </c>
       <c r="Q30" s="5" t="n">
         <f aca="false">Q25-Q28</f>
-        <v>23577.6041666667</v>
+        <v>-131923.357371795</v>
       </c>
       <c r="R30" s="5" t="n">
         <f aca="false">R25-R28</f>
-        <v>23577.6041666667</v>
+        <v>-131923.357371795</v>
       </c>
       <c r="S30" s="5" t="n">
         <f aca="false">S25-S28</f>
-        <v>40565.1041666667</v>
+        <v>-124082.97275641</v>
       </c>
       <c r="T30" s="5" t="n">
         <f aca="false">T25-T28</f>
-        <v>40565.1041666667</v>
+        <v>-7715.15899122811</v>
       </c>
       <c r="U30" s="5" t="n">
         <f aca="false">U25-U28</f>
-        <v>57552.6041666667</v>
+        <v>6590.10416666672</v>
       </c>
       <c r="V30" s="5" t="n">
         <f aca="false">V25-V28</f>
-        <v>74540.1041666667</v>
+        <v>20895.3673245614</v>
       </c>
       <c r="W30" s="5" t="n">
         <f aca="false">W25-W28</f>
-        <v>57552.6041666667</v>
+        <v>142490.104166667</v>
       </c>
       <c r="X30" s="5" t="n">
         <f aca="false">X25-X28</f>
-        <v>40565.1041666667</v>
+        <v>121032.209429825</v>
       </c>
       <c r="Y30" s="5" t="n">
         <f aca="false">Y25-Y28</f>
-        <v>74540.1041666667</v>
+        <v>163947.998903509</v>
       </c>
       <c r="Z30" s="5" t="n">
         <f aca="false">Z25-Z28</f>
-        <v>91527.6041666667</v>
+        <v>197584.698761261</v>
       </c>
       <c r="AA30" s="5" t="n">
         <f aca="false">AA25-AA28</f>
-        <v>176465.104166667</v>
+        <v>307773.887950451</v>
       </c>
       <c r="AB30" s="5" t="n">
         <f aca="false">AB25-AB28</f>
-        <v>193452.604166667</v>
+        <v>329811.725788288</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="13" t="n">
+      <c r="B31" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="14" t="n">
         <f aca="false">IF(C6=0,0,C30/C6)</f>
         <v>0.0611210191082802</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="14" t="n">
         <f aca="false">IF(D6=0,0,D30/D6)</f>
         <v>-0.00803409516672918</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="14" t="n">
         <f aca="false">IF(E6=0,0,E30/E6)</f>
         <v>-0.00803409516672918</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="14" t="n">
         <f aca="false">IF(F6=0,0,F30/F6)</f>
         <v>0.0175789101203113</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="14" t="n">
         <f aca="false">IF(G6=0,0,G30/G6)</f>
         <v>0.0175789101203113</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="14" t="n">
         <f aca="false">IF(H6=0,0,H30/H6)</f>
         <v>0.0404958095876635</v>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="I31" s="14" t="n">
         <f aca="false">IF(I6=0,0,I30/I6)</f>
         <v>0.0611210191082802</v>
       </c>
-      <c r="J31" s="13" t="n">
+      <c r="J31" s="14" t="n">
         <f aca="false">IF(J6=0,0,J30/J6)</f>
         <v>0.0404958095876635</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="14" t="n">
         <f aca="false">IF(K6=0,0,K30/K6)</f>
         <v>0.0175789101203113</v>
       </c>
-      <c r="L31" s="13" t="n">
+      <c r="L31" s="14" t="n">
         <f aca="false">IF(L6=0,0,L30/L6)</f>
         <v>0.0611210191082802</v>
       </c>
-      <c r="M31" s="13" t="n">
+      <c r="M31" s="14" t="n">
         <f aca="false">IF(M6=0,0,M30/M6)</f>
         <v>0.0797819229602668</v>
       </c>
-      <c r="N31" s="13" t="n">
+      <c r="N31" s="14" t="n">
         <f aca="false">IF(N6=0,0,N30/N6)</f>
         <v>0.151554630083292</v>
       </c>
-      <c r="O31" s="13" t="n">
+      <c r="O31" s="14" t="n">
         <f aca="false">IF(O6=0,0,O30/O6)</f>
         <v>0.162719273413541</v>
       </c>
-      <c r="P31" s="13" t="n">
+      <c r="P31" s="14" t="n">
         <f aca="false">IF(P6=0,0,P30/P6)</f>
         <v>0.0993868055555556</v>
       </c>
-      <c r="Q31" s="13" t="n">
+      <c r="Q31" s="14" t="n">
         <f aca="false">IF(Q6=0,0,Q30/Q6)</f>
-        <v>0.0369844771241831</v>
-      </c>
-      <c r="R31" s="13" t="n">
+        <v>-0.448366966230937</v>
+      </c>
+      <c r="R31" s="14" t="n">
         <f aca="false">IF(R6=0,0,R30/R6)</f>
-        <v>0.0369844771241831</v>
-      </c>
-      <c r="S31" s="13" t="n">
+        <v>-0.448366966230937</v>
+      </c>
+      <c r="S31" s="14" t="n">
         <f aca="false">IF(S6=0,0,S30/S6)</f>
-        <v>0.060096450617284</v>
-      </c>
-      <c r="T31" s="13" t="n">
+        <v>-0.398291023662551</v>
+      </c>
+      <c r="T31" s="14" t="n">
         <f aca="false">IF(T6=0,0,T30/T6)</f>
-        <v>0.060096450617284</v>
-      </c>
-      <c r="U31" s="13" t="n">
+        <v>-0.0135729648919754</v>
+      </c>
+      <c r="U31" s="14" t="n">
         <f aca="false">IF(U6=0,0,U30/U6)</f>
-        <v>0.0807755847953217</v>
-      </c>
-      <c r="V31" s="13" t="n">
+        <v>0.0109835069444445</v>
+      </c>
+      <c r="V31" s="14" t="n">
         <f aca="false">IF(V6=0,0,V30/V6)</f>
-        <v>0.0993868055555556</v>
-      </c>
-      <c r="W31" s="13" t="n">
+        <v>0.0330843315972223</v>
+      </c>
+      <c r="W31" s="14" t="n">
         <f aca="false">IF(W6=0,0,W30/W6)</f>
-        <v>0.0807755847953217</v>
-      </c>
-      <c r="X31" s="13" t="n">
+        <v>0.158322337962963</v>
+      </c>
+      <c r="X31" s="14" t="n">
         <f aca="false">IF(X6=0,0,X30/X6)</f>
-        <v>0.060096450617284</v>
-      </c>
-      <c r="Y31" s="13" t="n">
+        <v>0.141951356738683</v>
+      </c>
+      <c r="Y31" s="14" t="n">
         <f aca="false">IF(Y6=0,0,Y30/Y6)</f>
-        <v>0.0993868055555556</v>
-      </c>
-      <c r="Z31" s="13" t="n">
+        <v>0.173056221064815</v>
+      </c>
+      <c r="Z31" s="14" t="n">
         <f aca="false">IF(Z6=0,0,Z30/Z6)</f>
-        <v>0.116225529100529</v>
-      </c>
-      <c r="AA31" s="13" t="n">
+        <v>0.193403012014991</v>
+      </c>
+      <c r="AA31" s="14" t="n">
         <f aca="false">IF(AA6=0,0,AA30/AA6)</f>
-        <v>0.18098985042735</v>
-      </c>
-      <c r="AB31" s="13" t="n">
+        <v>0.243325509704416</v>
+      </c>
+      <c r="AB31" s="14" t="n">
         <f aca="false">IF(AB6=0,0,AB30/AB6)</f>
-        <v>0.191064300411523</v>
+        <v>0.251091231567215</v>
       </c>
     </row>
   </sheetData>
@@ -3649,20 +3713,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -3701,7 +3765,7 @@
         <v>40</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>29</v>
@@ -3742,57 +3806,57 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C6" s="5" t="n">
         <f aca="false">SUM(D6:O6)</f>
         <v>5100000</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$C$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>361250</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$D$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>361250</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$E$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>382500</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$F$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>382500</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$G$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>403750</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$H$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>425000</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$I$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>403750</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$J$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>382500</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$K$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>425000</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$L$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>446250</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$M$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>552500</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="12" t="n">
         <f aca="false">Assumptions!$C$7*Assumptions!$N$32/SUM(Assumptions!$C$32:$N$32)</f>
         <v>573750</v>
       </c>
@@ -3800,108 +3864,108 @@
         <f aca="false">SUM(Q6:AB6)</f>
         <v>6000000</v>
       </c>
-      <c r="Q6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$C$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>425000</v>
-      </c>
-      <c r="R6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$D$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>425000</v>
-      </c>
-      <c r="S6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$E$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>450000</v>
-      </c>
-      <c r="T6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$F$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>450000</v>
-      </c>
-      <c r="U6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$G$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>475000</v>
-      </c>
-      <c r="V6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$H$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>500000</v>
-      </c>
-      <c r="W6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$I$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>475000</v>
-      </c>
-      <c r="X6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$J$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>450000</v>
-      </c>
-      <c r="Y6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$K$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>500000</v>
-      </c>
-      <c r="Z6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$L$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>525000</v>
-      </c>
-      <c r="AA6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$M$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>650000</v>
-      </c>
-      <c r="AB6" s="11" t="n">
-        <f aca="false">Assumptions!$D$7*Assumptions!$N$32/SUM(Assumptions!$C$32:$N$32)</f>
-        <v>675000</v>
+      <c r="Q6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$C$37*Assumptions!$C$32/SUM(Assumptions!$C$32:$E$32)</f>
+        <v>196153.846153846</v>
+      </c>
+      <c r="R6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$C$37*Assumptions!$D$32/SUM(Assumptions!$C$32:$E$32)</f>
+        <v>196153.846153846</v>
+      </c>
+      <c r="S6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$C$37*Assumptions!$E$32/SUM(Assumptions!$C$32:$E$32)</f>
+        <v>207692.307692308</v>
+      </c>
+      <c r="T6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$D$37*Assumptions!$F$32/SUM(Assumptions!$F$32:$H$32)</f>
+        <v>378947.368421053</v>
+      </c>
+      <c r="U6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$D$37*Assumptions!$G$32/SUM(Assumptions!$F$32:$H$32)</f>
+        <v>400000</v>
+      </c>
+      <c r="V6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$D$37*Assumptions!$H$32/SUM(Assumptions!$F$32:$H$32)</f>
+        <v>421052.631578947</v>
+      </c>
+      <c r="W6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$E$37*Assumptions!$I$32/SUM(Assumptions!$I$32:$K$32)</f>
+        <v>600000</v>
+      </c>
+      <c r="X6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$E$37*Assumptions!$J$32/SUM(Assumptions!$I$32:$K$32)</f>
+        <v>568421.052631579</v>
+      </c>
+      <c r="Y6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$E$37*Assumptions!$K$32/SUM(Assumptions!$I$32:$K$32)</f>
+        <v>631578.947368421</v>
+      </c>
+      <c r="Z6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$F$37*Assumptions!$L$32/SUM(Assumptions!$L$32:$N$32)</f>
+        <v>681081.081081081</v>
+      </c>
+      <c r="AA6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$F$37*Assumptions!$M$32/SUM(Assumptions!$L$32:$N$32)</f>
+        <v>843243.243243243</v>
+      </c>
+      <c r="AB6" s="12" t="n">
+        <f aca="false">Assumptions!$D$7*Assumptions!$F$37*Assumptions!$N$32/SUM(Assumptions!$L$32:$N$32)</f>
+        <v>875675.675675676</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">SUM(D9:O9)</f>
         <v>2687700</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <f aca="false">D6*(1-Assumptions!$C$11)</f>
         <v>190378.75</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <f aca="false">E6*(1-Assumptions!$C$11)</f>
         <v>190378.75</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <f aca="false">F6*(1-Assumptions!$C$11)</f>
         <v>201577.5</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="12" t="n">
         <f aca="false">G6*(1-Assumptions!$C$11)</f>
         <v>201577.5</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="12" t="n">
         <f aca="false">H6*(1-Assumptions!$C$11)</f>
         <v>212776.25</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="12" t="n">
         <f aca="false">I6*(1-Assumptions!$C$11)</f>
         <v>223975</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="12" t="n">
         <f aca="false">J6*(1-Assumptions!$C$11)</f>
         <v>212776.25</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="12" t="n">
         <f aca="false">K6*(1-Assumptions!$C$11)</f>
         <v>201577.5</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="12" t="n">
         <f aca="false">L6*(1-Assumptions!$C$11)</f>
         <v>223975</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="12" t="n">
         <f aca="false">M6*(1-Assumptions!$C$11)</f>
         <v>235173.75</v>
       </c>
-      <c r="N9" s="11" t="n">
+      <c r="N9" s="12" t="n">
         <f aca="false">N6*(1-Assumptions!$C$11)</f>
         <v>291167.5</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="12" t="n">
         <f aca="false">O6*(1-Assumptions!$C$11)</f>
         <v>302366.25</v>
       </c>
@@ -3909,58 +3973,58 @@
         <f aca="false">SUM(Q9:AB9)</f>
         <v>3162000</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="12" t="n">
         <f aca="false">Q6*(1-Assumptions!$C$11)</f>
-        <v>223975</v>
-      </c>
-      <c r="R9" s="11" t="n">
+        <v>103373.076923077</v>
+      </c>
+      <c r="R9" s="12" t="n">
         <f aca="false">R6*(1-Assumptions!$C$11)</f>
-        <v>223975</v>
-      </c>
-      <c r="S9" s="11" t="n">
+        <v>103373.076923077</v>
+      </c>
+      <c r="S9" s="12" t="n">
         <f aca="false">S6*(1-Assumptions!$C$11)</f>
-        <v>237150</v>
-      </c>
-      <c r="T9" s="11" t="n">
+        <v>109453.846153846</v>
+      </c>
+      <c r="T9" s="12" t="n">
         <f aca="false">T6*(1-Assumptions!$C$11)</f>
-        <v>237150</v>
-      </c>
-      <c r="U9" s="11" t="n">
+        <v>199705.263157895</v>
+      </c>
+      <c r="U9" s="12" t="n">
         <f aca="false">U6*(1-Assumptions!$C$11)</f>
-        <v>250325</v>
-      </c>
-      <c r="V9" s="11" t="n">
+        <v>210800</v>
+      </c>
+      <c r="V9" s="12" t="n">
         <f aca="false">V6*(1-Assumptions!$C$11)</f>
-        <v>263500</v>
-      </c>
-      <c r="W9" s="11" t="n">
+        <v>221894.736842105</v>
+      </c>
+      <c r="W9" s="12" t="n">
         <f aca="false">W6*(1-Assumptions!$C$11)</f>
-        <v>250325</v>
-      </c>
-      <c r="X9" s="11" t="n">
+        <v>316200</v>
+      </c>
+      <c r="X9" s="12" t="n">
         <f aca="false">X6*(1-Assumptions!$C$11)</f>
-        <v>237150</v>
-      </c>
-      <c r="Y9" s="11" t="n">
+        <v>299557.894736842</v>
+      </c>
+      <c r="Y9" s="12" t="n">
         <f aca="false">Y6*(1-Assumptions!$C$11)</f>
-        <v>263500</v>
-      </c>
-      <c r="Z9" s="11" t="n">
+        <v>332842.105263158</v>
+      </c>
+      <c r="Z9" s="12" t="n">
         <f aca="false">Z6*(1-Assumptions!$C$11)</f>
-        <v>276675</v>
-      </c>
-      <c r="AA9" s="11" t="n">
+        <v>358929.72972973</v>
+      </c>
+      <c r="AA9" s="12" t="n">
         <f aca="false">AA6*(1-Assumptions!$C$11)</f>
-        <v>342550</v>
-      </c>
-      <c r="AB9" s="11" t="n">
+        <v>444389.189189189</v>
+      </c>
+      <c r="AB9" s="12" t="n">
         <f aca="false">AB6*(1-Assumptions!$C$11)</f>
-        <v>355725</v>
+        <v>461481.081081081</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(D11:O11)</f>
@@ -4020,220 +4084,220 @@
       </c>
       <c r="Q11" s="7" t="n">
         <f aca="false">Q6-Q9</f>
-        <v>201025</v>
+        <v>92780.7692307692</v>
       </c>
       <c r="R11" s="7" t="n">
         <f aca="false">R6-R9</f>
-        <v>201025</v>
+        <v>92780.7692307692</v>
       </c>
       <c r="S11" s="7" t="n">
         <f aca="false">S6-S9</f>
-        <v>212850</v>
+        <v>98238.4615384615</v>
       </c>
       <c r="T11" s="7" t="n">
         <f aca="false">T6-T9</f>
-        <v>212850</v>
+        <v>179242.105263158</v>
       </c>
       <c r="U11" s="7" t="n">
         <f aca="false">U6-U9</f>
-        <v>224675</v>
+        <v>189200</v>
       </c>
       <c r="V11" s="7" t="n">
         <f aca="false">V6-V9</f>
-        <v>236500</v>
+        <v>199157.894736842</v>
       </c>
       <c r="W11" s="7" t="n">
         <f aca="false">W6-W9</f>
-        <v>224675</v>
+        <v>283800</v>
       </c>
       <c r="X11" s="7" t="n">
         <f aca="false">X6-X9</f>
-        <v>212850</v>
+        <v>268863.157894737</v>
       </c>
       <c r="Y11" s="7" t="n">
         <f aca="false">Y6-Y9</f>
-        <v>236500</v>
+        <v>298736.842105263</v>
       </c>
       <c r="Z11" s="7" t="n">
         <f aca="false">Z6-Z9</f>
-        <v>248325</v>
+        <v>322151.351351351</v>
       </c>
       <c r="AA11" s="7" t="n">
         <f aca="false">AA6-AA9</f>
-        <v>307450</v>
+        <v>398854.054054054</v>
       </c>
       <c r="AB11" s="7" t="n">
         <f aca="false">AB6-AB9</f>
-        <v>319275</v>
+        <v>414194.594594595</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="13" t="n">
+      <c r="B12" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="14" t="n">
         <f aca="false">IF(C6=0,0,C11/C6)</f>
         <v>0.473</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <f aca="false">IF(D6=0,0,D11/D6)</f>
         <v>0.473</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <f aca="false">IF(E6=0,0,E11/E6)</f>
         <v>0.473</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="14" t="n">
         <f aca="false">IF(F6=0,0,F11/F6)</f>
         <v>0.473</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="14" t="n">
         <f aca="false">IF(G6=0,0,G11/G6)</f>
         <v>0.473</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="14" t="n">
         <f aca="false">IF(H6=0,0,H11/H6)</f>
         <v>0.473</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="14" t="n">
         <f aca="false">IF(I6=0,0,I11/I6)</f>
         <v>0.473</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="14" t="n">
         <f aca="false">IF(J6=0,0,J11/J6)</f>
         <v>0.473</v>
       </c>
-      <c r="K12" s="13" t="n">
+      <c r="K12" s="14" t="n">
         <f aca="false">IF(K6=0,0,K11/K6)</f>
         <v>0.473</v>
       </c>
-      <c r="L12" s="13" t="n">
+      <c r="L12" s="14" t="n">
         <f aca="false">IF(L6=0,0,L11/L6)</f>
         <v>0.473</v>
       </c>
-      <c r="M12" s="13" t="n">
+      <c r="M12" s="14" t="n">
         <f aca="false">IF(M6=0,0,M11/M6)</f>
         <v>0.473</v>
       </c>
-      <c r="N12" s="13" t="n">
+      <c r="N12" s="14" t="n">
         <f aca="false">IF(N6=0,0,N11/N6)</f>
         <v>0.473</v>
       </c>
-      <c r="O12" s="13" t="n">
+      <c r="O12" s="14" t="n">
         <f aca="false">IF(O6=0,0,O11/O6)</f>
         <v>0.473</v>
       </c>
-      <c r="P12" s="13" t="n">
+      <c r="P12" s="14" t="n">
         <f aca="false">IF(P6=0,0,P11/P6)</f>
         <v>0.473</v>
       </c>
-      <c r="Q12" s="13" t="n">
+      <c r="Q12" s="14" t="n">
         <f aca="false">IF(Q6=0,0,Q11/Q6)</f>
         <v>0.473</v>
       </c>
-      <c r="R12" s="13" t="n">
+      <c r="R12" s="14" t="n">
         <f aca="false">IF(R6=0,0,R11/R6)</f>
         <v>0.473</v>
       </c>
-      <c r="S12" s="13" t="n">
+      <c r="S12" s="14" t="n">
         <f aca="false">IF(S6=0,0,S11/S6)</f>
         <v>0.473</v>
       </c>
-      <c r="T12" s="13" t="n">
+      <c r="T12" s="14" t="n">
         <f aca="false">IF(T6=0,0,T11/T6)</f>
         <v>0.473</v>
       </c>
-      <c r="U12" s="13" t="n">
+      <c r="U12" s="14" t="n">
         <f aca="false">IF(U6=0,0,U11/U6)</f>
         <v>0.473</v>
       </c>
-      <c r="V12" s="13" t="n">
+      <c r="V12" s="14" t="n">
         <f aca="false">IF(V6=0,0,V11/V6)</f>
         <v>0.473</v>
       </c>
-      <c r="W12" s="13" t="n">
+      <c r="W12" s="14" t="n">
         <f aca="false">IF(W6=0,0,W11/W6)</f>
         <v>0.473</v>
       </c>
-      <c r="X12" s="13" t="n">
+      <c r="X12" s="14" t="n">
         <f aca="false">IF(X6=0,0,X11/X6)</f>
         <v>0.473</v>
       </c>
-      <c r="Y12" s="13" t="n">
+      <c r="Y12" s="14" t="n">
         <f aca="false">IF(Y6=0,0,Y11/Y6)</f>
         <v>0.473</v>
       </c>
-      <c r="Z12" s="13" t="n">
+      <c r="Z12" s="14" t="n">
         <f aca="false">IF(Z6=0,0,Z11/Z6)</f>
         <v>0.473</v>
       </c>
-      <c r="AA12" s="13" t="n">
+      <c r="AA12" s="14" t="n">
         <f aca="false">IF(AA6=0,0,AA11/AA6)</f>
         <v>0.473</v>
       </c>
-      <c r="AB12" s="13" t="n">
+      <c r="AB12" s="14" t="n">
         <f aca="false">IF(AB6=0,0,AB11/AB6)</f>
         <v>0.473</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">SUM(D15:O15)</f>
         <v>546250</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="H15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="I15" s="11" t="n">
+      <c r="I15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="N15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="O15" s="12" t="n">
         <f aca="false">Headcount!$D$28*(1+Assumptions!$C$15)/12</f>
         <v>45520.8333333333</v>
       </c>
@@ -4241,108 +4305,108 @@
         <f aca="false">SUM(Q15:AB15)</f>
         <v>565368.75</v>
       </c>
-      <c r="Q15" s="11" t="n">
+      <c r="Q15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="R15" s="11" t="n">
+      <c r="R15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="S15" s="11" t="n">
+      <c r="S15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="T15" s="11" t="n">
+      <c r="T15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="U15" s="11" t="n">
+      <c r="U15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="V15" s="11" t="n">
+      <c r="V15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="W15" s="11" t="n">
+      <c r="W15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="X15" s="11" t="n">
+      <c r="X15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="Y15" s="11" t="n">
+      <c r="Y15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="Z15" s="11" t="n">
+      <c r="Z15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="AA15" s="11" t="n">
+      <c r="AA15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
-      <c r="AB15" s="11" t="n">
+      <c r="AB15" s="12" t="n">
         <f aca="false">Headcount!$E$28*(1+Assumptions!$C$15)/12</f>
         <v>47114.0625</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">SUM(D16:O16)</f>
         <v>102000</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <f aca="false">D6*Assumptions!$C$16</f>
         <v>7225</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <f aca="false">E6*Assumptions!$C$16</f>
         <v>7225</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <f aca="false">F6*Assumptions!$C$16</f>
         <v>7650</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="12" t="n">
         <f aca="false">G6*Assumptions!$C$16</f>
         <v>7650</v>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="12" t="n">
         <f aca="false">H6*Assumptions!$C$16</f>
         <v>8075</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" s="12" t="n">
         <f aca="false">I6*Assumptions!$C$16</f>
         <v>8500</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="12" t="n">
         <f aca="false">J6*Assumptions!$C$16</f>
         <v>8075</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="12" t="n">
         <f aca="false">K6*Assumptions!$C$16</f>
         <v>7650</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" s="12" t="n">
         <f aca="false">L6*Assumptions!$C$16</f>
         <v>8500</v>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="M16" s="12" t="n">
         <f aca="false">M6*Assumptions!$C$16</f>
         <v>8925</v>
       </c>
-      <c r="N16" s="11" t="n">
+      <c r="N16" s="12" t="n">
         <f aca="false">N6*Assumptions!$C$16</f>
         <v>11050</v>
       </c>
-      <c r="O16" s="11" t="n">
+      <c r="O16" s="12" t="n">
         <f aca="false">O6*Assumptions!$C$16</f>
         <v>11475</v>
       </c>
@@ -4350,53 +4414,53 @@
         <f aca="false">SUM(Q16:AB16)</f>
         <v>120000</v>
       </c>
-      <c r="Q16" s="11" t="n">
+      <c r="Q16" s="12" t="n">
         <f aca="false">Q6*Assumptions!$C$16</f>
-        <v>8500</v>
-      </c>
-      <c r="R16" s="11" t="n">
+        <v>3923.07692307692</v>
+      </c>
+      <c r="R16" s="12" t="n">
         <f aca="false">R6*Assumptions!$C$16</f>
-        <v>8500</v>
-      </c>
-      <c r="S16" s="11" t="n">
+        <v>3923.07692307692</v>
+      </c>
+      <c r="S16" s="12" t="n">
         <f aca="false">S6*Assumptions!$C$16</f>
-        <v>9000</v>
-      </c>
-      <c r="T16" s="11" t="n">
+        <v>4153.84615384615</v>
+      </c>
+      <c r="T16" s="12" t="n">
         <f aca="false">T6*Assumptions!$C$16</f>
-        <v>9000</v>
-      </c>
-      <c r="U16" s="11" t="n">
+        <v>7578.94736842105</v>
+      </c>
+      <c r="U16" s="12" t="n">
         <f aca="false">U6*Assumptions!$C$16</f>
-        <v>9500</v>
-      </c>
-      <c r="V16" s="11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="V16" s="12" t="n">
         <f aca="false">V6*Assumptions!$C$16</f>
-        <v>10000</v>
-      </c>
-      <c r="W16" s="11" t="n">
+        <v>8421.05263157895</v>
+      </c>
+      <c r="W16" s="12" t="n">
         <f aca="false">W6*Assumptions!$C$16</f>
-        <v>9500</v>
-      </c>
-      <c r="X16" s="11" t="n">
+        <v>12000</v>
+      </c>
+      <c r="X16" s="12" t="n">
         <f aca="false">X6*Assumptions!$C$16</f>
-        <v>9000</v>
-      </c>
-      <c r="Y16" s="11" t="n">
+        <v>11368.4210526316</v>
+      </c>
+      <c r="Y16" s="12" t="n">
         <f aca="false">Y6*Assumptions!$C$16</f>
-        <v>10000</v>
-      </c>
-      <c r="Z16" s="11" t="n">
+        <v>12631.5789473684</v>
+      </c>
+      <c r="Z16" s="12" t="n">
         <f aca="false">Z6*Assumptions!$C$16</f>
-        <v>10500</v>
-      </c>
-      <c r="AA16" s="11" t="n">
+        <v>13621.6216216216</v>
+      </c>
+      <c r="AA16" s="12" t="n">
         <f aca="false">AA6*Assumptions!$C$16</f>
-        <v>13000</v>
-      </c>
-      <c r="AB16" s="11" t="n">
+        <v>16864.8648648649</v>
+      </c>
+      <c r="AB16" s="12" t="n">
         <f aca="false">AB6*Assumptions!$C$16</f>
-        <v>13500</v>
+        <v>17513.5135135135</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4407,51 +4471,51 @@
         <f aca="false">SUM(D17:O17)</f>
         <v>90000</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="I17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="N17" s="11" t="n">
+      <c r="N17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="O17" s="12" t="n">
         <f aca="false">Assumptions!$D$23/12</f>
         <v>7500</v>
       </c>
@@ -4459,51 +4523,51 @@
         <f aca="false">SUM(Q17:AB17)</f>
         <v>93150</v>
       </c>
-      <c r="Q17" s="11" t="n">
+      <c r="Q17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="R17" s="11" t="n">
+      <c r="R17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="S17" s="11" t="n">
+      <c r="S17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="T17" s="11" t="n">
+      <c r="T17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="U17" s="11" t="n">
+      <c r="U17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="V17" s="11" t="n">
+      <c r="V17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="W17" s="11" t="n">
+      <c r="W17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="X17" s="11" t="n">
+      <c r="X17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="Y17" s="11" t="n">
+      <c r="Y17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="Z17" s="11" t="n">
+      <c r="Z17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="AA17" s="11" t="n">
+      <c r="AA17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
-      <c r="AB17" s="11" t="n">
+      <c r="AB17" s="12" t="n">
         <f aca="false">Assumptions!$D$23*(1+Assumptions!$C$17)/12</f>
         <v>7762.5</v>
       </c>
@@ -4516,51 +4580,51 @@
         <f aca="false">SUM(D18:O18)</f>
         <v>140000</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="H18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="K18" s="11" t="n">
+      <c r="K18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="N18" s="11" t="n">
+      <c r="N18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
-      <c r="O18" s="11" t="n">
+      <c r="O18" s="12" t="n">
         <f aca="false">Assumptions!$D$24/12</f>
         <v>11666.6666666667</v>
       </c>
@@ -4568,51 +4632,51 @@
         <f aca="false">SUM(Q18:AB18)</f>
         <v>144900</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="R18" s="11" t="n">
+      <c r="R18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="S18" s="11" t="n">
+      <c r="S18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="T18" s="11" t="n">
+      <c r="T18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="U18" s="11" t="n">
+      <c r="U18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="V18" s="11" t="n">
+      <c r="V18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="W18" s="11" t="n">
+      <c r="W18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="X18" s="11" t="n">
+      <c r="X18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="Y18" s="11" t="n">
+      <c r="Y18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="Z18" s="11" t="n">
+      <c r="Z18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="AA18" s="11" t="n">
+      <c r="AA18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
-      <c r="AB18" s="11" t="n">
+      <c r="AB18" s="12" t="n">
         <f aca="false">Assumptions!$D$24*(1+Assumptions!$C$17)/12</f>
         <v>12075</v>
       </c>
@@ -4625,51 +4689,51 @@
         <f aca="false">SUM(D19:O19)</f>
         <v>60000</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="L19" s="11" t="n">
+      <c r="L19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="N19" s="11" t="n">
+      <c r="N19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
-      <c r="O19" s="11" t="n">
+      <c r="O19" s="12" t="n">
         <f aca="false">Assumptions!$D$25/12</f>
         <v>5000</v>
       </c>
@@ -4677,51 +4741,51 @@
         <f aca="false">SUM(Q19:AB19)</f>
         <v>62100</v>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="S19" s="11" t="n">
+      <c r="S19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="T19" s="11" t="n">
+      <c r="T19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="U19" s="11" t="n">
+      <c r="U19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="V19" s="11" t="n">
+      <c r="V19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="W19" s="11" t="n">
+      <c r="W19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="X19" s="11" t="n">
+      <c r="X19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="Y19" s="11" t="n">
+      <c r="Y19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="Z19" s="11" t="n">
+      <c r="Z19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="AA19" s="11" t="n">
+      <c r="AA19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
-      <c r="AB19" s="11" t="n">
+      <c r="AB19" s="12" t="n">
         <f aca="false">Assumptions!$D$25*(1+Assumptions!$C$17)/12</f>
         <v>5175</v>
       </c>
@@ -4734,51 +4798,51 @@
         <f aca="false">SUM(D20:O20)</f>
         <v>40000</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="H20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="K20" s="11" t="n">
+      <c r="K20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="L20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="M20" s="11" t="n">
+      <c r="M20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="N20" s="11" t="n">
+      <c r="N20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="O20" s="11" t="n">
+      <c r="O20" s="12" t="n">
         <f aca="false">Assumptions!$D$26/12</f>
         <v>3333.33333333333</v>
       </c>
@@ -4786,51 +4850,51 @@
         <f aca="false">SUM(Q20:AB20)</f>
         <v>41400</v>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="S20" s="11" t="n">
+      <c r="S20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="T20" s="11" t="n">
+      <c r="T20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="U20" s="11" t="n">
+      <c r="U20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="V20" s="11" t="n">
+      <c r="V20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="W20" s="11" t="n">
+      <c r="W20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="X20" s="11" t="n">
+      <c r="X20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="Y20" s="11" t="n">
+      <c r="Y20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="Z20" s="11" t="n">
+      <c r="Z20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="AA20" s="11" t="n">
+      <c r="AA20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
-      <c r="AB20" s="11" t="n">
+      <c r="AB20" s="12" t="n">
         <f aca="false">Assumptions!$D$26*(1+Assumptions!$C$17)/12</f>
         <v>3450</v>
       </c>
@@ -4843,51 +4907,51 @@
         <f aca="false">SUM(D21:O21)</f>
         <v>160000</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="G21" s="11" t="n">
+      <c r="G21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="H21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="M21" s="11" t="n">
+      <c r="M21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="N21" s="11" t="n">
+      <c r="N21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
-      <c r="O21" s="11" t="n">
+      <c r="O21" s="12" t="n">
         <f aca="false">Assumptions!$D$27/12</f>
         <v>13333.3333333333</v>
       </c>
@@ -4895,51 +4959,51 @@
         <f aca="false">SUM(Q21:AB21)</f>
         <v>165600</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="S21" s="11" t="n">
+      <c r="S21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="T21" s="11" t="n">
+      <c r="T21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="U21" s="11" t="n">
+      <c r="U21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="V21" s="11" t="n">
+      <c r="V21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="W21" s="11" t="n">
+      <c r="W21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="X21" s="11" t="n">
+      <c r="X21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="Y21" s="11" t="n">
+      <c r="Y21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="Z21" s="11" t="n">
+      <c r="Z21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="AA21" s="11" t="n">
+      <c r="AA21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
-      <c r="AB21" s="11" t="n">
+      <c r="AB21" s="12" t="n">
         <f aca="false">Assumptions!$D$27*(1+Assumptions!$C$17)/12</f>
         <v>13800</v>
       </c>
@@ -4952,51 +5016,51 @@
         <f aca="false">SUM(D22:O22)</f>
         <v>80000</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="G22" s="11" t="n">
+      <c r="G22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="H22" s="11" t="n">
+      <c r="H22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="K22" s="11" t="n">
+      <c r="K22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="M22" s="11" t="n">
+      <c r="M22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="N22" s="11" t="n">
+      <c r="N22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
-      <c r="O22" s="11" t="n">
+      <c r="O22" s="12" t="n">
         <f aca="false">Assumptions!$D$28/12</f>
         <v>6666.66666666667</v>
       </c>
@@ -5004,58 +5068,58 @@
         <f aca="false">SUM(Q22:AB22)</f>
         <v>82800</v>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="S22" s="11" t="n">
+      <c r="S22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="T22" s="11" t="n">
+      <c r="T22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="U22" s="11" t="n">
+      <c r="U22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="V22" s="11" t="n">
+      <c r="V22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="W22" s="11" t="n">
+      <c r="W22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="X22" s="11" t="n">
+      <c r="X22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="Y22" s="11" t="n">
+      <c r="Y22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="Z22" s="11" t="n">
+      <c r="Z22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="AA22" s="11" t="n">
+      <c r="AA22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
-      <c r="AB22" s="11" t="n">
+      <c r="AB22" s="12" t="n">
         <f aca="false">Assumptions!$D$28*(1+Assumptions!$C$17)/12</f>
         <v>6900</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C23" s="5" t="n">
         <f aca="false">SUM(D23:O23)</f>
@@ -5115,56 +5179,56 @@
       </c>
       <c r="Q23" s="5" t="n">
         <f aca="false">SUM(Q15:Q22)</f>
-        <v>104776.5625</v>
+        <v>100199.639423077</v>
       </c>
       <c r="R23" s="5" t="n">
         <f aca="false">SUM(R15:R22)</f>
-        <v>104776.5625</v>
+        <v>100199.639423077</v>
       </c>
       <c r="S23" s="5" t="n">
         <f aca="false">SUM(S15:S22)</f>
-        <v>105276.5625</v>
+        <v>100430.408653846</v>
       </c>
       <c r="T23" s="5" t="n">
         <f aca="false">SUM(T15:T22)</f>
-        <v>105276.5625</v>
+        <v>103855.509868421</v>
       </c>
       <c r="U23" s="5" t="n">
         <f aca="false">SUM(U15:U22)</f>
-        <v>105776.5625</v>
+        <v>104276.5625</v>
       </c>
       <c r="V23" s="5" t="n">
         <f aca="false">SUM(V15:V22)</f>
-        <v>106276.5625</v>
+        <v>104697.615131579</v>
       </c>
       <c r="W23" s="5" t="n">
         <f aca="false">SUM(W15:W22)</f>
-        <v>105776.5625</v>
+        <v>108276.5625</v>
       </c>
       <c r="X23" s="5" t="n">
         <f aca="false">SUM(X15:X22)</f>
-        <v>105276.5625</v>
+        <v>107644.983552632</v>
       </c>
       <c r="Y23" s="5" t="n">
         <f aca="false">SUM(Y15:Y22)</f>
-        <v>106276.5625</v>
+        <v>108908.141447368</v>
       </c>
       <c r="Z23" s="5" t="n">
         <f aca="false">SUM(Z15:Z22)</f>
-        <v>106776.5625</v>
+        <v>109898.184121622</v>
       </c>
       <c r="AA23" s="5" t="n">
         <f aca="false">SUM(AA15:AA22)</f>
-        <v>109276.5625</v>
+        <v>113141.427364865</v>
       </c>
       <c r="AB23" s="5" t="n">
         <f aca="false">SUM(AB15:AB22)</f>
-        <v>109776.5625</v>
+        <v>113790.076013514</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C25" s="5" t="n">
         <f aca="false">SUM(D25:O25)</f>
@@ -5224,215 +5288,215 @@
       </c>
       <c r="Q25" s="5" t="n">
         <f aca="false">Q11-Q23</f>
-        <v>96248.4375</v>
+        <v>-7418.87019230769</v>
       </c>
       <c r="R25" s="5" t="n">
         <f aca="false">R11-R23</f>
-        <v>96248.4375</v>
+        <v>-7418.87019230769</v>
       </c>
       <c r="S25" s="5" t="n">
         <f aca="false">S11-S23</f>
-        <v>107573.4375</v>
+        <v>-2191.94711538461</v>
       </c>
       <c r="T25" s="5" t="n">
         <f aca="false">T11-T23</f>
-        <v>107573.4375</v>
+        <v>75386.5953947369</v>
       </c>
       <c r="U25" s="5" t="n">
         <f aca="false">U11-U23</f>
-        <v>118898.4375</v>
+        <v>84923.4375</v>
       </c>
       <c r="V25" s="5" t="n">
         <f aca="false">V11-V23</f>
-        <v>130223.4375</v>
+        <v>94460.2796052632</v>
       </c>
       <c r="W25" s="5" t="n">
         <f aca="false">W11-W23</f>
-        <v>118898.4375</v>
+        <v>175523.4375</v>
       </c>
       <c r="X25" s="5" t="n">
         <f aca="false">X11-X23</f>
-        <v>107573.4375</v>
+        <v>161218.174342105</v>
       </c>
       <c r="Y25" s="5" t="n">
         <f aca="false">Y11-Y23</f>
-        <v>130223.4375</v>
+        <v>189828.700657895</v>
       </c>
       <c r="Z25" s="5" t="n">
         <f aca="false">Z11-Z23</f>
-        <v>141548.4375</v>
+        <v>212253.16722973</v>
       </c>
       <c r="AA25" s="5" t="n">
         <f aca="false">AA11-AA23</f>
-        <v>198173.4375</v>
+        <v>285712.626689189</v>
       </c>
       <c r="AB25" s="5" t="n">
         <f aca="false">AB11-AB23</f>
-        <v>209498.4375</v>
+        <v>300404.518581081</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="13" t="n">
+      <c r="B26" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="14" t="n">
         <f aca="false">IF(C6=0,0,C25/C6)</f>
         <v>0.234127450980392</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <f aca="false">IF(D6=0,0,D25/D6)</f>
         <v>0.195502883506344</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="14" t="n">
         <f aca="false">IF(E6=0,0,E25/E6)</f>
         <v>0.195502883506344</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="14" t="n">
         <f aca="false">IF(F6=0,0,F25/F6)</f>
         <v>0.209808278867102</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="G26" s="14" t="n">
         <f aca="false">IF(G6=0,0,G25/G6)</f>
         <v>0.209808278867102</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="H26" s="14" t="n">
         <f aca="false">IF(H6=0,0,H25/H6)</f>
         <v>0.222607843137255</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="I26" s="14" t="n">
         <f aca="false">IF(I6=0,0,I25/I6)</f>
         <v>0.234127450980392</v>
       </c>
-      <c r="J26" s="13" t="n">
+      <c r="J26" s="14" t="n">
         <f aca="false">IF(J6=0,0,J25/J6)</f>
         <v>0.222607843137255</v>
       </c>
-      <c r="K26" s="13" t="n">
+      <c r="K26" s="14" t="n">
         <f aca="false">IF(K6=0,0,K25/K6)</f>
         <v>0.209808278867102</v>
       </c>
-      <c r="L26" s="13" t="n">
+      <c r="L26" s="14" t="n">
         <f aca="false">IF(L6=0,0,L25/L6)</f>
         <v>0.234127450980392</v>
       </c>
-      <c r="M26" s="13" t="n">
+      <c r="M26" s="14" t="n">
         <f aca="false">IF(M6=0,0,M25/M6)</f>
         <v>0.244549953314659</v>
       </c>
-      <c r="N26" s="13" t="n">
+      <c r="N26" s="14" t="n">
         <f aca="false">IF(N6=0,0,N25/N6)</f>
         <v>0.284636500754148</v>
       </c>
-      <c r="O26" s="13" t="n">
+      <c r="O26" s="14" t="n">
         <f aca="false">IF(O6=0,0,O25/O6)</f>
         <v>0.290872185911402</v>
       </c>
-      <c r="P26" s="13" t="n">
+      <c r="P26" s="14" t="n">
         <f aca="false">IF(P6=0,0,P25/P6)</f>
         <v>0.260446875</v>
       </c>
-      <c r="Q26" s="13" t="n">
+      <c r="Q26" s="14" t="n">
         <f aca="false">IF(Q6=0,0,Q25/Q6)</f>
-        <v>0.226466911764706</v>
-      </c>
-      <c r="R26" s="13" t="n">
+        <v>-0.0378216911764706</v>
+      </c>
+      <c r="R26" s="14" t="n">
         <f aca="false">IF(R6=0,0,R25/R6)</f>
-        <v>0.226466911764706</v>
-      </c>
-      <c r="S26" s="13" t="n">
+        <v>-0.0378216911764706</v>
+      </c>
+      <c r="S26" s="14" t="n">
         <f aca="false">IF(S6=0,0,S25/S6)</f>
-        <v>0.239052083333333</v>
-      </c>
-      <c r="T26" s="13" t="n">
+        <v>-0.0105538194444444</v>
+      </c>
+      <c r="T26" s="14" t="n">
         <f aca="false">IF(T6=0,0,T25/T6)</f>
-        <v>0.239052083333333</v>
-      </c>
-      <c r="U26" s="13" t="n">
+        <v>0.198936848958333</v>
+      </c>
+      <c r="U26" s="14" t="n">
         <f aca="false">IF(U6=0,0,U25/U6)</f>
-        <v>0.2503125</v>
-      </c>
-      <c r="V26" s="13" t="n">
+        <v>0.21230859375</v>
+      </c>
+      <c r="V26" s="14" t="n">
         <f aca="false">IF(V6=0,0,V25/V6)</f>
-        <v>0.260446875</v>
-      </c>
-      <c r="W26" s="13" t="n">
+        <v>0.2243431640625</v>
+      </c>
+      <c r="W26" s="14" t="n">
         <f aca="false">IF(W6=0,0,W25/W6)</f>
-        <v>0.2503125</v>
-      </c>
-      <c r="X26" s="13" t="n">
+        <v>0.2925390625</v>
+      </c>
+      <c r="X26" s="14" t="n">
         <f aca="false">IF(X6=0,0,X25/X6)</f>
-        <v>0.239052083333333</v>
-      </c>
-      <c r="Y26" s="13" t="n">
+        <v>0.283624565972222</v>
+      </c>
+      <c r="Y26" s="14" t="n">
         <f aca="false">IF(Y6=0,0,Y25/Y6)</f>
-        <v>0.260446875</v>
-      </c>
-      <c r="Z26" s="13" t="n">
+        <v>0.300562109375</v>
+      </c>
+      <c r="Z26" s="14" t="n">
         <f aca="false">IF(Z6=0,0,Z25/Z6)</f>
-        <v>0.269616071428571</v>
-      </c>
-      <c r="AA26" s="13" t="n">
+        <v>0.311641555059524</v>
+      </c>
+      <c r="AA26" s="14" t="n">
         <f aca="false">IF(AA6=0,0,AA25/AA6)</f>
-        <v>0.304882211538462</v>
-      </c>
-      <c r="AB26" s="13" t="n">
+        <v>0.338825871394231</v>
+      </c>
+      <c r="AB26" s="14" t="n">
         <f aca="false">IF(AB6=0,0,AB25/AB6)</f>
-        <v>0.310368055555556</v>
+        <v>0.343054542824074</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C28" s="7" t="n">
         <f aca="false">SUM(D28:O28)</f>
         <v>20000</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="E28" s="11" t="n">
+      <c r="E28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="G28" s="11" t="n">
+      <c r="G28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="H28" s="11" t="n">
+      <c r="H28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="I28" s="11" t="n">
+      <c r="I28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="J28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="M28" s="11" t="n">
+      <c r="M28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="N28" s="11" t="n">
+      <c r="N28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="O28" s="11" t="n">
+      <c r="O28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
@@ -5440,58 +5504,58 @@
         <f aca="false">SUM(Q28:AB28)</f>
         <v>20000</v>
       </c>
-      <c r="Q28" s="11" t="n">
+      <c r="Q28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="R28" s="11" t="n">
+      <c r="R28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="S28" s="11" t="n">
+      <c r="S28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="T28" s="11" t="n">
+      <c r="T28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="U28" s="11" t="n">
+      <c r="U28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="V28" s="11" t="n">
+      <c r="V28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="W28" s="11" t="n">
+      <c r="W28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="X28" s="11" t="n">
+      <c r="X28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="Y28" s="11" t="n">
+      <c r="Y28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="Z28" s="11" t="n">
+      <c r="Z28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="AA28" s="11" t="n">
+      <c r="AA28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
-      <c r="AB28" s="11" t="n">
+      <c r="AB28" s="12" t="n">
         <f aca="false">Assumptions!$C$19/12</f>
         <v>1666.66666666667</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C30" s="5" t="n">
         <f aca="false">SUM(D30:O30)</f>
@@ -5551,160 +5615,160 @@
       </c>
       <c r="Q30" s="5" t="n">
         <f aca="false">Q25-Q28</f>
-        <v>94581.7708333333</v>
+        <v>-9085.53685897435</v>
       </c>
       <c r="R30" s="5" t="n">
         <f aca="false">R25-R28</f>
-        <v>94581.7708333333</v>
+        <v>-9085.53685897435</v>
       </c>
       <c r="S30" s="5" t="n">
         <f aca="false">S25-S28</f>
-        <v>105906.770833333</v>
+        <v>-3858.61378205128</v>
       </c>
       <c r="T30" s="5" t="n">
         <f aca="false">T25-T28</f>
-        <v>105906.770833333</v>
+        <v>73719.9287280702</v>
       </c>
       <c r="U30" s="5" t="n">
         <f aca="false">U25-U28</f>
-        <v>117231.770833333</v>
+        <v>83256.7708333333</v>
       </c>
       <c r="V30" s="5" t="n">
         <f aca="false">V25-V28</f>
-        <v>128556.770833333</v>
+        <v>92793.6129385965</v>
       </c>
       <c r="W30" s="5" t="n">
         <f aca="false">W25-W28</f>
-        <v>117231.770833333</v>
+        <v>173856.770833333</v>
       </c>
       <c r="X30" s="5" t="n">
         <f aca="false">X25-X28</f>
-        <v>105906.770833333</v>
+        <v>159551.507675439</v>
       </c>
       <c r="Y30" s="5" t="n">
         <f aca="false">Y25-Y28</f>
-        <v>128556.770833333</v>
+        <v>188162.033991228</v>
       </c>
       <c r="Z30" s="5" t="n">
         <f aca="false">Z25-Z28</f>
-        <v>139881.770833333</v>
+        <v>210586.500563063</v>
       </c>
       <c r="AA30" s="5" t="n">
         <f aca="false">AA25-AA28</f>
-        <v>196506.770833333</v>
+        <v>284045.960022523</v>
       </c>
       <c r="AB30" s="5" t="n">
         <f aca="false">AB25-AB28</f>
-        <v>207831.770833333</v>
+        <v>298737.851914414</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="13" t="n">
+      <c r="B31" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="14" t="n">
         <f aca="false">IF(C6=0,0,C30/C6)</f>
         <v>0.230205882352941</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="14" t="n">
         <f aca="false">IF(D6=0,0,D30/D6)</f>
         <v>0.190889273356401</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="14" t="n">
         <f aca="false">IF(E6=0,0,E30/E6)</f>
         <v>0.190889273356401</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="14" t="n">
         <f aca="false">IF(F6=0,0,F30/F6)</f>
         <v>0.205450980392157</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="14" t="n">
         <f aca="false">IF(G6=0,0,G30/G6)</f>
         <v>0.205450980392157</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="14" t="n">
         <f aca="false">IF(H6=0,0,H30/H6)</f>
         <v>0.218479876160991</v>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="I31" s="14" t="n">
         <f aca="false">IF(I6=0,0,I30/I6)</f>
         <v>0.230205882352941</v>
       </c>
-      <c r="J31" s="13" t="n">
+      <c r="J31" s="14" t="n">
         <f aca="false">IF(J6=0,0,J30/J6)</f>
         <v>0.218479876160991</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="14" t="n">
         <f aca="false">IF(K6=0,0,K30/K6)</f>
         <v>0.205450980392157</v>
       </c>
-      <c r="L31" s="13" t="n">
+      <c r="L31" s="14" t="n">
         <f aca="false">IF(L6=0,0,L30/L6)</f>
         <v>0.230205882352941</v>
       </c>
-      <c r="M31" s="13" t="n">
+      <c r="M31" s="14" t="n">
         <f aca="false">IF(M6=0,0,M30/M6)</f>
         <v>0.24081512605042</v>
       </c>
-      <c r="N31" s="13" t="n">
+      <c r="N31" s="14" t="n">
         <f aca="false">IF(N6=0,0,N30/N6)</f>
         <v>0.281619909502262</v>
       </c>
-      <c r="O31" s="13" t="n">
+      <c r="O31" s="14" t="n">
         <f aca="false">IF(O6=0,0,O30/O6)</f>
         <v>0.287967320261438</v>
       </c>
-      <c r="P31" s="13" t="n">
+      <c r="P31" s="14" t="n">
         <f aca="false">IF(P6=0,0,P30/P6)</f>
         <v>0.257113541666667</v>
       </c>
-      <c r="Q31" s="13" t="n">
+      <c r="Q31" s="14" t="n">
         <f aca="false">IF(Q6=0,0,Q30/Q6)</f>
-        <v>0.222545343137255</v>
-      </c>
-      <c r="R31" s="13" t="n">
+        <v>-0.0463184232026144</v>
+      </c>
+      <c r="R31" s="14" t="n">
         <f aca="false">IF(R6=0,0,R30/R6)</f>
-        <v>0.222545343137255</v>
-      </c>
-      <c r="S31" s="13" t="n">
+        <v>-0.0463184232026144</v>
+      </c>
+      <c r="S31" s="14" t="n">
         <f aca="false">IF(S6=0,0,S30/S6)</f>
-        <v>0.23534837962963</v>
-      </c>
-      <c r="T31" s="13" t="n">
+        <v>-0.0185785108024691</v>
+      </c>
+      <c r="T31" s="14" t="n">
         <f aca="false">IF(T6=0,0,T30/T6)</f>
-        <v>0.23534837962963</v>
-      </c>
-      <c r="U31" s="13" t="n">
+        <v>0.194538700810185</v>
+      </c>
+      <c r="U31" s="14" t="n">
         <f aca="false">IF(U6=0,0,U30/U6)</f>
-        <v>0.246803728070175</v>
-      </c>
-      <c r="V31" s="13" t="n">
+        <v>0.208141927083333</v>
+      </c>
+      <c r="V31" s="14" t="n">
         <f aca="false">IF(V6=0,0,V30/V6)</f>
-        <v>0.257113541666667</v>
-      </c>
-      <c r="W31" s="13" t="n">
+        <v>0.220384830729167</v>
+      </c>
+      <c r="W31" s="14" t="n">
         <f aca="false">IF(W6=0,0,W30/W6)</f>
-        <v>0.246803728070175</v>
-      </c>
-      <c r="X31" s="13" t="n">
+        <v>0.289761284722222</v>
+      </c>
+      <c r="X31" s="14" t="n">
         <f aca="false">IF(X6=0,0,X30/X6)</f>
-        <v>0.23534837962963</v>
-      </c>
-      <c r="Y31" s="13" t="n">
+        <v>0.28069246720679</v>
+      </c>
+      <c r="Y31" s="14" t="n">
         <f aca="false">IF(Y6=0,0,Y30/Y6)</f>
-        <v>0.257113541666667</v>
-      </c>
-      <c r="Z31" s="13" t="n">
+        <v>0.297923220486111</v>
+      </c>
+      <c r="Z31" s="14" t="n">
         <f aca="false">IF(Z6=0,0,Z30/Z6)</f>
-        <v>0.266441468253968</v>
-      </c>
-      <c r="AA31" s="13" t="n">
+        <v>0.309194465112434</v>
+      </c>
+      <c r="AA31" s="14" t="n">
         <f aca="false">IF(AA6=0,0,AA30/AA6)</f>
-        <v>0.302318108974359</v>
-      </c>
-      <c r="AB31" s="13" t="n">
+        <v>0.336849375667735</v>
+      </c>
+      <c r="AB31" s="14" t="n">
         <f aca="false">IF(AB6=0,0,AB30/AB6)</f>
-        <v>0.307898919753087</v>
+        <v>0.341151250643004</v>
       </c>
     </row>
   </sheetData>
@@ -5733,23 +5797,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -5788,7 +5852,7 @@
         <v>40</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>29</v>
@@ -5829,7 +5893,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C6" s="5" t="n">
         <f aca="false">'USA PL'!C6+'Nigeria PL'!C6</f>
@@ -5889,56 +5953,56 @@
       </c>
       <c r="Q6" s="5" t="n">
         <f aca="false">'USA PL'!Q6+'Nigeria PL'!Q6</f>
-        <v>1062500</v>
+        <v>490384.615384615</v>
       </c>
       <c r="R6" s="5" t="n">
         <f aca="false">'USA PL'!R6+'Nigeria PL'!R6</f>
-        <v>1062500</v>
+        <v>490384.615384615</v>
       </c>
       <c r="S6" s="5" t="n">
         <f aca="false">'USA PL'!S6+'Nigeria PL'!S6</f>
-        <v>1125000</v>
+        <v>519230.769230769</v>
       </c>
       <c r="T6" s="5" t="n">
         <f aca="false">'USA PL'!T6+'Nigeria PL'!T6</f>
-        <v>1125000</v>
+        <v>947368.421052632</v>
       </c>
       <c r="U6" s="5" t="n">
         <f aca="false">'USA PL'!U6+'Nigeria PL'!U6</f>
-        <v>1187500</v>
+        <v>1000000</v>
       </c>
       <c r="V6" s="5" t="n">
         <f aca="false">'USA PL'!V6+'Nigeria PL'!V6</f>
-        <v>1250000</v>
+        <v>1052631.57894737</v>
       </c>
       <c r="W6" s="5" t="n">
         <f aca="false">'USA PL'!W6+'Nigeria PL'!W6</f>
-        <v>1187500</v>
+        <v>1500000</v>
       </c>
       <c r="X6" s="5" t="n">
         <f aca="false">'USA PL'!X6+'Nigeria PL'!X6</f>
-        <v>1125000</v>
+        <v>1421052.63157895</v>
       </c>
       <c r="Y6" s="5" t="n">
         <f aca="false">'USA PL'!Y6+'Nigeria PL'!Y6</f>
-        <v>1250000</v>
+        <v>1578947.36842105</v>
       </c>
       <c r="Z6" s="5" t="n">
         <f aca="false">'USA PL'!Z6+'Nigeria PL'!Z6</f>
-        <v>1312500</v>
+        <v>1702702.7027027</v>
       </c>
       <c r="AA6" s="5" t="n">
         <f aca="false">'USA PL'!AA6+'Nigeria PL'!AA6</f>
-        <v>1625000</v>
+        <v>2108108.10810811</v>
       </c>
       <c r="AB6" s="5" t="n">
         <f aca="false">'USA PL'!AB6+'Nigeria PL'!AB6</f>
-        <v>1687500</v>
+        <v>2189189.18918919</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">'USA PL'!C9+'Nigeria PL'!C9</f>
@@ -5998,56 +6062,56 @@
       </c>
       <c r="Q9" s="7" t="n">
         <f aca="false">'USA PL'!Q9+'Nigeria PL'!Q9</f>
-        <v>559937.5</v>
+        <v>258432.692307692</v>
       </c>
       <c r="R9" s="7" t="n">
         <f aca="false">'USA PL'!R9+'Nigeria PL'!R9</f>
-        <v>559937.5</v>
+        <v>258432.692307692</v>
       </c>
       <c r="S9" s="7" t="n">
         <f aca="false">'USA PL'!S9+'Nigeria PL'!S9</f>
-        <v>592875</v>
+        <v>273634.615384615</v>
       </c>
       <c r="T9" s="7" t="n">
         <f aca="false">'USA PL'!T9+'Nigeria PL'!T9</f>
-        <v>592875</v>
+        <v>499263.157894737</v>
       </c>
       <c r="U9" s="7" t="n">
         <f aca="false">'USA PL'!U9+'Nigeria PL'!U9</f>
-        <v>625812.5</v>
+        <v>527000</v>
       </c>
       <c r="V9" s="7" t="n">
         <f aca="false">'USA PL'!V9+'Nigeria PL'!V9</f>
-        <v>658750</v>
+        <v>554736.842105263</v>
       </c>
       <c r="W9" s="7" t="n">
         <f aca="false">'USA PL'!W9+'Nigeria PL'!W9</f>
-        <v>625812.5</v>
+        <v>790500</v>
       </c>
       <c r="X9" s="7" t="n">
         <f aca="false">'USA PL'!X9+'Nigeria PL'!X9</f>
-        <v>592875</v>
+        <v>748894.736842105</v>
       </c>
       <c r="Y9" s="7" t="n">
         <f aca="false">'USA PL'!Y9+'Nigeria PL'!Y9</f>
-        <v>658750</v>
+        <v>832105.263157895</v>
       </c>
       <c r="Z9" s="7" t="n">
         <f aca="false">'USA PL'!Z9+'Nigeria PL'!Z9</f>
-        <v>691687.5</v>
+        <v>897324.324324324</v>
       </c>
       <c r="AA9" s="7" t="n">
         <f aca="false">'USA PL'!AA9+'Nigeria PL'!AA9</f>
-        <v>856375</v>
+        <v>1110972.97297297</v>
       </c>
       <c r="AB9" s="7" t="n">
         <f aca="false">'USA PL'!AB9+'Nigeria PL'!AB9</f>
-        <v>889312.5</v>
+        <v>1153702.7027027</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">'USA PL'!C11+'Nigeria PL'!C11</f>
@@ -6107,170 +6171,170 @@
       </c>
       <c r="Q11" s="5" t="n">
         <f aca="false">'USA PL'!Q11+'Nigeria PL'!Q11</f>
-        <v>502562.5</v>
+        <v>231951.923076923</v>
       </c>
       <c r="R11" s="5" t="n">
         <f aca="false">'USA PL'!R11+'Nigeria PL'!R11</f>
-        <v>502562.5</v>
+        <v>231951.923076923</v>
       </c>
       <c r="S11" s="5" t="n">
         <f aca="false">'USA PL'!S11+'Nigeria PL'!S11</f>
-        <v>532125</v>
+        <v>245596.153846154</v>
       </c>
       <c r="T11" s="5" t="n">
         <f aca="false">'USA PL'!T11+'Nigeria PL'!T11</f>
-        <v>532125</v>
+        <v>448105.263157895</v>
       </c>
       <c r="U11" s="5" t="n">
         <f aca="false">'USA PL'!U11+'Nigeria PL'!U11</f>
-        <v>561687.5</v>
+        <v>473000</v>
       </c>
       <c r="V11" s="5" t="n">
         <f aca="false">'USA PL'!V11+'Nigeria PL'!V11</f>
-        <v>591250</v>
+        <v>497894.736842105</v>
       </c>
       <c r="W11" s="5" t="n">
         <f aca="false">'USA PL'!W11+'Nigeria PL'!W11</f>
-        <v>561687.5</v>
+        <v>709500</v>
       </c>
       <c r="X11" s="5" t="n">
         <f aca="false">'USA PL'!X11+'Nigeria PL'!X11</f>
-        <v>532125</v>
+        <v>672157.894736842</v>
       </c>
       <c r="Y11" s="5" t="n">
         <f aca="false">'USA PL'!Y11+'Nigeria PL'!Y11</f>
-        <v>591250</v>
+        <v>746842.105263158</v>
       </c>
       <c r="Z11" s="5" t="n">
         <f aca="false">'USA PL'!Z11+'Nigeria PL'!Z11</f>
-        <v>620812.5</v>
+        <v>805378.378378378</v>
       </c>
       <c r="AA11" s="5" t="n">
         <f aca="false">'USA PL'!AA11+'Nigeria PL'!AA11</f>
-        <v>768625</v>
+        <v>997135.135135135</v>
       </c>
       <c r="AB11" s="5" t="n">
         <f aca="false">'USA PL'!AB11+'Nigeria PL'!AB11</f>
-        <v>798187.5</v>
+        <v>1035486.48648649</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="13" t="n">
+      <c r="B12" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="14" t="n">
         <f aca="false">IF(C6=0,0,C11/C6)</f>
         <v>0.473</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <f aca="false">IF(D6=0,0,D11/D6)</f>
         <v>0.473</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <f aca="false">IF(E6=0,0,E11/E6)</f>
         <v>0.473</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="14" t="n">
         <f aca="false">IF(F6=0,0,F11/F6)</f>
         <v>0.473</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="14" t="n">
         <f aca="false">IF(G6=0,0,G11/G6)</f>
         <v>0.473</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="14" t="n">
         <f aca="false">IF(H6=0,0,H11/H6)</f>
         <v>0.473</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="14" t="n">
         <f aca="false">IF(I6=0,0,I11/I6)</f>
         <v>0.473</v>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="14" t="n">
         <f aca="false">IF(J6=0,0,J11/J6)</f>
         <v>0.473</v>
       </c>
-      <c r="K12" s="13" t="n">
+      <c r="K12" s="14" t="n">
         <f aca="false">IF(K6=0,0,K11/K6)</f>
         <v>0.473</v>
       </c>
-      <c r="L12" s="13" t="n">
+      <c r="L12" s="14" t="n">
         <f aca="false">IF(L6=0,0,L11/L6)</f>
         <v>0.473</v>
       </c>
-      <c r="M12" s="13" t="n">
+      <c r="M12" s="14" t="n">
         <f aca="false">IF(M6=0,0,M11/M6)</f>
         <v>0.473</v>
       </c>
-      <c r="N12" s="13" t="n">
+      <c r="N12" s="14" t="n">
         <f aca="false">IF(N6=0,0,N11/N6)</f>
         <v>0.473</v>
       </c>
-      <c r="O12" s="13" t="n">
+      <c r="O12" s="14" t="n">
         <f aca="false">IF(O6=0,0,O11/O6)</f>
         <v>0.473</v>
       </c>
-      <c r="P12" s="13" t="n">
+      <c r="P12" s="14" t="n">
         <f aca="false">IF(P6=0,0,P11/P6)</f>
         <v>0.473</v>
       </c>
-      <c r="Q12" s="13" t="n">
+      <c r="Q12" s="14" t="n">
         <f aca="false">IF(Q6=0,0,Q11/Q6)</f>
         <v>0.473</v>
       </c>
-      <c r="R12" s="13" t="n">
+      <c r="R12" s="14" t="n">
         <f aca="false">IF(R6=0,0,R11/R6)</f>
         <v>0.473</v>
       </c>
-      <c r="S12" s="13" t="n">
+      <c r="S12" s="14" t="n">
         <f aca="false">IF(S6=0,0,S11/S6)</f>
         <v>0.473</v>
       </c>
-      <c r="T12" s="13" t="n">
+      <c r="T12" s="14" t="n">
         <f aca="false">IF(T6=0,0,T11/T6)</f>
         <v>0.473</v>
       </c>
-      <c r="U12" s="13" t="n">
+      <c r="U12" s="14" t="n">
         <f aca="false">IF(U6=0,0,U11/U6)</f>
         <v>0.473</v>
       </c>
-      <c r="V12" s="13" t="n">
+      <c r="V12" s="14" t="n">
         <f aca="false">IF(V6=0,0,V11/V6)</f>
         <v>0.473</v>
       </c>
-      <c r="W12" s="13" t="n">
+      <c r="W12" s="14" t="n">
         <f aca="false">IF(W6=0,0,W11/W6)</f>
         <v>0.473</v>
       </c>
-      <c r="X12" s="13" t="n">
+      <c r="X12" s="14" t="n">
         <f aca="false">IF(X6=0,0,X11/X6)</f>
         <v>0.473</v>
       </c>
-      <c r="Y12" s="13" t="n">
+      <c r="Y12" s="14" t="n">
         <f aca="false">IF(Y6=0,0,Y11/Y6)</f>
         <v>0.473</v>
       </c>
-      <c r="Z12" s="13" t="n">
+      <c r="Z12" s="14" t="n">
         <f aca="false">IF(Z6=0,0,Z11/Z6)</f>
         <v>0.473</v>
       </c>
-      <c r="AA12" s="13" t="n">
+      <c r="AA12" s="14" t="n">
         <f aca="false">IF(AA6=0,0,AA11/AA6)</f>
         <v>0.473</v>
       </c>
-      <c r="AB12" s="13" t="n">
+      <c r="AB12" s="14" t="n">
         <f aca="false">IF(AB6=0,0,AB11/AB6)</f>
         <v>0.473</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">'USA PL'!C15+'Nigeria PL'!C15</f>
@@ -6379,7 +6443,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">'USA PL'!C16+'Nigeria PL'!C16</f>
@@ -6439,51 +6503,51 @@
       </c>
       <c r="Q16" s="7" t="n">
         <f aca="false">'USA PL'!Q16+'Nigeria PL'!Q16</f>
-        <v>21250</v>
+        <v>9807.69230769231</v>
       </c>
       <c r="R16" s="7" t="n">
         <f aca="false">'USA PL'!R16+'Nigeria PL'!R16</f>
-        <v>21250</v>
+        <v>9807.69230769231</v>
       </c>
       <c r="S16" s="7" t="n">
         <f aca="false">'USA PL'!S16+'Nigeria PL'!S16</f>
-        <v>22500</v>
+        <v>10384.6153846154</v>
       </c>
       <c r="T16" s="7" t="n">
         <f aca="false">'USA PL'!T16+'Nigeria PL'!T16</f>
-        <v>22500</v>
+        <v>18947.3684210526</v>
       </c>
       <c r="U16" s="7" t="n">
         <f aca="false">'USA PL'!U16+'Nigeria PL'!U16</f>
-        <v>23750</v>
+        <v>20000</v>
       </c>
       <c r="V16" s="7" t="n">
         <f aca="false">'USA PL'!V16+'Nigeria PL'!V16</f>
-        <v>25000</v>
+        <v>21052.6315789474</v>
       </c>
       <c r="W16" s="7" t="n">
         <f aca="false">'USA PL'!W16+'Nigeria PL'!W16</f>
-        <v>23750</v>
+        <v>30000</v>
       </c>
       <c r="X16" s="7" t="n">
         <f aca="false">'USA PL'!X16+'Nigeria PL'!X16</f>
-        <v>22500</v>
+        <v>28421.0526315789</v>
       </c>
       <c r="Y16" s="7" t="n">
         <f aca="false">'USA PL'!Y16+'Nigeria PL'!Y16</f>
-        <v>25000</v>
+        <v>31578.9473684211</v>
       </c>
       <c r="Z16" s="7" t="n">
         <f aca="false">'USA PL'!Z16+'Nigeria PL'!Z16</f>
-        <v>26250</v>
+        <v>34054.0540540541</v>
       </c>
       <c r="AA16" s="7" t="n">
         <f aca="false">'USA PL'!AA16+'Nigeria PL'!AA16</f>
-        <v>32500</v>
+        <v>42162.1621621622</v>
       </c>
       <c r="AB16" s="7" t="n">
         <f aca="false">'USA PL'!AB16+'Nigeria PL'!AB16</f>
-        <v>33750</v>
+        <v>43783.7837837838</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7142,7 +7206,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C23" s="5" t="n">
         <f aca="false">'USA PL'!C23+'Nigeria PL'!C23</f>
@@ -7202,56 +7266,56 @@
       </c>
       <c r="Q23" s="5" t="n">
         <f aca="false">'USA PL'!Q23+'Nigeria PL'!Q23</f>
-        <v>379403.125</v>
+        <v>367960.817307692</v>
       </c>
       <c r="R23" s="5" t="n">
         <f aca="false">'USA PL'!R23+'Nigeria PL'!R23</f>
-        <v>379403.125</v>
+        <v>367960.817307692</v>
       </c>
       <c r="S23" s="5" t="n">
         <f aca="false">'USA PL'!S23+'Nigeria PL'!S23</f>
-        <v>380653.125</v>
+        <v>368537.740384615</v>
       </c>
       <c r="T23" s="5" t="n">
         <f aca="false">'USA PL'!T23+'Nigeria PL'!T23</f>
-        <v>380653.125</v>
+        <v>377100.493421053</v>
       </c>
       <c r="U23" s="5" t="n">
         <f aca="false">'USA PL'!U23+'Nigeria PL'!U23</f>
-        <v>381903.125</v>
+        <v>378153.125</v>
       </c>
       <c r="V23" s="5" t="n">
         <f aca="false">'USA PL'!V23+'Nigeria PL'!V23</f>
-        <v>383153.125</v>
+        <v>379205.756578947</v>
       </c>
       <c r="W23" s="5" t="n">
         <f aca="false">'USA PL'!W23+'Nigeria PL'!W23</f>
-        <v>381903.125</v>
+        <v>388153.125</v>
       </c>
       <c r="X23" s="5" t="n">
         <f aca="false">'USA PL'!X23+'Nigeria PL'!X23</f>
-        <v>380653.125</v>
+        <v>386574.177631579</v>
       </c>
       <c r="Y23" s="5" t="n">
         <f aca="false">'USA PL'!Y23+'Nigeria PL'!Y23</f>
-        <v>383153.125</v>
+        <v>389732.072368421</v>
       </c>
       <c r="Z23" s="5" t="n">
         <f aca="false">'USA PL'!Z23+'Nigeria PL'!Z23</f>
-        <v>384403.125</v>
+        <v>392207.179054054</v>
       </c>
       <c r="AA23" s="5" t="n">
         <f aca="false">'USA PL'!AA23+'Nigeria PL'!AA23</f>
-        <v>390653.125</v>
+        <v>400315.287162162</v>
       </c>
       <c r="AB23" s="5" t="n">
         <f aca="false">'USA PL'!AB23+'Nigeria PL'!AB23</f>
-        <v>391903.125</v>
+        <v>401936.908783784</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C25" s="5" t="n">
         <f aca="false">'USA PL'!C25+'Nigeria PL'!C25</f>
@@ -7311,165 +7375,165 @@
       </c>
       <c r="Q25" s="5" t="n">
         <f aca="false">'USA PL'!Q25+'Nigeria PL'!Q25</f>
-        <v>123159.375</v>
+        <v>-136008.894230769</v>
       </c>
       <c r="R25" s="5" t="n">
         <f aca="false">'USA PL'!R25+'Nigeria PL'!R25</f>
-        <v>123159.375</v>
+        <v>-136008.894230769</v>
       </c>
       <c r="S25" s="5" t="n">
         <f aca="false">'USA PL'!S25+'Nigeria PL'!S25</f>
-        <v>151471.875</v>
+        <v>-122941.586538462</v>
       </c>
       <c r="T25" s="5" t="n">
         <f aca="false">'USA PL'!T25+'Nigeria PL'!T25</f>
-        <v>151471.875</v>
+        <v>71004.7697368421</v>
       </c>
       <c r="U25" s="5" t="n">
         <f aca="false">'USA PL'!U25+'Nigeria PL'!U25</f>
-        <v>179784.375</v>
+        <v>94846.8750000001</v>
       </c>
       <c r="V25" s="5" t="n">
         <f aca="false">'USA PL'!V25+'Nigeria PL'!V25</f>
-        <v>208096.875</v>
+        <v>118688.980263158</v>
       </c>
       <c r="W25" s="5" t="n">
         <f aca="false">'USA PL'!W25+'Nigeria PL'!W25</f>
-        <v>179784.375</v>
+        <v>321346.875</v>
       </c>
       <c r="X25" s="5" t="n">
         <f aca="false">'USA PL'!X25+'Nigeria PL'!X25</f>
-        <v>151471.875</v>
+        <v>285583.717105263</v>
       </c>
       <c r="Y25" s="5" t="n">
         <f aca="false">'USA PL'!Y25+'Nigeria PL'!Y25</f>
-        <v>208096.875</v>
+        <v>357110.032894737</v>
       </c>
       <c r="Z25" s="5" t="n">
         <f aca="false">'USA PL'!Z25+'Nigeria PL'!Z25</f>
-        <v>236409.375</v>
+        <v>413171.199324324</v>
       </c>
       <c r="AA25" s="5" t="n">
         <f aca="false">'USA PL'!AA25+'Nigeria PL'!AA25</f>
-        <v>377971.875</v>
+        <v>596819.847972973</v>
       </c>
       <c r="AB25" s="5" t="n">
         <f aca="false">'USA PL'!AB25+'Nigeria PL'!AB25</f>
-        <v>406284.375</v>
+        <v>633549.577702703</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="13" t="n">
+      <c r="B26" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="14" t="n">
         <f aca="false">IF(C6=0,0,C25/C6)</f>
         <v>0.132343629343629</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <f aca="false">IF(D6=0,0,D25/D6)</f>
         <v>0.0757572109925051</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="14" t="n">
         <f aca="false">IF(E6=0,0,E25/E6)</f>
         <v>0.0757572109925051</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="14" t="n">
         <f aca="false">IF(F6=0,0,F25/F6)</f>
         <v>0.0967151437151437</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="G26" s="14" t="n">
         <f aca="false">IF(G6=0,0,G25/G6)</f>
         <v>0.0967151437151437</v>
       </c>
-      <c r="H26" s="13" t="n">
+      <c r="H26" s="14" t="n">
         <f aca="false">IF(H6=0,0,H25/H6)</f>
         <v>0.115466978256452</v>
       </c>
-      <c r="I26" s="13" t="n">
+      <c r="I26" s="14" t="n">
         <f aca="false">IF(I6=0,0,I25/I6)</f>
         <v>0.132343629343629</v>
       </c>
-      <c r="J26" s="13" t="n">
+      <c r="J26" s="14" t="n">
         <f aca="false">IF(J6=0,0,J25/J6)</f>
         <v>0.115466978256452</v>
       </c>
-      <c r="K26" s="13" t="n">
+      <c r="K26" s="14" t="n">
         <f aca="false">IF(K6=0,0,K25/K6)</f>
         <v>0.0967151437151437</v>
       </c>
-      <c r="L26" s="13" t="n">
+      <c r="L26" s="14" t="n">
         <f aca="false">IF(L6=0,0,L25/L6)</f>
         <v>0.132343629343629</v>
       </c>
-      <c r="M26" s="13" t="n">
+      <c r="M26" s="14" t="n">
         <f aca="false">IF(M6=0,0,M25/M6)</f>
         <v>0.147612980327266</v>
       </c>
-      <c r="N26" s="13" t="n">
+      <c r="N26" s="14" t="n">
         <f aca="false">IF(N6=0,0,N25/N6)</f>
         <v>0.206341253341253</v>
       </c>
-      <c r="O26" s="13" t="n">
+      <c r="O26" s="14" t="n">
         <f aca="false">IF(O6=0,0,O25/O6)</f>
         <v>0.215476762476762</v>
       </c>
-      <c r="P26" s="13" t="n">
+      <c r="P26" s="14" t="n">
         <f aca="false">IF(P6=0,0,P25/P6)</f>
         <v>0.1664775</v>
       </c>
-      <c r="Q26" s="13" t="n">
+      <c r="Q26" s="14" t="n">
         <f aca="false">IF(Q6=0,0,Q25/Q6)</f>
-        <v>0.115914705882353</v>
-      </c>
-      <c r="R26" s="13" t="n">
+        <v>-0.277351470588235</v>
+      </c>
+      <c r="R26" s="14" t="n">
         <f aca="false">IF(R6=0,0,R25/R6)</f>
-        <v>0.115914705882353</v>
-      </c>
-      <c r="S26" s="13" t="n">
+        <v>-0.277351470588235</v>
+      </c>
+      <c r="S26" s="14" t="n">
         <f aca="false">IF(S6=0,0,S25/S6)</f>
-        <v>0.134641666666667</v>
-      </c>
-      <c r="T26" s="13" t="n">
+        <v>-0.236776388888889</v>
+      </c>
+      <c r="T26" s="14" t="n">
         <f aca="false">IF(T6=0,0,T25/T6)</f>
-        <v>0.134641666666667</v>
-      </c>
-      <c r="U26" s="13" t="n">
+        <v>0.0749494791666667</v>
+      </c>
+      <c r="U26" s="14" t="n">
         <f aca="false">IF(U6=0,0,U25/U6)</f>
-        <v>0.151397368421053</v>
-      </c>
-      <c r="V26" s="13" t="n">
+        <v>0.0948468750000001</v>
+      </c>
+      <c r="V26" s="14" t="n">
         <f aca="false">IF(V6=0,0,V25/V6)</f>
-        <v>0.1664775</v>
-      </c>
-      <c r="W26" s="13" t="n">
+        <v>0.11275453125</v>
+      </c>
+      <c r="W26" s="14" t="n">
         <f aca="false">IF(W6=0,0,W25/W6)</f>
-        <v>0.151397368421053</v>
-      </c>
-      <c r="X26" s="13" t="n">
+        <v>0.21423125</v>
+      </c>
+      <c r="X26" s="14" t="n">
         <f aca="false">IF(X6=0,0,X25/X6)</f>
-        <v>0.134641666666667</v>
-      </c>
-      <c r="Y26" s="13" t="n">
+        <v>0.200966319444444</v>
+      </c>
+      <c r="Y26" s="14" t="n">
         <f aca="false">IF(Y6=0,0,Y25/Y6)</f>
-        <v>0.1664775</v>
-      </c>
-      <c r="Z26" s="13" t="n">
+        <v>0.2261696875</v>
+      </c>
+      <c r="Z26" s="14" t="n">
         <f aca="false">IF(Z6=0,0,Z25/Z6)</f>
-        <v>0.180121428571429</v>
-      </c>
-      <c r="AA26" s="13" t="n">
+        <v>0.242656101190476</v>
+      </c>
+      <c r="AA26" s="14" t="n">
         <f aca="false">IF(AA6=0,0,AA25/AA6)</f>
-        <v>0.232598076923077</v>
-      </c>
-      <c r="AB26" s="13" t="n">
+        <v>0.283106850961539</v>
+      </c>
+      <c r="AB26" s="14" t="n">
         <f aca="false">IF(AB6=0,0,AB25/AB6)</f>
-        <v>0.240761111111111</v>
+        <v>0.289399189814815</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C28" s="7" t="n">
         <f aca="false">'USA PL'!C28+'Nigeria PL'!C28</f>
@@ -7578,7 +7642,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C30" s="5" t="n">
         <f aca="false">'USA PL'!C30+'Nigeria PL'!C30</f>
@@ -7638,160 +7702,160 @@
       </c>
       <c r="Q30" s="5" t="n">
         <f aca="false">'USA PL'!Q30+'Nigeria PL'!Q30</f>
-        <v>118159.375</v>
+        <v>-141008.894230769</v>
       </c>
       <c r="R30" s="5" t="n">
         <f aca="false">'USA PL'!R30+'Nigeria PL'!R30</f>
-        <v>118159.375</v>
+        <v>-141008.894230769</v>
       </c>
       <c r="S30" s="5" t="n">
         <f aca="false">'USA PL'!S30+'Nigeria PL'!S30</f>
-        <v>146471.875</v>
+        <v>-127941.586538462</v>
       </c>
       <c r="T30" s="5" t="n">
         <f aca="false">'USA PL'!T30+'Nigeria PL'!T30</f>
-        <v>146471.875</v>
+        <v>66004.7697368421</v>
       </c>
       <c r="U30" s="5" t="n">
         <f aca="false">'USA PL'!U30+'Nigeria PL'!U30</f>
-        <v>174784.375</v>
+        <v>89846.8750000001</v>
       </c>
       <c r="V30" s="5" t="n">
         <f aca="false">'USA PL'!V30+'Nigeria PL'!V30</f>
-        <v>203096.875</v>
+        <v>113688.980263158</v>
       </c>
       <c r="W30" s="5" t="n">
         <f aca="false">'USA PL'!W30+'Nigeria PL'!W30</f>
-        <v>174784.375</v>
+        <v>316346.875</v>
       </c>
       <c r="X30" s="5" t="n">
         <f aca="false">'USA PL'!X30+'Nigeria PL'!X30</f>
-        <v>146471.875</v>
+        <v>280583.717105263</v>
       </c>
       <c r="Y30" s="5" t="n">
         <f aca="false">'USA PL'!Y30+'Nigeria PL'!Y30</f>
-        <v>203096.875</v>
+        <v>352110.032894737</v>
       </c>
       <c r="Z30" s="5" t="n">
         <f aca="false">'USA PL'!Z30+'Nigeria PL'!Z30</f>
-        <v>231409.375</v>
+        <v>408171.199324324</v>
       </c>
       <c r="AA30" s="5" t="n">
         <f aca="false">'USA PL'!AA30+'Nigeria PL'!AA30</f>
-        <v>372971.875</v>
+        <v>591819.847972973</v>
       </c>
       <c r="AB30" s="5" t="n">
         <f aca="false">'USA PL'!AB30+'Nigeria PL'!AB30</f>
-        <v>401284.375</v>
+        <v>628549.577702703</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="13" t="n">
+      <c r="B31" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="14" t="n">
         <f aca="false">IF(C6=0,0,C30/C6)</f>
         <v>0.127710424710425</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="14" t="n">
         <f aca="false">IF(D6=0,0,D30/D6)</f>
         <v>0.0703063820122643</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="14" t="n">
         <f aca="false">IF(E6=0,0,E30/E6)</f>
         <v>0.0703063820122643</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="14" t="n">
         <f aca="false">IF(F6=0,0,F30/F6)</f>
         <v>0.0915671385671385</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="14" t="n">
         <f aca="false">IF(G6=0,0,G30/G6)</f>
         <v>0.0915671385671385</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="14" t="n">
         <f aca="false">IF(H6=0,0,H30/H6)</f>
         <v>0.110589920747815</v>
       </c>
-      <c r="I31" s="13" t="n">
+      <c r="I31" s="14" t="n">
         <f aca="false">IF(I6=0,0,I30/I6)</f>
         <v>0.127710424710425</v>
       </c>
-      <c r="J31" s="13" t="n">
+      <c r="J31" s="14" t="n">
         <f aca="false">IF(J6=0,0,J30/J6)</f>
         <v>0.110589920747815</v>
       </c>
-      <c r="K31" s="13" t="n">
+      <c r="K31" s="14" t="n">
         <f aca="false">IF(K6=0,0,K30/K6)</f>
         <v>0.0915671385671385</v>
       </c>
-      <c r="L31" s="13" t="n">
+      <c r="L31" s="14" t="n">
         <f aca="false">IF(L6=0,0,L30/L6)</f>
         <v>0.127710424710425</v>
       </c>
-      <c r="M31" s="13" t="n">
+      <c r="M31" s="14" t="n">
         <f aca="false">IF(M6=0,0,M30/M6)</f>
         <v>0.143200404486119</v>
       </c>
-      <c r="N31" s="13" t="n">
+      <c r="N31" s="14" t="n">
         <f aca="false">IF(N6=0,0,N30/N6)</f>
         <v>0.20277724977725</v>
       </c>
-      <c r="O31" s="13" t="n">
+      <c r="O31" s="14" t="n">
         <f aca="false">IF(O6=0,0,O30/O6)</f>
         <v>0.212044759044759</v>
       </c>
-      <c r="P31" s="13" t="n">
+      <c r="P31" s="14" t="n">
         <f aca="false">IF(P6=0,0,P30/P6)</f>
         <v>0.1624775</v>
       </c>
-      <c r="Q31" s="13" t="n">
+      <c r="Q31" s="14" t="n">
         <f aca="false">IF(Q6=0,0,Q30/Q6)</f>
-        <v>0.111208823529412</v>
-      </c>
-      <c r="R31" s="13" t="n">
+        <v>-0.287547549019608</v>
+      </c>
+      <c r="R31" s="14" t="n">
         <f aca="false">IF(R6=0,0,R30/R6)</f>
-        <v>0.111208823529412</v>
-      </c>
-      <c r="S31" s="13" t="n">
+        <v>-0.287547549019608</v>
+      </c>
+      <c r="S31" s="14" t="n">
         <f aca="false">IF(S6=0,0,S30/S6)</f>
-        <v>0.130197222222222</v>
-      </c>
-      <c r="T31" s="13" t="n">
+        <v>-0.246406018518519</v>
+      </c>
+      <c r="T31" s="14" t="n">
         <f aca="false">IF(T6=0,0,T30/T6)</f>
-        <v>0.130197222222222</v>
-      </c>
-      <c r="U31" s="13" t="n">
+        <v>0.0696717013888889</v>
+      </c>
+      <c r="U31" s="14" t="n">
         <f aca="false">IF(U6=0,0,U30/U6)</f>
-        <v>0.147186842105263</v>
-      </c>
-      <c r="V31" s="13" t="n">
+        <v>0.0898468750000001</v>
+      </c>
+      <c r="V31" s="14" t="n">
         <f aca="false">IF(V6=0,0,V30/V6)</f>
-        <v>0.1624775</v>
-      </c>
-      <c r="W31" s="13" t="n">
+        <v>0.10800453125</v>
+      </c>
+      <c r="W31" s="14" t="n">
         <f aca="false">IF(W6=0,0,W30/W6)</f>
-        <v>0.147186842105263</v>
-      </c>
-      <c r="X31" s="13" t="n">
+        <v>0.210897916666667</v>
+      </c>
+      <c r="X31" s="14" t="n">
         <f aca="false">IF(X6=0,0,X30/X6)</f>
-        <v>0.130197222222222</v>
-      </c>
-      <c r="Y31" s="13" t="n">
+        <v>0.197447800925926</v>
+      </c>
+      <c r="Y31" s="14" t="n">
         <f aca="false">IF(Y6=0,0,Y30/Y6)</f>
-        <v>0.1624775</v>
-      </c>
-      <c r="Z31" s="13" t="n">
+        <v>0.223003020833333</v>
+      </c>
+      <c r="Z31" s="14" t="n">
         <f aca="false">IF(Z6=0,0,Z30/Z6)</f>
-        <v>0.176311904761905</v>
-      </c>
-      <c r="AA31" s="13" t="n">
+        <v>0.239719593253968</v>
+      </c>
+      <c r="AA31" s="14" t="n">
         <f aca="false">IF(AA6=0,0,AA30/AA6)</f>
-        <v>0.229521153846154</v>
-      </c>
-      <c r="AB31" s="13" t="n">
+        <v>0.280735056089744</v>
+      </c>
+      <c r="AB31" s="14" t="n">
         <f aca="false">IF(AB6=0,0,AB30/AB6)</f>
-        <v>0.237798148148148</v>
+        <v>0.287115239197531</v>
       </c>
     </row>
   </sheetData>
@@ -7820,86 +7884,86 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7909,10 +7973,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="11" t="n">
-        <f aca="false">Assumptions!$C$38</f>
+        <v>124</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <f aca="false">Assumptions!$C$43</f>
         <v>2200000</v>
       </c>
       <c r="D6" s="7" t="n">
@@ -7965,355 +8029,355 @@
       </c>
       <c r="P6" s="7" t="n">
         <f aca="false">O11</f>
-        <v>2665252.60416667</v>
+        <v>2853020.87339744</v>
       </c>
       <c r="Q6" s="7" t="n">
         <f aca="false">P11</f>
-        <v>2692163.54166667</v>
+        <v>2724430.84935897</v>
       </c>
       <c r="R6" s="7" t="n">
         <f aca="false">Q11</f>
-        <v>2698561.97916667</v>
+        <v>2586373.5176282</v>
       </c>
       <c r="S6" s="7" t="n">
         <f aca="false">R11</f>
-        <v>2742460.41666667</v>
+        <v>2325109.10087719</v>
       </c>
       <c r="T6" s="7" t="n">
         <f aca="false">S11</f>
-        <v>2765846.35416667</v>
+        <v>2303453.59100877</v>
       </c>
       <c r="U6" s="7" t="n">
         <f aca="false">T11</f>
-        <v>2806219.79166667</v>
+        <v>2296103.34429825</v>
       </c>
       <c r="V6" s="7" t="n">
         <f aca="false">U11</f>
-        <v>2904605.72916667</v>
+        <v>2173505.72916667</v>
       </c>
       <c r="W6" s="7" t="n">
         <f aca="false">V11</f>
-        <v>2986004.16666667</v>
+        <v>2345239.69298246</v>
       </c>
       <c r="X6" s="7" t="n">
         <f aca="false">W11</f>
-        <v>2988877.60416667</v>
+        <v>2417784.18311403</v>
       </c>
       <c r="Y6" s="7" t="n">
         <f aca="false">X11</f>
-        <v>3046238.54166667</v>
+        <v>2544449.01463964</v>
       </c>
       <c r="Z6" s="7" t="n">
         <f aca="false">Y11</f>
-        <v>3038536.97916667</v>
+        <v>2612312.99268018</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="C7" s="12" t="n">
         <f aca="false">'USA PL'!D6</f>
         <v>556041.666666667</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="12" t="n">
         <f aca="false">'USA PL'!D6</f>
         <v>556041.666666667</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <f aca="false">'USA PL'!E6</f>
         <v>556041.666666667</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <f aca="false">'USA PL'!F6</f>
         <v>588750</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="12" t="n">
         <f aca="false">'USA PL'!G6</f>
         <v>588750</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="12" t="n">
         <f aca="false">'USA PL'!H6</f>
         <v>621458.333333333</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="12" t="n">
         <f aca="false">'USA PL'!I6</f>
         <v>654166.666666667</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="12" t="n">
         <f aca="false">'USA PL'!J6</f>
         <v>621458.333333333</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="12" t="n">
         <f aca="false">'USA PL'!K6</f>
         <v>588750</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="12" t="n">
         <f aca="false">'USA PL'!L6</f>
         <v>654166.666666667</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="12" t="n">
         <f aca="false">'USA PL'!M6</f>
         <v>686875</v>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="N7" s="12" t="n">
         <f aca="false">'USA PL'!N6</f>
         <v>850416.666666667</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="O7" s="12" t="n">
         <f aca="false">'USA PL'!O6</f>
         <v>883125</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="12" t="n">
         <f aca="false">'USA PL'!Q6</f>
-        <v>637500</v>
-      </c>
-      <c r="Q7" s="11" t="n">
+        <v>294230.769230769</v>
+      </c>
+      <c r="Q7" s="12" t="n">
         <f aca="false">'USA PL'!R6</f>
-        <v>637500</v>
-      </c>
-      <c r="R7" s="11" t="n">
+        <v>294230.769230769</v>
+      </c>
+      <c r="R7" s="12" t="n">
         <f aca="false">'USA PL'!S6</f>
-        <v>675000</v>
-      </c>
-      <c r="S7" s="11" t="n">
+        <v>311538.461538462</v>
+      </c>
+      <c r="S7" s="12" t="n">
         <f aca="false">'USA PL'!T6</f>
-        <v>675000</v>
-      </c>
-      <c r="T7" s="11" t="n">
+        <v>568421.052631579</v>
+      </c>
+      <c r="T7" s="12" t="n">
         <f aca="false">'USA PL'!U6</f>
-        <v>712500</v>
-      </c>
-      <c r="U7" s="11" t="n">
+        <v>600000</v>
+      </c>
+      <c r="U7" s="12" t="n">
         <f aca="false">'USA PL'!V6</f>
-        <v>750000</v>
-      </c>
-      <c r="V7" s="11" t="n">
+        <v>631578.947368421</v>
+      </c>
+      <c r="V7" s="12" t="n">
         <f aca="false">'USA PL'!W6</f>
-        <v>712500</v>
-      </c>
-      <c r="W7" s="11" t="n">
+        <v>900000</v>
+      </c>
+      <c r="W7" s="12" t="n">
         <f aca="false">'USA PL'!X6</f>
-        <v>675000</v>
-      </c>
-      <c r="X7" s="11" t="n">
+        <v>852631.578947368</v>
+      </c>
+      <c r="X7" s="12" t="n">
         <f aca="false">'USA PL'!Y6</f>
-        <v>750000</v>
-      </c>
-      <c r="Y7" s="11" t="n">
+        <v>947368.421052632</v>
+      </c>
+      <c r="Y7" s="12" t="n">
         <f aca="false">'USA PL'!Z6</f>
-        <v>787500</v>
-      </c>
-      <c r="Z7" s="11" t="n">
+        <v>1021621.62162162</v>
+      </c>
+      <c r="Z7" s="12" t="n">
         <f aca="false">'USA PL'!AA6</f>
-        <v>975000</v>
+        <v>1264864.86486486</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="11" t="n">
+        <v>126</v>
+      </c>
+      <c r="C8" s="12" t="n">
         <f aca="false">'USA PL'!D9</f>
         <v>293033.958333333</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="12" t="n">
         <f aca="false">'USA PL'!E9</f>
         <v>293033.958333333</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="12" t="n">
         <f aca="false">'USA PL'!F9</f>
         <v>310271.25</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="12" t="n">
         <f aca="false">'USA PL'!G9</f>
         <v>310271.25</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="12" t="n">
         <f aca="false">'USA PL'!H9</f>
         <v>327508.541666667</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="12" t="n">
         <f aca="false">'USA PL'!I9</f>
         <v>344745.833333333</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="12" t="n">
         <f aca="false">'USA PL'!J9</f>
         <v>327508.541666667</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="12" t="n">
         <f aca="false">'USA PL'!K9</f>
         <v>310271.25</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="12" t="n">
         <f aca="false">'USA PL'!L9</f>
         <v>344745.833333333</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="12" t="n">
         <f aca="false">'USA PL'!M9</f>
         <v>361983.125</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="12" t="n">
         <f aca="false">'USA PL'!N9</f>
         <v>448169.583333333</v>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="N8" s="12" t="n">
         <f aca="false">'USA PL'!O9</f>
         <v>465406.875</v>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="O8" s="12" t="n">
         <f aca="false">'USA PL'!Q9</f>
-        <v>335962.5</v>
-      </c>
-      <c r="P8" s="11" t="n">
+        <v>155059.615384615</v>
+      </c>
+      <c r="P8" s="12" t="n">
         <f aca="false">'USA PL'!R9</f>
-        <v>335962.5</v>
-      </c>
-      <c r="Q8" s="11" t="n">
+        <v>155059.615384615</v>
+      </c>
+      <c r="Q8" s="12" t="n">
         <f aca="false">'USA PL'!S9</f>
-        <v>355725</v>
-      </c>
-      <c r="R8" s="11" t="n">
+        <v>164180.769230769</v>
+      </c>
+      <c r="R8" s="12" t="n">
         <f aca="false">'USA PL'!T9</f>
-        <v>355725</v>
-      </c>
-      <c r="S8" s="11" t="n">
+        <v>299557.894736842</v>
+      </c>
+      <c r="S8" s="12" t="n">
         <f aca="false">'USA PL'!U9</f>
-        <v>375487.5</v>
-      </c>
-      <c r="T8" s="11" t="n">
+        <v>316200</v>
+      </c>
+      <c r="T8" s="12" t="n">
         <f aca="false">'USA PL'!V9</f>
-        <v>395250</v>
-      </c>
-      <c r="U8" s="11" t="n">
+        <v>332842.105263158</v>
+      </c>
+      <c r="U8" s="12" t="n">
         <f aca="false">'USA PL'!W9</f>
-        <v>375487.5</v>
-      </c>
-      <c r="V8" s="11" t="n">
+        <v>474300</v>
+      </c>
+      <c r="V8" s="12" t="n">
         <f aca="false">'USA PL'!X9</f>
-        <v>355725</v>
-      </c>
-      <c r="W8" s="11" t="n">
+        <v>449336.842105263</v>
+      </c>
+      <c r="W8" s="12" t="n">
         <f aca="false">'USA PL'!Y9</f>
-        <v>395250</v>
-      </c>
-      <c r="X8" s="11" t="n">
+        <v>499263.157894737</v>
+      </c>
+      <c r="X8" s="12" t="n">
         <f aca="false">'USA PL'!Z9</f>
-        <v>415012.5</v>
-      </c>
-      <c r="Y8" s="11" t="n">
+        <v>538394.594594595</v>
+      </c>
+      <c r="Y8" s="12" t="n">
         <f aca="false">'USA PL'!AA9</f>
-        <v>513825</v>
-      </c>
-      <c r="Z8" s="11" t="n">
+        <v>666583.783783784</v>
+      </c>
+      <c r="Z8" s="12" t="n">
         <f aca="false">'USA PL'!AB9</f>
-        <v>533587.5</v>
+        <v>692221.621621622</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="11" t="n">
+        <v>127</v>
+      </c>
+      <c r="C9" s="12" t="n">
         <f aca="false">'USA PL'!D23</f>
         <v>264141.666666667</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="12" t="n">
         <f aca="false">'USA PL'!E23</f>
         <v>264141.666666667</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="12" t="n">
         <f aca="false">'USA PL'!F23</f>
         <v>264795.833333333</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="12" t="n">
         <f aca="false">'USA PL'!G23</f>
         <v>264795.833333333</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="12" t="n">
         <f aca="false">'USA PL'!H23</f>
         <v>265450</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="12" t="n">
         <f aca="false">'USA PL'!I23</f>
         <v>266104.166666667</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="12" t="n">
         <f aca="false">'USA PL'!J23</f>
         <v>265450</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="12" t="n">
         <f aca="false">'USA PL'!K23</f>
         <v>264795.833333333</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="12" t="n">
         <f aca="false">'USA PL'!L23</f>
         <v>266104.166666667</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="12" t="n">
         <f aca="false">'USA PL'!M23</f>
         <v>266758.333333333</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="12" t="n">
         <f aca="false">'USA PL'!N23</f>
         <v>270029.166666667</v>
       </c>
-      <c r="N9" s="11" t="n">
+      <c r="N9" s="12" t="n">
         <f aca="false">'USA PL'!O23</f>
         <v>270683.333333333</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="12" t="n">
         <f aca="false">'USA PL'!Q23</f>
-        <v>274626.5625</v>
-      </c>
-      <c r="P9" s="11" t="n">
+        <v>267761.177884615</v>
+      </c>
+      <c r="P9" s="12" t="n">
         <f aca="false">'USA PL'!R23</f>
-        <v>274626.5625</v>
-      </c>
-      <c r="Q9" s="11" t="n">
+        <v>267761.177884615</v>
+      </c>
+      <c r="Q9" s="12" t="n">
         <f aca="false">'USA PL'!S23</f>
-        <v>275376.5625</v>
-      </c>
-      <c r="R9" s="11" t="n">
+        <v>268107.331730769</v>
+      </c>
+      <c r="R9" s="12" t="n">
         <f aca="false">'USA PL'!T23</f>
-        <v>275376.5625</v>
-      </c>
-      <c r="S9" s="11" t="n">
+        <v>273244.983552632</v>
+      </c>
+      <c r="S9" s="12" t="n">
         <f aca="false">'USA PL'!U23</f>
-        <v>276126.5625</v>
-      </c>
-      <c r="T9" s="11" t="n">
+        <v>273876.5625</v>
+      </c>
+      <c r="T9" s="12" t="n">
         <f aca="false">'USA PL'!V23</f>
-        <v>276876.5625</v>
-      </c>
-      <c r="U9" s="11" t="n">
+        <v>274508.141447368</v>
+      </c>
+      <c r="U9" s="12" t="n">
         <f aca="false">'USA PL'!W23</f>
-        <v>276126.5625</v>
-      </c>
-      <c r="V9" s="11" t="n">
+        <v>279876.5625</v>
+      </c>
+      <c r="V9" s="12" t="n">
         <f aca="false">'USA PL'!X23</f>
-        <v>275376.5625</v>
-      </c>
-      <c r="W9" s="11" t="n">
+        <v>278929.194078947</v>
+      </c>
+      <c r="W9" s="12" t="n">
         <f aca="false">'USA PL'!Y23</f>
-        <v>276876.5625</v>
-      </c>
-      <c r="X9" s="11" t="n">
+        <v>280823.930921053</v>
+      </c>
+      <c r="X9" s="12" t="n">
         <f aca="false">'USA PL'!Z23</f>
-        <v>277626.5625</v>
-      </c>
-      <c r="Y9" s="11" t="n">
+        <v>282308.994932432</v>
+      </c>
+      <c r="Y9" s="12" t="n">
         <f aca="false">'USA PL'!AA23</f>
-        <v>281376.5625</v>
-      </c>
-      <c r="Z9" s="11" t="n">
+        <v>287173.859797297</v>
+      </c>
+      <c r="Z9" s="12" t="n">
         <f aca="false">'USA PL'!AB23</f>
-        <v>282126.5625</v>
+        <v>288146.83277027</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C10" s="5" t="n">
         <f aca="false">C7-C8-C9</f>
@@ -8365,56 +8429,56 @@
       </c>
       <c r="O10" s="5" t="n">
         <f aca="false">O7-O8-O9</f>
-        <v>272535.9375</v>
+        <v>460304.206730769</v>
       </c>
       <c r="P10" s="5" t="n">
         <f aca="false">P7-P8-P9</f>
-        <v>26910.9375000001</v>
+        <v>-128590.024038462</v>
       </c>
       <c r="Q10" s="5" t="n">
         <f aca="false">Q7-Q8-Q9</f>
-        <v>6398.43750000006</v>
+        <v>-138057.331730769</v>
       </c>
       <c r="R10" s="5" t="n">
         <f aca="false">R7-R8-R9</f>
-        <v>43898.4375000001</v>
+        <v>-261264.416751012</v>
       </c>
       <c r="S10" s="5" t="n">
         <f aca="false">S7-S8-S9</f>
-        <v>23385.9375000001</v>
+        <v>-21655.5098684211</v>
       </c>
       <c r="T10" s="5" t="n">
         <f aca="false">T7-T8-T9</f>
-        <v>40373.4375000001</v>
+        <v>-7350.24671052623</v>
       </c>
       <c r="U10" s="5" t="n">
         <f aca="false">U7-U8-U9</f>
-        <v>98385.9375000001</v>
+        <v>-122597.615131579</v>
       </c>
       <c r="V10" s="5" t="n">
         <f aca="false">V7-V8-V9</f>
-        <v>81398.4375000001</v>
+        <v>171733.963815789</v>
       </c>
       <c r="W10" s="5" t="n">
         <f aca="false">W7-W8-W9</f>
-        <v>2873.43750000006</v>
+        <v>72544.490131579</v>
       </c>
       <c r="X10" s="5" t="n">
         <f aca="false">X7-X8-X9</f>
-        <v>57360.9375000001</v>
+        <v>126664.831525605</v>
       </c>
       <c r="Y10" s="5" t="n">
         <f aca="false">Y7-Y8-Y9</f>
-        <v>-7701.56249999994</v>
+        <v>67863.9780405405</v>
       </c>
       <c r="Z10" s="5" t="n">
         <f aca="false">Z7-Z8-Z9</f>
-        <v>159285.9375</v>
+        <v>284496.410472973</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">C6+C10</f>
@@ -8466,51 +8530,51 @@
       </c>
       <c r="O11" s="5" t="n">
         <f aca="false">O6+O10</f>
-        <v>2665252.60416667</v>
+        <v>2853020.87339744</v>
       </c>
       <c r="P11" s="5" t="n">
         <f aca="false">P6+P10</f>
-        <v>2692163.54166667</v>
+        <v>2724430.84935897</v>
       </c>
       <c r="Q11" s="5" t="n">
         <f aca="false">Q6+Q10</f>
-        <v>2698561.97916667</v>
+        <v>2586373.5176282</v>
       </c>
       <c r="R11" s="5" t="n">
         <f aca="false">R6+R10</f>
-        <v>2742460.41666667</v>
+        <v>2325109.10087719</v>
       </c>
       <c r="S11" s="5" t="n">
         <f aca="false">S6+S10</f>
-        <v>2765846.35416667</v>
+        <v>2303453.59100877</v>
       </c>
       <c r="T11" s="5" t="n">
         <f aca="false">T6+T10</f>
-        <v>2806219.79166667</v>
+        <v>2296103.34429825</v>
       </c>
       <c r="U11" s="5" t="n">
         <f aca="false">U6+U10</f>
-        <v>2904605.72916667</v>
+        <v>2173505.72916667</v>
       </c>
       <c r="V11" s="5" t="n">
         <f aca="false">V6+V10</f>
-        <v>2986004.16666667</v>
+        <v>2345239.69298246</v>
       </c>
       <c r="W11" s="5" t="n">
         <f aca="false">W6+W10</f>
-        <v>2988877.60416667</v>
+        <v>2417784.18311403</v>
       </c>
       <c r="X11" s="5" t="n">
         <f aca="false">X6+X10</f>
-        <v>3046238.54166667</v>
+        <v>2544449.01463964</v>
       </c>
       <c r="Y11" s="5" t="n">
         <f aca="false">Y6+Y10</f>
-        <v>3038536.97916667</v>
+        <v>2612312.99268018</v>
       </c>
       <c r="Z11" s="5" t="n">
         <f aca="false">Z6+Z10</f>
-        <v>3197822.91666667</v>
+        <v>2896809.40315315</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8520,10 +8584,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="11" t="n">
-        <f aca="false">Assumptions!$C$39</f>
+        <v>124</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <f aca="false">Assumptions!$C$44</f>
         <v>2200000</v>
       </c>
       <c r="D14" s="7" t="n">
@@ -8576,355 +8640,355 @@
       </c>
       <c r="P14" s="7" t="n">
         <f aca="false">O19</f>
-        <v>3426548.4375</v>
+        <v>3551727.28365384</v>
       </c>
       <c r="Q14" s="7" t="n">
         <f aca="false">P19</f>
-        <v>3522796.875</v>
+        <v>3544308.41346154</v>
       </c>
       <c r="R14" s="7" t="n">
         <f aca="false">Q19</f>
-        <v>3605370.3125</v>
+        <v>3530578.00480769</v>
       </c>
       <c r="S14" s="7" t="n">
         <f aca="false">R19</f>
-        <v>3712943.75</v>
+        <v>3434709.53947368</v>
       </c>
       <c r="T14" s="7" t="n">
         <f aca="false">S19</f>
-        <v>3806842.1875</v>
+        <v>3498580.34539474</v>
       </c>
       <c r="U14" s="7" t="n">
         <f aca="false">T19</f>
-        <v>3912065.625</v>
+        <v>3571987.99342105</v>
       </c>
       <c r="V14" s="7" t="n">
         <f aca="false">U19</f>
-        <v>4055964.0625</v>
+        <v>3568564.0625</v>
       </c>
       <c r="W14" s="7" t="n">
         <f aca="false">V19</f>
-        <v>4188537.5</v>
+        <v>3761361.18421053</v>
       </c>
       <c r="X14" s="7" t="n">
         <f aca="false">W19</f>
-        <v>4268760.9375</v>
+        <v>3888031.99013158</v>
       </c>
       <c r="Y14" s="7" t="n">
         <f aca="false">X19</f>
-        <v>4385309.375</v>
+        <v>4050783.02364865</v>
       </c>
       <c r="Z14" s="7" t="n">
         <f aca="false">Y19</f>
-        <v>4458482.8125</v>
+        <v>4174333.48817567</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="C15" s="12" t="n">
         <f aca="false">'Nigeria PL'!D6</f>
         <v>361250</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="12" t="n">
         <f aca="false">'Nigeria PL'!D6</f>
         <v>361250</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <f aca="false">'Nigeria PL'!E6</f>
         <v>361250</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <f aca="false">'Nigeria PL'!F6</f>
         <v>382500</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="12" t="n">
         <f aca="false">'Nigeria PL'!G6</f>
         <v>382500</v>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="H15" s="12" t="n">
         <f aca="false">'Nigeria PL'!H6</f>
         <v>403750</v>
       </c>
-      <c r="I15" s="11" t="n">
+      <c r="I15" s="12" t="n">
         <f aca="false">'Nigeria PL'!I6</f>
         <v>425000</v>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J15" s="12" t="n">
         <f aca="false">'Nigeria PL'!J6</f>
         <v>403750</v>
       </c>
-      <c r="K15" s="11" t="n">
+      <c r="K15" s="12" t="n">
         <f aca="false">'Nigeria PL'!K6</f>
         <v>382500</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" s="12" t="n">
         <f aca="false">'Nigeria PL'!L6</f>
         <v>425000</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="M15" s="12" t="n">
         <f aca="false">'Nigeria PL'!M6</f>
         <v>446250</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="N15" s="12" t="n">
         <f aca="false">'Nigeria PL'!N6</f>
         <v>552500</v>
       </c>
-      <c r="O15" s="11" t="n">
+      <c r="O15" s="12" t="n">
         <f aca="false">'Nigeria PL'!O6</f>
         <v>573750</v>
       </c>
-      <c r="P15" s="11" t="n">
+      <c r="P15" s="12" t="n">
         <f aca="false">'Nigeria PL'!Q6</f>
-        <v>425000</v>
-      </c>
-      <c r="Q15" s="11" t="n">
+        <v>196153.846153846</v>
+      </c>
+      <c r="Q15" s="12" t="n">
         <f aca="false">'Nigeria PL'!R6</f>
-        <v>425000</v>
-      </c>
-      <c r="R15" s="11" t="n">
+        <v>196153.846153846</v>
+      </c>
+      <c r="R15" s="12" t="n">
         <f aca="false">'Nigeria PL'!S6</f>
-        <v>450000</v>
-      </c>
-      <c r="S15" s="11" t="n">
+        <v>207692.307692308</v>
+      </c>
+      <c r="S15" s="12" t="n">
         <f aca="false">'Nigeria PL'!T6</f>
-        <v>450000</v>
-      </c>
-      <c r="T15" s="11" t="n">
+        <v>378947.368421053</v>
+      </c>
+      <c r="T15" s="12" t="n">
         <f aca="false">'Nigeria PL'!U6</f>
-        <v>475000</v>
-      </c>
-      <c r="U15" s="11" t="n">
+        <v>400000</v>
+      </c>
+      <c r="U15" s="12" t="n">
         <f aca="false">'Nigeria PL'!V6</f>
-        <v>500000</v>
-      </c>
-      <c r="V15" s="11" t="n">
+        <v>421052.631578947</v>
+      </c>
+      <c r="V15" s="12" t="n">
         <f aca="false">'Nigeria PL'!W6</f>
-        <v>475000</v>
-      </c>
-      <c r="W15" s="11" t="n">
+        <v>600000</v>
+      </c>
+      <c r="W15" s="12" t="n">
         <f aca="false">'Nigeria PL'!X6</f>
-        <v>450000</v>
-      </c>
-      <c r="X15" s="11" t="n">
+        <v>568421.052631579</v>
+      </c>
+      <c r="X15" s="12" t="n">
         <f aca="false">'Nigeria PL'!Y6</f>
-        <v>500000</v>
-      </c>
-      <c r="Y15" s="11" t="n">
+        <v>631578.947368421</v>
+      </c>
+      <c r="Y15" s="12" t="n">
         <f aca="false">'Nigeria PL'!Z6</f>
-        <v>525000</v>
-      </c>
-      <c r="Z15" s="11" t="n">
+        <v>681081.081081081</v>
+      </c>
+      <c r="Z15" s="12" t="n">
         <f aca="false">'Nigeria PL'!AA6</f>
-        <v>650000</v>
+        <v>843243.243243243</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="11" t="n">
+        <v>126</v>
+      </c>
+      <c r="C16" s="12" t="n">
         <f aca="false">'Nigeria PL'!D9</f>
         <v>190378.75</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="12" t="n">
         <f aca="false">'Nigeria PL'!E9</f>
         <v>190378.75</v>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="12" t="n">
         <f aca="false">'Nigeria PL'!F9</f>
         <v>201577.5</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <f aca="false">'Nigeria PL'!G9</f>
         <v>201577.5</v>
       </c>
-      <c r="G16" s="11" t="n">
+      <c r="G16" s="12" t="n">
         <f aca="false">'Nigeria PL'!H9</f>
         <v>212776.25</v>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="12" t="n">
         <f aca="false">'Nigeria PL'!I9</f>
         <v>223975</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" s="12" t="n">
         <f aca="false">'Nigeria PL'!J9</f>
         <v>212776.25</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="12" t="n">
         <f aca="false">'Nigeria PL'!K9</f>
         <v>201577.5</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="12" t="n">
         <f aca="false">'Nigeria PL'!L9</f>
         <v>223975</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" s="12" t="n">
         <f aca="false">'Nigeria PL'!M9</f>
         <v>235173.75</v>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="M16" s="12" t="n">
         <f aca="false">'Nigeria PL'!N9</f>
         <v>291167.5</v>
       </c>
-      <c r="N16" s="11" t="n">
+      <c r="N16" s="12" t="n">
         <f aca="false">'Nigeria PL'!O9</f>
         <v>302366.25</v>
       </c>
-      <c r="O16" s="11" t="n">
+      <c r="O16" s="12" t="n">
         <f aca="false">'Nigeria PL'!Q9</f>
-        <v>223975</v>
-      </c>
-      <c r="P16" s="11" t="n">
+        <v>103373.076923077</v>
+      </c>
+      <c r="P16" s="12" t="n">
         <f aca="false">'Nigeria PL'!R9</f>
-        <v>223975</v>
-      </c>
-      <c r="Q16" s="11" t="n">
+        <v>103373.076923077</v>
+      </c>
+      <c r="Q16" s="12" t="n">
         <f aca="false">'Nigeria PL'!S9</f>
-        <v>237150</v>
-      </c>
-      <c r="R16" s="11" t="n">
+        <v>109453.846153846</v>
+      </c>
+      <c r="R16" s="12" t="n">
         <f aca="false">'Nigeria PL'!T9</f>
-        <v>237150</v>
-      </c>
-      <c r="S16" s="11" t="n">
+        <v>199705.263157895</v>
+      </c>
+      <c r="S16" s="12" t="n">
         <f aca="false">'Nigeria PL'!U9</f>
-        <v>250325</v>
-      </c>
-      <c r="T16" s="11" t="n">
+        <v>210800</v>
+      </c>
+      <c r="T16" s="12" t="n">
         <f aca="false">'Nigeria PL'!V9</f>
-        <v>263500</v>
-      </c>
-      <c r="U16" s="11" t="n">
+        <v>221894.736842105</v>
+      </c>
+      <c r="U16" s="12" t="n">
         <f aca="false">'Nigeria PL'!W9</f>
-        <v>250325</v>
-      </c>
-      <c r="V16" s="11" t="n">
+        <v>316200</v>
+      </c>
+      <c r="V16" s="12" t="n">
         <f aca="false">'Nigeria PL'!X9</f>
-        <v>237150</v>
-      </c>
-      <c r="W16" s="11" t="n">
+        <v>299557.894736842</v>
+      </c>
+      <c r="W16" s="12" t="n">
         <f aca="false">'Nigeria PL'!Y9</f>
-        <v>263500</v>
-      </c>
-      <c r="X16" s="11" t="n">
+        <v>332842.105263158</v>
+      </c>
+      <c r="X16" s="12" t="n">
         <f aca="false">'Nigeria PL'!Z9</f>
-        <v>276675</v>
-      </c>
-      <c r="Y16" s="11" t="n">
+        <v>358929.72972973</v>
+      </c>
+      <c r="Y16" s="12" t="n">
         <f aca="false">'Nigeria PL'!AA9</f>
-        <v>342550</v>
-      </c>
-      <c r="Z16" s="11" t="n">
+        <v>444389.189189189</v>
+      </c>
+      <c r="Z16" s="12" t="n">
         <f aca="false">'Nigeria PL'!AB9</f>
-        <v>355725</v>
+        <v>461481.081081081</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="C17" s="11" t="n">
+        <v>127</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <f aca="false">'Nigeria PL'!D23</f>
         <v>100245.833333333</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="12" t="n">
         <f aca="false">'Nigeria PL'!E23</f>
         <v>100245.833333333</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <f aca="false">'Nigeria PL'!F23</f>
         <v>100670.833333333</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="12" t="n">
         <f aca="false">'Nigeria PL'!G23</f>
         <v>100670.833333333</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="12" t="n">
         <f aca="false">'Nigeria PL'!H23</f>
         <v>101095.833333333</v>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H17" s="12" t="n">
         <f aca="false">'Nigeria PL'!I23</f>
         <v>101520.833333333</v>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="I17" s="12" t="n">
         <f aca="false">'Nigeria PL'!J23</f>
         <v>101095.833333333</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J17" s="12" t="n">
         <f aca="false">'Nigeria PL'!K23</f>
         <v>100670.833333333</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" s="12" t="n">
         <f aca="false">'Nigeria PL'!L23</f>
         <v>101520.833333333</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="12" t="n">
         <f aca="false">'Nigeria PL'!M23</f>
         <v>101945.833333333</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <f aca="false">'Nigeria PL'!N23</f>
         <v>104070.833333333</v>
       </c>
-      <c r="N17" s="11" t="n">
+      <c r="N17" s="12" t="n">
         <f aca="false">'Nigeria PL'!O23</f>
         <v>104495.833333333</v>
       </c>
-      <c r="O17" s="11" t="n">
+      <c r="O17" s="12" t="n">
         <f aca="false">'Nigeria PL'!Q23</f>
-        <v>104776.5625</v>
-      </c>
-      <c r="P17" s="11" t="n">
+        <v>100199.639423077</v>
+      </c>
+      <c r="P17" s="12" t="n">
         <f aca="false">'Nigeria PL'!R23</f>
-        <v>104776.5625</v>
-      </c>
-      <c r="Q17" s="11" t="n">
+        <v>100199.639423077</v>
+      </c>
+      <c r="Q17" s="12" t="n">
         <f aca="false">'Nigeria PL'!S23</f>
-        <v>105276.5625</v>
-      </c>
-      <c r="R17" s="11" t="n">
+        <v>100430.408653846</v>
+      </c>
+      <c r="R17" s="12" t="n">
         <f aca="false">'Nigeria PL'!T23</f>
-        <v>105276.5625</v>
-      </c>
-      <c r="S17" s="11" t="n">
+        <v>103855.509868421</v>
+      </c>
+      <c r="S17" s="12" t="n">
         <f aca="false">'Nigeria PL'!U23</f>
-        <v>105776.5625</v>
-      </c>
-      <c r="T17" s="11" t="n">
+        <v>104276.5625</v>
+      </c>
+      <c r="T17" s="12" t="n">
         <f aca="false">'Nigeria PL'!V23</f>
-        <v>106276.5625</v>
-      </c>
-      <c r="U17" s="11" t="n">
+        <v>104697.615131579</v>
+      </c>
+      <c r="U17" s="12" t="n">
         <f aca="false">'Nigeria PL'!W23</f>
-        <v>105776.5625</v>
-      </c>
-      <c r="V17" s="11" t="n">
+        <v>108276.5625</v>
+      </c>
+      <c r="V17" s="12" t="n">
         <f aca="false">'Nigeria PL'!X23</f>
-        <v>105276.5625</v>
-      </c>
-      <c r="W17" s="11" t="n">
+        <v>107644.983552632</v>
+      </c>
+      <c r="W17" s="12" t="n">
         <f aca="false">'Nigeria PL'!Y23</f>
-        <v>106276.5625</v>
-      </c>
-      <c r="X17" s="11" t="n">
+        <v>108908.141447368</v>
+      </c>
+      <c r="X17" s="12" t="n">
         <f aca="false">'Nigeria PL'!Z23</f>
-        <v>106776.5625</v>
-      </c>
-      <c r="Y17" s="11" t="n">
+        <v>109898.184121622</v>
+      </c>
+      <c r="Y17" s="12" t="n">
         <f aca="false">'Nigeria PL'!AA23</f>
-        <v>109276.5625</v>
-      </c>
-      <c r="Z17" s="11" t="n">
+        <v>113141.427364865</v>
+      </c>
+      <c r="Z17" s="12" t="n">
         <f aca="false">'Nigeria PL'!AB23</f>
-        <v>109776.5625</v>
+        <v>113790.076013514</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C18" s="5" t="n">
         <f aca="false">C15-C16-C17</f>
@@ -8976,56 +9040,56 @@
       </c>
       <c r="O18" s="5" t="n">
         <f aca="false">O15-O16-O17</f>
-        <v>244998.4375</v>
+        <v>370177.283653846</v>
       </c>
       <c r="P18" s="5" t="n">
         <f aca="false">P15-P16-P17</f>
-        <v>96248.4375</v>
+        <v>-7418.87019230769</v>
       </c>
       <c r="Q18" s="5" t="n">
         <f aca="false">Q15-Q16-Q17</f>
-        <v>82573.4375</v>
+        <v>-13730.4086538461</v>
       </c>
       <c r="R18" s="5" t="n">
         <f aca="false">R15-R16-R17</f>
-        <v>107573.4375</v>
+        <v>-95868.4653340081</v>
       </c>
       <c r="S18" s="5" t="n">
         <f aca="false">S15-S16-S17</f>
-        <v>93898.4375</v>
+        <v>63870.8059210527</v>
       </c>
       <c r="T18" s="5" t="n">
         <f aca="false">T15-T16-T17</f>
-        <v>105223.4375</v>
+        <v>73407.6480263158</v>
       </c>
       <c r="U18" s="5" t="n">
         <f aca="false">U15-U16-U17</f>
-        <v>143898.4375</v>
+        <v>-3423.93092105263</v>
       </c>
       <c r="V18" s="5" t="n">
         <f aca="false">V15-V16-V17</f>
-        <v>132573.4375</v>
+        <v>192797.121710526</v>
       </c>
       <c r="W18" s="5" t="n">
         <f aca="false">W15-W16-W17</f>
-        <v>80223.4375</v>
+        <v>126670.805921053</v>
       </c>
       <c r="X18" s="5" t="n">
         <f aca="false">X15-X16-X17</f>
-        <v>116548.4375</v>
+        <v>162751.03351707</v>
       </c>
       <c r="Y18" s="5" t="n">
         <f aca="false">Y15-Y16-Y17</f>
-        <v>73173.4375</v>
+        <v>123550.464527027</v>
       </c>
       <c r="Z18" s="5" t="n">
         <f aca="false">Z15-Z16-Z17</f>
-        <v>184498.4375</v>
+        <v>267972.086148649</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C19" s="5" t="n">
         <f aca="false">C14+C18</f>
@@ -9077,61 +9141,61 @@
       </c>
       <c r="O19" s="5" t="n">
         <f aca="false">O14+O18</f>
-        <v>3426548.4375</v>
+        <v>3551727.28365384</v>
       </c>
       <c r="P19" s="5" t="n">
         <f aca="false">P14+P18</f>
-        <v>3522796.875</v>
+        <v>3544308.41346154</v>
       </c>
       <c r="Q19" s="5" t="n">
         <f aca="false">Q14+Q18</f>
-        <v>3605370.3125</v>
+        <v>3530578.00480769</v>
       </c>
       <c r="R19" s="5" t="n">
         <f aca="false">R14+R18</f>
-        <v>3712943.75</v>
+        <v>3434709.53947368</v>
       </c>
       <c r="S19" s="5" t="n">
         <f aca="false">S14+S18</f>
-        <v>3806842.1875</v>
+        <v>3498580.34539474</v>
       </c>
       <c r="T19" s="5" t="n">
         <f aca="false">T14+T18</f>
-        <v>3912065.625</v>
+        <v>3571987.99342105</v>
       </c>
       <c r="U19" s="5" t="n">
         <f aca="false">U14+U18</f>
-        <v>4055964.0625</v>
+        <v>3568564.0625</v>
       </c>
       <c r="V19" s="5" t="n">
         <f aca="false">V14+V18</f>
-        <v>4188537.5</v>
+        <v>3761361.18421053</v>
       </c>
       <c r="W19" s="5" t="n">
         <f aca="false">W14+W18</f>
-        <v>4268760.9375</v>
+        <v>3888031.99013158</v>
       </c>
       <c r="X19" s="5" t="n">
         <f aca="false">X14+X18</f>
-        <v>4385309.375</v>
+        <v>4050783.02364865</v>
       </c>
       <c r="Y19" s="5" t="n">
         <f aca="false">Y14+Y18</f>
-        <v>4458482.8125</v>
+        <v>4174333.48817567</v>
       </c>
       <c r="Z19" s="5" t="n">
         <f aca="false">Z14+Z18</f>
-        <v>4642981.25</v>
+        <v>4442305.57432432</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C22" s="7" t="n">
         <f aca="false">C6+C14</f>
@@ -9187,52 +9251,52 @@
       </c>
       <c r="P22" s="7" t="n">
         <f aca="false">P6+P14</f>
-        <v>6091801.04166666</v>
+        <v>6404748.15705128</v>
       </c>
       <c r="Q22" s="7" t="n">
         <f aca="false">Q6+Q14</f>
-        <v>6214960.41666666</v>
+        <v>6268739.26282051</v>
       </c>
       <c r="R22" s="7" t="n">
         <f aca="false">R6+R14</f>
-        <v>6303932.29166666</v>
+        <v>6116951.5224359</v>
       </c>
       <c r="S22" s="7" t="n">
         <f aca="false">S6+S14</f>
-        <v>6455404.16666666</v>
+        <v>5759818.64035087</v>
       </c>
       <c r="T22" s="7" t="n">
         <f aca="false">T6+T14</f>
-        <v>6572688.54166666</v>
+        <v>5802033.93640351</v>
       </c>
       <c r="U22" s="7" t="n">
         <f aca="false">U6+U14</f>
-        <v>6718285.41666666</v>
+        <v>5868091.3377193</v>
       </c>
       <c r="V22" s="7" t="n">
         <f aca="false">V6+V14</f>
-        <v>6960569.79166666</v>
+        <v>5742069.79166666</v>
       </c>
       <c r="W22" s="7" t="n">
         <f aca="false">W6+W14</f>
-        <v>7174541.66666666</v>
+        <v>6106600.87719298</v>
       </c>
       <c r="X22" s="7" t="n">
         <f aca="false">X6+X14</f>
-        <v>7257638.54166666</v>
+        <v>6305816.17324561</v>
       </c>
       <c r="Y22" s="7" t="n">
         <f aca="false">Y6+Y14</f>
-        <v>7431547.91666666</v>
+        <v>6595232.03828829</v>
       </c>
       <c r="Z22" s="7" t="n">
         <f aca="false">Z6+Z14</f>
-        <v>7497019.79166666</v>
+        <v>6786646.48085585</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">C7+C15</f>
@@ -9288,52 +9352,52 @@
       </c>
       <c r="P23" s="7" t="n">
         <f aca="false">P7+P15</f>
-        <v>1062500</v>
+        <v>490384.615384615</v>
       </c>
       <c r="Q23" s="7" t="n">
         <f aca="false">Q7+Q15</f>
-        <v>1062500</v>
+        <v>490384.615384615</v>
       </c>
       <c r="R23" s="7" t="n">
         <f aca="false">R7+R15</f>
-        <v>1125000</v>
+        <v>519230.769230769</v>
       </c>
       <c r="S23" s="7" t="n">
         <f aca="false">S7+S15</f>
-        <v>1125000</v>
+        <v>947368.421052632</v>
       </c>
       <c r="T23" s="7" t="n">
         <f aca="false">T7+T15</f>
-        <v>1187500</v>
+        <v>1000000</v>
       </c>
       <c r="U23" s="7" t="n">
         <f aca="false">U7+U15</f>
-        <v>1250000</v>
+        <v>1052631.57894737</v>
       </c>
       <c r="V23" s="7" t="n">
         <f aca="false">V7+V15</f>
-        <v>1187500</v>
+        <v>1500000</v>
       </c>
       <c r="W23" s="7" t="n">
         <f aca="false">W7+W15</f>
-        <v>1125000</v>
+        <v>1421052.63157895</v>
       </c>
       <c r="X23" s="7" t="n">
         <f aca="false">X7+X15</f>
-        <v>1250000</v>
+        <v>1578947.36842105</v>
       </c>
       <c r="Y23" s="7" t="n">
         <f aca="false">Y7+Y15</f>
-        <v>1312500</v>
+        <v>1702702.7027027</v>
       </c>
       <c r="Z23" s="7" t="n">
         <f aca="false">Z7+Z15</f>
-        <v>1625000</v>
+        <v>2108108.10810811</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C24" s="7" t="n">
         <f aca="false">C8+C16</f>
@@ -9385,56 +9449,56 @@
       </c>
       <c r="O24" s="7" t="n">
         <f aca="false">O8+O16</f>
-        <v>559937.5</v>
+        <v>258432.692307692</v>
       </c>
       <c r="P24" s="7" t="n">
         <f aca="false">P8+P16</f>
-        <v>559937.5</v>
+        <v>258432.692307692</v>
       </c>
       <c r="Q24" s="7" t="n">
         <f aca="false">Q8+Q16</f>
-        <v>592875</v>
+        <v>273634.615384615</v>
       </c>
       <c r="R24" s="7" t="n">
         <f aca="false">R8+R16</f>
-        <v>592875</v>
+        <v>499263.157894737</v>
       </c>
       <c r="S24" s="7" t="n">
         <f aca="false">S8+S16</f>
-        <v>625812.5</v>
+        <v>527000</v>
       </c>
       <c r="T24" s="7" t="n">
         <f aca="false">T8+T16</f>
-        <v>658750</v>
+        <v>554736.842105263</v>
       </c>
       <c r="U24" s="7" t="n">
         <f aca="false">U8+U16</f>
-        <v>625812.5</v>
+        <v>790500</v>
       </c>
       <c r="V24" s="7" t="n">
         <f aca="false">V8+V16</f>
-        <v>592875</v>
+        <v>748894.736842105</v>
       </c>
       <c r="W24" s="7" t="n">
         <f aca="false">W8+W16</f>
-        <v>658750</v>
+        <v>832105.263157895</v>
       </c>
       <c r="X24" s="7" t="n">
         <f aca="false">X8+X16</f>
-        <v>691687.5</v>
+        <v>897324.324324324</v>
       </c>
       <c r="Y24" s="7" t="n">
         <f aca="false">Y8+Y16</f>
-        <v>856375</v>
+        <v>1110972.97297297</v>
       </c>
       <c r="Z24" s="7" t="n">
         <f aca="false">Z8+Z16</f>
-        <v>889312.5</v>
+        <v>1153702.7027027</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C25" s="7" t="n">
         <f aca="false">C9+C17</f>
@@ -9486,56 +9550,56 @@
       </c>
       <c r="O25" s="7" t="n">
         <f aca="false">O9+O17</f>
-        <v>379403.125</v>
+        <v>367960.817307692</v>
       </c>
       <c r="P25" s="7" t="n">
         <f aca="false">P9+P17</f>
-        <v>379403.125</v>
+        <v>367960.817307692</v>
       </c>
       <c r="Q25" s="7" t="n">
         <f aca="false">Q9+Q17</f>
-        <v>380653.125</v>
+        <v>368537.740384615</v>
       </c>
       <c r="R25" s="7" t="n">
         <f aca="false">R9+R17</f>
-        <v>380653.125</v>
+        <v>377100.493421053</v>
       </c>
       <c r="S25" s="7" t="n">
         <f aca="false">S9+S17</f>
-        <v>381903.125</v>
+        <v>378153.125</v>
       </c>
       <c r="T25" s="7" t="n">
         <f aca="false">T9+T17</f>
-        <v>383153.125</v>
+        <v>379205.756578947</v>
       </c>
       <c r="U25" s="7" t="n">
         <f aca="false">U9+U17</f>
-        <v>381903.125</v>
+        <v>388153.125</v>
       </c>
       <c r="V25" s="7" t="n">
         <f aca="false">V9+V17</f>
-        <v>380653.125</v>
+        <v>386574.177631579</v>
       </c>
       <c r="W25" s="7" t="n">
         <f aca="false">W9+W17</f>
-        <v>383153.125</v>
+        <v>389732.072368421</v>
       </c>
       <c r="X25" s="7" t="n">
         <f aca="false">X9+X17</f>
-        <v>384403.125</v>
+        <v>392207.179054054</v>
       </c>
       <c r="Y25" s="7" t="n">
         <f aca="false">Y9+Y17</f>
-        <v>390653.125</v>
+        <v>400315.287162162</v>
       </c>
       <c r="Z25" s="7" t="n">
         <f aca="false">Z9+Z17</f>
-        <v>391903.125</v>
+        <v>401936.908783784</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C26" s="5" t="n">
         <f aca="false">C10+C18</f>
@@ -9587,56 +9651,56 @@
       </c>
       <c r="O26" s="5" t="n">
         <f aca="false">O10+O18</f>
-        <v>517534.375</v>
+        <v>830481.490384615</v>
       </c>
       <c r="P26" s="5" t="n">
         <f aca="false">P10+P18</f>
-        <v>123159.375</v>
+        <v>-136008.894230769</v>
       </c>
       <c r="Q26" s="5" t="n">
         <f aca="false">Q10+Q18</f>
-        <v>88971.8750000001</v>
+        <v>-151787.740384615</v>
       </c>
       <c r="R26" s="5" t="n">
         <f aca="false">R10+R18</f>
-        <v>151471.875</v>
+        <v>-357132.88208502</v>
       </c>
       <c r="S26" s="5" t="n">
         <f aca="false">S10+S18</f>
-        <v>117284.375</v>
+        <v>42215.2960526316</v>
       </c>
       <c r="T26" s="5" t="n">
         <f aca="false">T10+T18</f>
-        <v>145596.875</v>
+        <v>66057.4013157896</v>
       </c>
       <c r="U26" s="5" t="n">
         <f aca="false">U10+U18</f>
-        <v>242284.375</v>
+        <v>-126021.546052632</v>
       </c>
       <c r="V26" s="5" t="n">
         <f aca="false">V10+V18</f>
-        <v>213971.875</v>
+        <v>364531.085526316</v>
       </c>
       <c r="W26" s="5" t="n">
         <f aca="false">W10+W18</f>
-        <v>83096.8750000001</v>
+        <v>199215.296052632</v>
       </c>
       <c r="X26" s="5" t="n">
         <f aca="false">X10+X18</f>
-        <v>173909.375</v>
+        <v>289415.865042674</v>
       </c>
       <c r="Y26" s="5" t="n">
         <f aca="false">Y10+Y18</f>
-        <v>65471.8750000001</v>
+        <v>191414.442567568</v>
       </c>
       <c r="Z26" s="5" t="n">
         <f aca="false">Z10+Z18</f>
-        <v>343784.375</v>
+        <v>552468.496621622</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="3" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C27" s="5" t="n">
         <f aca="false">C11+C19</f>
@@ -9688,51 +9752,51 @@
       </c>
       <c r="O27" s="5" t="n">
         <f aca="false">O11+O19</f>
-        <v>6091801.04166666</v>
+        <v>6404748.15705128</v>
       </c>
       <c r="P27" s="5" t="n">
         <f aca="false">P11+P19</f>
-        <v>6214960.41666666</v>
+        <v>6268739.26282051</v>
       </c>
       <c r="Q27" s="5" t="n">
         <f aca="false">Q11+Q19</f>
-        <v>6303932.29166666</v>
+        <v>6116951.5224359</v>
       </c>
       <c r="R27" s="5" t="n">
         <f aca="false">R11+R19</f>
-        <v>6455404.16666666</v>
+        <v>5759818.64035087</v>
       </c>
       <c r="S27" s="5" t="n">
         <f aca="false">S11+S19</f>
-        <v>6572688.54166666</v>
+        <v>5802033.93640351</v>
       </c>
       <c r="T27" s="5" t="n">
         <f aca="false">T11+T19</f>
-        <v>6718285.41666666</v>
+        <v>5868091.3377193</v>
       </c>
       <c r="U27" s="5" t="n">
         <f aca="false">U11+U19</f>
-        <v>6960569.79166666</v>
+        <v>5742069.79166666</v>
       </c>
       <c r="V27" s="5" t="n">
         <f aca="false">V11+V19</f>
-        <v>7174541.66666666</v>
+        <v>6106600.87719298</v>
       </c>
       <c r="W27" s="5" t="n">
         <f aca="false">W11+W19</f>
-        <v>7257638.54166666</v>
+        <v>6305816.17324561</v>
       </c>
       <c r="X27" s="5" t="n">
         <f aca="false">X11+X19</f>
-        <v>7431547.91666666</v>
+        <v>6595232.03828829</v>
       </c>
       <c r="Y27" s="5" t="n">
         <f aca="false">Y11+Y19</f>
-        <v>7497019.79166666</v>
+        <v>6786646.48085585</v>
       </c>
       <c r="Z27" s="5" t="n">
         <f aca="false">Z11+Z19</f>
-        <v>7840804.16666666</v>
+        <v>7339114.97747748</v>
       </c>
     </row>
   </sheetData>

--- a/Lumin Light Financial Model - 2025-2026.xlsx
+++ b/Lumin Light Financial Model - 2025-2026.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="135">
   <si>
     <t xml:space="preserve">Lumin Light — 2025-2026 Financial Model — Assumptions</t>
   </si>
@@ -175,6 +175,18 @@
   </si>
   <si>
     <t xml:space="preserve">STARTING CASH BALANCE — Jan 1, 2025 ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHANNEL REVENUE TARGET SPLIT — 2026 (% of Annual Revenue, by Subsidiary)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Institutional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
   </si>
   <si>
     <t xml:space="preserve">Lumin Light — Headcount &amp; Salaries</t>
@@ -798,7 +810,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:N44"/>
+  <dimension ref="B1:N49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -1213,6 +1225,55 @@
       </c>
       <c r="C44" s="4" t="n">
         <v>2200000</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <f aca="false">C48+D48</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <f aca="false">C49+D49</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1242,31 +1303,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>6</v>
@@ -1281,7 +1342,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>6</v>
@@ -1296,7 +1357,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>6</v>
@@ -1311,7 +1372,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>6</v>
@@ -1326,7 +1387,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>7</v>
@@ -1341,7 +1402,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C10" s="0" t="s">
         <v>6</v>
@@ -1356,7 +1417,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C11" s="0" t="s">
         <v>6</v>
@@ -1371,7 +1432,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C12" s="0" t="s">
         <v>7</v>
@@ -1386,7 +1447,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C13" s="0" t="s">
         <v>6</v>
@@ -1401,7 +1462,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C14" s="0" t="s">
         <v>6</v>
@@ -1416,7 +1477,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C15" s="0" t="s">
         <v>6</v>
@@ -1431,7 +1492,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C16" s="0" t="s">
         <v>7</v>
@@ -1446,7 +1507,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C17" s="0" t="s">
         <v>6</v>
@@ -1461,7 +1522,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" s="0" t="s">
         <v>7</v>
@@ -1476,7 +1537,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C19" s="0" t="s">
         <v>6</v>
@@ -1491,7 +1552,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>7</v>
@@ -1506,7 +1567,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C21" s="0" t="s">
         <v>7</v>
@@ -1521,7 +1582,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C22" s="0" t="s">
         <v>6</v>
@@ -1536,7 +1597,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C23" s="0" t="s">
         <v>7</v>
@@ -1551,7 +1612,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C24" s="0" t="s">
         <v>6</v>
@@ -1566,7 +1627,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D26" s="5" t="n">
         <f aca="false">SUM(D5:D24)</f>
@@ -1579,7 +1640,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="0" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D27" s="7" t="n">
         <f aca="false">SUMIF(C5:C24,"Lumin Light USA",D5:D24)</f>
@@ -1592,7 +1653,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D28" s="7" t="n">
         <f aca="false">SUMIF(C5:C24,"Lumin Light Nigeria",D5:D24)</f>
@@ -1629,20 +1690,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -1681,7 +1742,7 @@
         <v>40</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>29</v>
@@ -1722,7 +1783,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C6" s="5" t="n">
         <f aca="false">SUM(D6:O6)</f>
@@ -1831,7 +1892,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">SUM(D9:O9)</f>
@@ -1940,7 +2001,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(D11:O11)</f>
@@ -2049,7 +2110,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">IF(C6=0,0,C11/C6)</f>
@@ -2158,12 +2219,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">SUM(D15:O15)</f>
@@ -2272,7 +2333,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">SUM(D16:O16)</f>
@@ -3035,7 +3096,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C23" s="5" t="n">
         <f aca="false">SUM(D23:O23)</f>
@@ -3144,7 +3205,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C25" s="5" t="n">
         <f aca="false">SUM(D25:O25)</f>
@@ -3253,7 +3314,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">IF(C6=0,0,C25/C6)</f>
@@ -3362,7 +3423,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C28" s="7" t="n">
         <f aca="false">SUM(D28:O28)</f>
@@ -3471,7 +3532,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C30" s="5" t="n">
         <f aca="false">SUM(D30:O30)</f>
@@ -3580,7 +3641,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">IF(C6=0,0,C30/C6)</f>
@@ -3713,20 +3774,20 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -3765,7 +3826,7 @@
         <v>40</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>29</v>
@@ -3806,7 +3867,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C6" s="5" t="n">
         <f aca="false">SUM(D6:O6)</f>
@@ -3915,7 +3976,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">SUM(D9:O9)</f>
@@ -4024,7 +4085,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">SUM(D11:O11)</f>
@@ -4133,7 +4194,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">IF(C6=0,0,C11/C6)</f>
@@ -4242,12 +4303,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">SUM(D15:O15)</f>
@@ -4356,7 +4417,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">SUM(D16:O16)</f>
@@ -5119,7 +5180,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C23" s="5" t="n">
         <f aca="false">SUM(D23:O23)</f>
@@ -5228,7 +5289,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C25" s="5" t="n">
         <f aca="false">SUM(D25:O25)</f>
@@ -5337,7 +5398,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">IF(C6=0,0,C25/C6)</f>
@@ -5446,7 +5507,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C28" s="7" t="n">
         <f aca="false">SUM(D28:O28)</f>
@@ -5555,7 +5616,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C30" s="5" t="n">
         <f aca="false">SUM(D30:O30)</f>
@@ -5664,7 +5725,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">IF(C6=0,0,C30/C6)</f>
@@ -5797,23 +5858,23 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>29</v>
@@ -5852,7 +5913,7 @@
         <v>40</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>29</v>
@@ -5893,7 +5954,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C6" s="5" t="n">
         <f aca="false">'USA PL'!C6+'Nigeria PL'!C6</f>
@@ -6002,7 +6063,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">'USA PL'!C9+'Nigeria PL'!C9</f>
@@ -6111,7 +6172,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">'USA PL'!C11+'Nigeria PL'!C11</f>
@@ -6220,7 +6281,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">IF(C6=0,0,C11/C6)</f>
@@ -6329,12 +6390,12 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C15" s="7" t="n">
         <f aca="false">'USA PL'!C15+'Nigeria PL'!C15</f>
@@ -6443,7 +6504,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">'USA PL'!C16+'Nigeria PL'!C16</f>
@@ -7206,7 +7267,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C23" s="5" t="n">
         <f aca="false">'USA PL'!C23+'Nigeria PL'!C23</f>
@@ -7315,7 +7376,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C25" s="5" t="n">
         <f aca="false">'USA PL'!C25+'Nigeria PL'!C25</f>
@@ -7424,7 +7485,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">IF(C6=0,0,C25/C6)</f>
@@ -7533,7 +7594,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="0" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C28" s="7" t="n">
         <f aca="false">'USA PL'!C28+'Nigeria PL'!C28</f>
@@ -7642,7 +7703,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C30" s="5" t="n">
         <f aca="false">'USA PL'!C30+'Nigeria PL'!C30</f>
@@ -7751,7 +7812,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C31" s="14" t="n">
         <f aca="false">IF(C6=0,0,C30/C6)</f>
@@ -7884,86 +7945,86 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Y4" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="Z4" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7973,7 +8034,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C6" s="12" t="n">
         <f aca="false">Assumptions!$C$43</f>
@@ -8074,7 +8135,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C7" s="12" t="n">
         <f aca="false">'USA PL'!D6</f>
@@ -8175,7 +8236,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">'USA PL'!D9</f>
@@ -8276,7 +8337,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C9" s="12" t="n">
         <f aca="false">'USA PL'!D23</f>
@@ -8377,7 +8438,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C10" s="5" t="n">
         <f aca="false">C7-C8-C9</f>
@@ -8478,7 +8539,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C11" s="5" t="n">
         <f aca="false">C6+C10</f>
@@ -8584,7 +8645,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">Assumptions!$C$44</f>
@@ -8685,7 +8746,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C15" s="12" t="n">
         <f aca="false">'Nigeria PL'!D6</f>
@@ -8786,7 +8847,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C16" s="12" t="n">
         <f aca="false">'Nigeria PL'!D9</f>
@@ -8887,7 +8948,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">'Nigeria PL'!D23</f>
@@ -8988,7 +9049,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C18" s="5" t="n">
         <f aca="false">C15-C16-C17</f>
@@ -9089,7 +9150,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C19" s="5" t="n">
         <f aca="false">C14+C18</f>
@@ -9190,12 +9251,12 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C22" s="7" t="n">
         <f aca="false">C6+C14</f>
@@ -9296,7 +9357,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">C7+C15</f>
@@ -9397,7 +9458,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C24" s="7" t="n">
         <f aca="false">C8+C16</f>
@@ -9498,7 +9559,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C25" s="7" t="n">
         <f aca="false">C9+C17</f>
@@ -9599,7 +9660,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C26" s="5" t="n">
         <f aca="false">C10+C18</f>
@@ -9700,7 +9761,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C27" s="5" t="n">
         <f aca="false">C11+C19</f>
